--- a/data/Ngan-Hang-Cau-Hoi.xlsx
+++ b/data/Ngan-Hang-Cau-Hoi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nhing\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9f54d0bdb7235122/Documents/My App/trac-nghiem-luat-dau-thau/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B32B0D1-E964-45B5-876C-751CC32868FC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0822E189-CD53-41B9-B216-EFA7EF505EBC}"/>
   </bookViews>
@@ -64,13 +64,6 @@
     <t>Đối với đấu thầu qua mạng, trường hợp cần sửa đổi E-HSDT đã nộp trước thời điểm đóng thầu, nhà thầu phải thực hiện theo phương án nào sau đây trong trường hợp E-HSMT của gói thầu này không phải sửa đổi?</t>
   </si>
   <si>
-    <t>A. Phải tiến hành rút toàn bộ E-HSDT đã nộp trước đó để sửa đổi cho phù hợp và tiến hành nộp lại
-E-HSDT mới
-B. Không phải tiến hành rút toàn bộ E-HSDT đã nộp trước đó, chỉ cần sửa đổi cho phù hợp và tiến hành nộp lại E-HSDT mới
-C. Sửa đổi cho phù hợp E-HSDT đã nộp mà không phải nộp lại E- HSDT mới
-D. Nhà thầu không được sửa đổi E-HSDT đã nộp</t>
-  </si>
-  <si>
     <t>Đối với gói thầu thuộc phạm vi điều chỉnh của Hiệp định Đối tác Toàn diện và Tiến bộ
 Xuyên Thái Bình Dương (CPTPP), ngôn ngữ sử dụng trong đấu thầu nội khối là:</t>
   </si>
@@ -1361,14 +1354,6 @@
 quy định trong hồ sơ mời thầu như thế nào là phù hợp?</t>
   </si>
   <si>
-    <t>A. Nhà thầu đã hoàn thành công trình xây dựng nhà, kết cấu dạng nhà cấp II, có giá trị tối thiểu là
-50% x (2X) VND
-B. Nhà thầu đã hoàn thành công trình xây dựng nhà, kết cấu dạng nhà cấp II, có giá trị tối thiểu là 50% x (2X) VND, trong đó phải bao gồm hạng mục hàng rào bảo vệ, nhà bảo vệ
-C. Nhà thầu đã hoàn thành công trình xây dựng nhà, kết cấu dạng nhà cấp III, có giá trị tối thiểu là
-50% x (2X) VND
-D. Nhà thầu đã hoàn thành công trình xây dựng nhà, kết cấu dạng nhà cấp III, có giá trị tối thiểu là 50% x (2X) VND, trong đó phải bao gồm hạng mục hàng rào bảo vệ, nhà bảo vệ</t>
-  </si>
-  <si>
     <t>A. Phải sử dụng phương pháp đánh giá “đạt”, “không đạt”
 B. Phải sử dụng phương pháp chấm điểm
 C. Được sử dụng một trong hai phương pháp “đạt”, “không đạt” hoặc chấm điểm
@@ -1396,14 +1381,6 @@
 B. Có giá trị bằng 70% giá gói thầu
 C. Có giá trị bằng 50% giá trị theo chu kỳ 01 năm của gói thầu
 D. Có giá trị tối thiểu bằng 50% giá gói thầu</t>
-  </si>
-  <si>
-    <t>A. Chủ đầu tư phải ghi tỷ lệ % giá trị dành cho nhà thầu phụ trong E-BDL làm cơ sở để nhà thầu lập
-E-HSDT
-B. Năng lực và kinh nghiệm của nhà thầu phụ sẽ không được xem xét khi đánh giá E-HSDT của nhà thầu
-C. Nhà thầu được ký kết hợp đồng với các nhà thầu phụ trong danh sách các nhà thầu phụ nêu trong
-E-HSDT
-D. Nhà thầu được ký kết hợp đồng với các nhà thầu phụ được chủ đầu tư chấp thuận để tham gia thực hiện cung cấp dịch vụ liên quan</t>
   </si>
   <si>
     <t>Trong  quá  trình  đánh  giá  hồ  sơ  dự  thầu  gói thầu áp dụng đấu thầu rộng rãi, chủ đầu tư phát hiện người đại diện theo pháp luật của 02 nhà thầu tham dự thầu là anh em ruột thì xem xét,
@@ -1613,13 +1590,6 @@
 D. Chủ đầu tư coi là tình huống trong đấu thầu và xử lý trên cơ sở bảo đảm cạnh tranh, công bằng, minh bạch, hiệu quả kinh tế và trách nhiệm giải trình</t>
   </si>
   <si>
-    <t>A. Gói thầu xây lắp, hàng hóa và dịch vụ phi tư vấn áp dụng hình thức chào hàng cạnh tranh và sử dụng phương pháp dựa trên kỹ thuật để đánh giá về tài chính và có giá đề nghị trúng thầu vượt giá gói thầu được phép thương thảo về chi phí
-B. Gói thầu mua thuốc áp dụng phương thức một giai đoạn hai túi hồ sơ và sử dụng phương pháp kết hợp giữa kỹ thuật và giá được phép thương thảo về chi phí trong quá trình thương thảo hợp đồng
-C. Gói thầu dịch vụ tư vấn áp dụng hình thức đấu thầu rộng rãi được phép thương thảo về chi phí trong quá trình thương thảo hợp đồng
-D. Không được phép thương thảo về chi phí trong quá trình thương thảo hợp đồng đối với tất cả các
-gói thầu, trừ trường hợp nhà thầu tự nguyện giảm giá</t>
-  </si>
-  <si>
     <t>A. Hợp đồng thuốc đã cung cấp thuốc cho cơ sở khám chữa bệnh tư nhân
 B. Hợp đồng thuốc đã cung cấp thuốc cho các cơ sở kinh doanh thuốc
 C. Phương án A và B đều đúng
@@ -1663,13 +1633,6 @@
 giá là một công trình xây lắp tương tự?</t>
   </si>
   <si>
-    <t>A. Nhà thầu có 2 công trình xây dựng có loại kết cấu dạng nhà cấp III với giá trị đã hoàn thành toàn bộ lần lượt là 30 tỷ đồng, 50 tỷ đồng
-B. Nhà thầu có 2 công trình xây dựng có loại kết cấu dạng nhà cấp III với giá trị đã hoàn thành toàn bộ lần lượt là 30 tỷ đồng, 20 tỷ đồng
-C. Nhà thầu có 3 công trình xây dựng có loại kết cấu dạng nhà cấp III với giá trị đã hoàn thành toàn bộ lần lượt là 30 tỷ đồng, 20 tỷ đồng, 10 tỷ đồng
-D. Nhà thầu có 1 công trình xây dựng có loại kết cấu dạng nhà cấp III với giá trị đã hoàn thành toàn
-bộ là 60 tỷ đồng</t>
-  </si>
-  <si>
     <t>Gói thầu cung cấp dịch vụ vệ sinh tòa nhà do Sở Tài chính tỉnh X làm chủ đầu tư có giá gói thầu 01 tỷ đồng, thời gian thực hiện là 12 tháng, hợp đồng tương tự yêu cầu 30% giá
 gói thầu. Trường hợp nào sau đây nhà thầu được coi là đáp ứng về giá trị của hợp đồng tương tự?</t>
   </si>
@@ -1756,13 +1719,6 @@
   <si>
     <t>Hồ sơ hợp đồng bao gồm các tài liệu nào sau
 đây?</t>
-  </si>
-  <si>
-    <t>A. Văn bản hợp đồng
-B. Phụ lục hợp đồng gồm danh mục chi tiết về phạm vi công việc, biểu giá, tiến độ thực hiện (nếu
-có)
-C. Quyết định phê duyệt kết quả lựa chọn nhà thầu
-D. Tất cả các phương án trên.</t>
   </si>
   <si>
     <t>A. Được đăng tải trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 24 giờ kể từ thời điểm mở thầu
@@ -1877,13 +1833,6 @@
 D. Phương án A và B đều đúng</t>
   </si>
   <si>
-    <t>A. Thời hạn áp dụng thỏa thuận khung được quy định là 40 tháng
-B. Thời hạn áp dụng thỏa thuận khung được quy định trong kế hoạch lựa chọn nhà thầu nhưng không
-quá 36 tháng
-C. Thời hạn áp dụng thỏa thuận khung do người có thẩm quyền quyết định trong kế hoạch lựa chọn nhà thầu
-D. Phương án B và C đều đúng</t>
-  </si>
-  <si>
     <t>A. Nhà thầu đã ký kết thỏa thuận khung phải thực hiện biện pháp bảo đảm thực hiện hợp đồng trước hoặc cùng thời điểm hợp đồng có hiệu lực cho đơn vị mua sắm tập trung
 B. Nhà thầu đã ký kết thỏa thuận khung phải thực hiện biện pháp bảo đảm thực hiện hợp đồng trước hoặc cùng thời điểm hợp đồng có hiệu lực cho đơn vị có nhu cầu mua sắm
 C. Nhà thầu đã ký kết thỏa thuận khung không phải thực hiện biện pháp bảo đảm thực hiện hợp đồng trước thời điểm hợp đồng có hiệu lực cho đơn vị có nhu cầu mua sắm
@@ -1914,22 +1863,8 @@
 D. Đơn vị mua sắm tập trung thực hiện trách nhiệm của tổ chuyên gia theo quy định của Luật Đấu thầu</t>
   </si>
   <si>
-    <t>A. Nhà thầu sẽ bị khóa tài khoản trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 06 tháng kể từ ngày đơn vị có nhu cầu mua sắm công khai tên nhà thầu trên Hệ thống mạng đấu thầu quốc gia
-B. Nhà thầu sẽ bị khóa tài khoản trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 06 tháng kể từ ngày đơn vị mua sắm tập trung công khai tên nhà thầu trên Hệ thống mạng đấu thầu quốc gia, trừ trường hợp bất khả kháng
-C. Nhà thầu sẽ bị khóa tài khoản trên Hệ thống mạng đấu thầu quốc gia trong thời hạn trong thời hạn 03 tháng kể từ ngày Bộ Tài chính nhận được văn bản đề nghị của đơn vị có nhu cầu mua sắm, trừ trường hợp bất khả kháng
-D. Nhà thầu sẽ bị khóa tài khoản trên Hệ thống mạng đấu thầu quốc gia trong thời hạn trong thời hạn 06 tháng kể từ ngày Bộ Tài chính nhận được văn bản đề nghị của đơn vị có nhu cầu mua sắm, trừ
-trường hợp bất khả kháng</t>
-  </si>
-  <si>
     <t>Đối với gói thầu mua sắm tập trung áp dụng lựa chọn nhà thầu căn cứ theo khả năng cung cấp và áp dụng phương pháp giá thấp nhất,
 việc lựa chọn danh sách nhà thầu trúng thầu được thực hiện như thế nào?</t>
-  </si>
-  <si>
-    <t>A. Phải đảm bảo tổng số lượng hàng hóa mà các nhà thầu trúng thầu chào thầu tối thiểu bằng số lượng hàng hóa nêu trong hồ sơ mời thầu, đồng thời bảo đảm điểm tổng hợp của gói thầu cao nhất
-B. Phải đảm bảo tổng số lượng hàng hóa mà các nhà thầu trúng thầu chào thầu bằng số lượng hàng hóa nêu trong hồ sơ mời thầu, đồng thời bảo đảm tổng giá đề nghị trúng thầu của gói thầu cao nhất
-C. Phải đảm bảo tổng số lượng hàng hóa mà các nhà thầu trúng thầu chào thầu bằng số lượng hàng hóa nêu trong hồ sơ mời thầu, đồng thời bảo đảm tổng giá đề nghị trúng thầu của gói thầu thấp nhất
-D. Phải đảm bảo tổng số lượng hàng hóa mà các nhà thầu trúng thầu chào thầu bằng số lượng hàng
-hóa nêu trong hồ sơ mời thầu, đồng thời bảo đảm tổng giá đánh giá của gói thầu là thấp nhất</t>
   </si>
   <si>
     <t>Đối với gói thầu mua sắm tập trung áp dụng lựa chọn nhà thầu căn cứ khối lượng mời
@@ -2079,14 +2014,6 @@
     <t>Thành viên A trong nhà thầu liên danh A-B thực hiện hành vi "làm giả hoặc làm sai lệch thông tin, hồ sơ, tài liệu trong đấu thầu" thì
 việc cấm tham gia hoạt động đấu thầu được xử
 lý như thế nào?</t>
-  </si>
-  <si>
-    <t>A. Cấm tham gia hoạt động đấu thầu từ 03 năm đến 05 năm đối với thành viên A
-B. Cấm tham gia hoạt động đấu thầu từ 01 năm đến dưới 03 năm đối với thành viên A
-C. Cấm tham gia hoạt động đấu thầu từ 03 năm đến 05 năm đối với tất cả thành viên trong nhà thầu
-liên danh A-B
-D. Cấm tham gia hoạt động đấu thầu từ 01 năm đến 03 năm đối với tất cả thành viên trong nhà thầu
-liên danh A-B</t>
   </si>
   <si>
     <t>Đình chỉ cuộc thầu được thực hiện trong thời
@@ -2412,13 +2339,6 @@
 D. Tất cả các đáp án trên đều không đúng</t>
   </si>
   <si>
-    <t>A. Từ ngày có thời điểm đóng thầu đến khi có kết quả lựa chọn nhà thầu
-B. Từ ngày phát hành hồ sơ mời sơ tuyển, hồ sơ mời quan tâm, hồ sơ mời thầu, hồ sơ yêu cầu đến trước khi ký kết hợp đồng, thỏa thuận khung đối với mua sắm tập trung
-C. Từ ngày có thời điểm đóng thầu đến khi ký kết hợp đồng, thỏa thuận khung đối với mua sắm tập
-trung
-D. Từ ngày phát hành hồ sơ mời sơ tuyển, hồ sơ mời quan tâm, hồ sơ mời thầu, hồ sơ yêu cầu kể cả sau khi đã ký hợp đồng</t>
-  </si>
-  <si>
     <t>A. Yêu cầu nhà thầu thực hiện các thủ tục để mở khóa tài khoản làm cơ sở xem xét, đánh giá E- HSDT của nhà thầu
 B. Tiếp tục xem xét, đánh giá E-HSDT của nhà thầu
 C. Không tiếp tục xem xét, đánh giá E-HSDT của nhà thầu
@@ -3025,14 +2945,6 @@
 B. Thời gian hiệu lực của bảo lãnh dự thầu luôn đáp ứng yêu cầu trong E-HSMT
 C. Đối tượng thụ hưởng bảo lãnh dự thầu luôn đáp ứng yêu cầu trong E-HSMT
 D. Các phương án trên đều đúng</t>
-  </si>
-  <si>
-    <t>Gói thầu mua sắm hàng hóa có:
-- Thời điểm đóng thầu theo E-TBMT là: 8h00 ngày 25/9/2025
-- Hiệu lực của bảo đảm dự thầu theo yêu cầu của E-HSMT là: 90 ngày
-- Do lỗi hệ thống nên Hệ thống tự động gia hạn thời điểm đóng thầu mới là: 11h ngày 26/9/2025
-Nhà thầu A đã nộp E-HSDT trước thời điểm Hệ thống xảy ra sự cố với hiệu lực của bảo đảm dự thầu là 90 ngày kể từ ngày 25/9/2025; Nhà thầu B nộp E-HSDT sau khi Hệ thống được khắc phục và trước thời điểm đóng thầu mới với hiệu lực của bảo đảm dự thầu là 90 ngày kể từ ngày 26/9/2025. Trong trường hợp này, bảo đảm dự thầu của nhà thầu A và nhà thầu B được đánh giá như thế
-nào?</t>
   </si>
   <si>
     <t>A. Bảo đảm dự thầu của nhà thầu A được đánh giá là không hợp lệ; Bảo đảm dự thầu của nhà thầu B được đánh giá là hợp lệ
@@ -3496,13 +3408,6 @@
 B. Chỉ phải đính kèm hồ sơ năng lực và kinh nghiệm của mình khi tham dự thầu
 C. Không phải cập nhật năng lực và kinh nghiệm của mình khi tham dự thầu nhưng phải đính kèm hồ sơ năng lực và kinh nghiệm
 D. Phương án A và C đều đúng</t>
-  </si>
-  <si>
-    <t>A. Quy trình 02 áp dụng đối với gói thầu mua sắm hàng hóa, dịch vụ phi tư vấn, máy đặt, máy mượn theo phương thức một giai đoạn một túi hồ sơ, sử dụng phương pháp “giá thấp nhất” và các nhà thầu, E-HSDT đều không có bất kỳ ưu đãi nào
-B. Hệ thống tự động xếp hạng nhà thầu theo giá dự thầu sau khi trừ đi giá trị giảm giá (nếu có) thấp nhất (không phải phê duyệt danh sách xếp hạng nhà thầu) đối với gói thầu áp dụng quy trình 02
-C. Trường hợp có từ 02 nhà thầu trở lên cùng xếp thứ nhất thì không đánh giá theo quy trình 02 mà phải đánh giá
-theo quy trình 01
-D. Cả 3 đáp án đều đúng</t>
   </si>
   <si>
     <t>A. Đánh giá E-HSDT của tất cả nhà thầu tham dự thầu về: tính hợp lệ của E-HSDT; năng lực và kinh nghiệm; kỹ thuật. Trường hợp nhà thầu không đáp ứng bước trước thì không tiếp tục đánh giá bước tiếp theo
@@ -3850,6 +3755,87 @@
 B. Sau khi tính ưu đãi, nếu các hồ sơ dự thầu xếp hạng ngang nhau thì ưu tiên cho nhà thầu có đề xuất chi phí nội khối thấp hơn.
 C. Nhà thầu được hưởng tất cả các ưu đãi thuộc đối tượng áp dụng
 D. Sau khi tính ưu đãi, nếu các hồ sơ dự thầu xếp hạng ngang nhau thì ưu tiên cho nhà thầu có đề xuất chi phí nội khối ít chênh lệch nhất so với yêu cầu của hồ sơ mời thầu</t>
+  </si>
+  <si>
+    <t>Gói thầu mua sắm hàng hóa có:
+- Thời điểm đóng thầu theo E-TBMT là: 8h00 ngày 25/9/2025
+- Hiệu lực của bảo đảm dự thầu theo yêu cầu của E-HSMT là: 90 ngày
+- Do lỗi hệ thống nên Hệ thống tự động gia hạn thời điểm đóng thầu mới là: 11h ngày 26/9/2025
+Nhà thầu A đã nộp E-HSDT trước thời điểm Hệ thống xảy ra sự cố với hiệu lực của bảo đảm dự thầu là 90 ngày kể từ ngày 25/9/2025; Nhà thầu B nộp E-HSDT sau khi Hệ thống được khắc phục và trước thời điểm đóng thầu mới với hiệu lực của bảo đảm dự thầu là 90 ngày kể từ ngày 26/9/2025. Trong trường hợp này, bảo đảm dự thầu của nhà thầu A và nhà thầu B được đánh giá như thế nào?</t>
+  </si>
+  <si>
+    <t>A. Thời hạn áp dụng thỏa thuận khung được quy định là 40 tháng
+B. Thời hạn áp dụng thỏa thuận khung được quy định trong kế hoạch lựa chọn nhà thầu nhưng không quá 36 tháng
+C. Thời hạn áp dụng thỏa thuận khung do người có thẩm quyền quyết định trong kế hoạch lựa chọn nhà thầu
+D. Phương án B và C đều đúng</t>
+  </si>
+  <si>
+    <t>A. Nhà thầu sẽ bị khóa tài khoản trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 06 tháng kể từ ngày đơn vị có nhu cầu mua sắm công khai tên nhà thầu trên Hệ thống mạng đấu thầu quốc gia
+B. Nhà thầu sẽ bị khóa tài khoản trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 06 tháng kể từ ngày đơn vị mua sắm tập trung công khai tên nhà thầu trên Hệ thống mạng đấu thầu quốc gia, trừ trường hợp bất khả kháng
+C. Nhà thầu sẽ bị khóa tài khoản trên Hệ thống mạng đấu thầu quốc gia trong thời hạn trong thời hạn 03 tháng kể từ ngày Bộ Tài chính nhận được văn bản đề nghị của đơn vị có nhu cầu mua sắm, trừ trường hợp bất khả kháng
+D. Nhà thầu sẽ bị khóa tài khoản trên Hệ thống mạng đấu thầu quốc gia trong thời hạn trong thời hạn 06 tháng kể từ ngày Bộ Tài chính nhận được văn bản đề nghị của đơn vị có nhu cầu mua sắm, trừ trường hợp bất khả kháng</t>
+  </si>
+  <si>
+    <t>A. Phải đảm bảo tổng số lượng hàng hóa mà các nhà thầu trúng thầu chào thầu tối thiểu bằng số lượng hàng hóa nêu trong hồ sơ mời thầu, đồng thời bảo đảm điểm tổng hợp của gói thầu cao nhất
+B. Phải đảm bảo tổng số lượng hàng hóa mà các nhà thầu trúng thầu chào thầu bằng số lượng hàng hóa nêu trong hồ sơ mời thầu, đồng thời bảo đảm tổng giá đề nghị trúng thầu của gói thầu cao nhất
+C. Phải đảm bảo tổng số lượng hàng hóa mà các nhà thầu trúng thầu chào thầu bằng số lượng hàng hóa nêu trong hồ sơ mời thầu, đồng thời bảo đảm tổng giá đề nghị trúng thầu của gói thầu thấp nhất
+D. Phải đảm bảo tổng số lượng hàng hóa mà các nhà thầu trúng thầu chào thầu bằng số lượng hàng hóa nêu trong hồ sơ mời thầu, đồng thời bảo đảm tổng giá đánh giá của gói thầu là thấp nhất</t>
+  </si>
+  <si>
+    <t>A. Cấm tham gia hoạt động đấu thầu từ 03 năm đến 05 năm đối với thành viên A
+B. Cấm tham gia hoạt động đấu thầu từ 01 năm đến dưới 03 năm đối với thành viên A
+C. Cấm tham gia hoạt động đấu thầu từ 03 năm đến 05 năm đối với tất cả thành viên trong nhà thầu liên danh A-B
+D. Cấm tham gia hoạt động đấu thầu từ 01 năm đến 03 năm đối với tất cả thành viên trong nhà thầu
+liên danh A-B</t>
+  </si>
+  <si>
+    <t>A. Từ ngày có thời điểm đóng thầu đến khi có kết quả lựa chọn nhà thầu
+B. Từ ngày phát hành hồ sơ mời sơ tuyển, hồ sơ mời quan tâm, hồ sơ mời thầu, hồ sơ yêu cầu đến trước khi ký kết hợp đồng, thỏa thuận khung đối với mua sắm tập trung
+C. Từ ngày có thời điểm đóng thầu đến khi ký kết hợp đồng, thỏa thuận khung đối với mua sắm tập trung
+D. Từ ngày phát hành hồ sơ mời sơ tuyển, hồ sơ mời quan tâm, hồ sơ mời thầu, hồ sơ yêu cầu kể cả sau khi đã ký hợp đồng</t>
+  </si>
+  <si>
+    <t>A. Nhà thầu đã hoàn thành công trình xây dựng nhà, kết cấu dạng nhà cấp II, có giá trị tối thiểu là 50% x (2X) VND
+B. Nhà thầu đã hoàn thành công trình xây dựng nhà, kết cấu dạng nhà cấp II, có giá trị tối thiểu là 50% x (2X) VND, trong đó phải bao gồm hạng mục hàng rào bảo vệ, nhà bảo vệ
+C. Nhà thầu đã hoàn thành công trình xây dựng nhà, kết cấu dạng nhà cấp III, có giá trị tối thiểu là 50% x (2X) VND
+D. Nhà thầu đã hoàn thành công trình xây dựng nhà, kết cấu dạng nhà cấp III, có giá trị tối thiểu là 50% x (2X) VND, trong đó phải bao gồm hạng mục hàng rào bảo vệ, nhà bảo vệ</t>
+  </si>
+  <si>
+    <t>A. Chủ đầu tư phải ghi tỷ lệ % giá trị dành cho nhà thầu phụ trong E-BDL làm cơ sở để nhà thầu lập E-HSDT
+B. Năng lực và kinh nghiệm của nhà thầu phụ sẽ không được xem xét khi đánh giá E-HSDT của nhà thầu
+C. Nhà thầu được ký kết hợp đồng với các nhà thầu phụ trong danh sách các nhà thầu phụ nêu trong
+E-HSDT
+D. Nhà thầu được ký kết hợp đồng với các nhà thầu phụ được chủ đầu tư chấp thuận để tham gia thực hiện cung cấp dịch vụ liên quan</t>
+  </si>
+  <si>
+    <t>A. Phải tiến hành rút toàn bộ E-HSDT đã nộp trước đó để sửa đổi cho phù hợp và tiến hành nộp lại E-HSDT mới
+B. Không phải tiến hành rút toàn bộ E-HSDT đã nộp trước đó, chỉ cần sửa đổi cho phù hợp và tiến hành nộp lại E-HSDT mới
+C. Sửa đổi cho phù hợp E-HSDT đã nộp mà không phải nộp lại E- HSDT mới
+D. Nhà thầu không được sửa đổi E-HSDT đã nộp</t>
+  </si>
+  <si>
+    <t>A. Gói thầu xây lắp, hàng hóa và dịch vụ phi tư vấn áp dụng hình thức chào hàng cạnh tranh và sử dụng phương pháp dựa trên kỹ thuật để đánh giá về tài chính và có giá đề nghị trúng thầu vượt giá gói thầu được phép thương thảo về chi phí
+B. Gói thầu mua thuốc áp dụng phương thức một giai đoạn hai túi hồ sơ và sử dụng phương pháp kết hợp giữa kỹ thuật và giá được phép thương thảo về chi phí trong quá trình thương thảo hợp đồng
+C. Gói thầu dịch vụ tư vấn áp dụng hình thức đấu thầu rộng rãi được phép thương thảo về chi phí trong quá trình thương thảo hợp đồng
+D. Không được phép thương thảo về chi phí trong quá trình thương thảo hợp đồng đối với tất cả các gói thầu, trừ trường hợp nhà thầu tự nguyện giảm giá</t>
+  </si>
+  <si>
+    <t>A. Nhà thầu có 2 công trình xây dựng có loại kết cấu dạng nhà cấp III với giá trị đã hoàn thành toàn bộ lần lượt là 30 tỷ đồng, 50 tỷ đồng
+B. Nhà thầu có 2 công trình xây dựng có loại kết cấu dạng nhà cấp III với giá trị đã hoàn thành toàn bộ lần lượt là 30 tỷ đồng, 20 tỷ đồng
+C. Nhà thầu có 3 công trình xây dựng có loại kết cấu dạng nhà cấp III với giá trị đã hoàn thành toàn bộ lần lượt là 30 tỷ đồng, 20 tỷ đồng, 10 tỷ đồng
+D. Nhà thầu có 1 công trình xây dựng có loại kết cấu dạng nhà cấp III với giá trị đã hoàn thành toàn bộ là 60 tỷ đồng</t>
+  </si>
+  <si>
+    <t>A. Văn bản hợp đồng
+B. Phụ lục hợp đồng gồm danh mục chi tiết về phạm vi công việc, biểu giá, tiến độ thực hiện (nếu có)
+C. Quyết định phê duyệt kết quả lựa chọn nhà thầu
+D. Tất cả các phương án trên.</t>
+  </si>
+  <si>
+    <t>A. Quy trình 02 áp dụng đối với gói thầu mua sắm hàng hóa, dịch vụ phi tư vấn, máy đặt, máy mượn theo phương thức một giai đoạn một túi hồ sơ, sử dụng phương pháp “giá thấp nhất” và các nhà thầu, E-HSDT đều không có bất kỳ ưu đãi nào
+B. Hệ thống tự động xếp hạng nhà thầu theo giá dự thầu sau khi trừ đi giá trị giảm giá (nếu có) thấp nhất (không phải phê duyệt danh sách xếp hạng nhà thầu) đối với gói thầu áp dụng quy trình 02
+C. Trường hợp có từ 02 nhà thầu trở lên cùng xếp thứ nhất thì không đánh giá theo quy trình 02 mà phải đánh giá theo quy trình 01
+D. Cả 3 đáp án đều đúng</t>
   </si>
 </sst>
 </file>
@@ -4145,66 +4131,6 @@
               </a:lnTo>
               <a:lnTo>
                 <a:pt x="96011" y="0"/>
-              </a:lnTo>
-              <a:close/>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFF00">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>177165</xdr:colOff>
-      <xdr:row>369</xdr:row>
-      <xdr:rowOff>809625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4563110" cy="175260"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="Shape 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3FBB9C15-358E-4891-895C-CDA0BCAD73BB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3987165" y="5337175"/>
-          <a:ext cx="4563110" cy="175260"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst>
-            <a:path w="4563110" h="175260">
-              <a:moveTo>
-                <a:pt x="4563109" y="0"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="0" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="175260"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="4563109" y="175260"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="4563109" y="0"/>
               </a:lnTo>
               <a:close/>
             </a:path>
@@ -4722,24 +4648,24 @@
   <dimension ref="A1:D391"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.15234375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="133.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="225.69140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.84375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.23046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="105.921875" customWidth="1"/>
+    <col min="3" max="3" width="255.69140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4747,10 +4673,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>1</v>
@@ -4761,10 +4687,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>0</v>
@@ -4775,10 +4701,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>0</v>
@@ -4789,13 +4715,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>238</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4803,10 +4729,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>239</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>240</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>1</v>
@@ -4817,10 +4743,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>241</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>242</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>0</v>
@@ -4831,10 +4757,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>1</v>
@@ -4845,13 +4771,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4859,13 +4785,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>246</v>
-      </c>
       <c r="D10" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4873,10 +4799,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>0</v>
@@ -4887,10 +4813,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>0</v>
@@ -4901,10 +4827,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>0</v>
@@ -4915,13 +4841,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>251</v>
-      </c>
       <c r="D14" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4929,13 +4855,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>253</v>
-      </c>
       <c r="D15" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="93" x14ac:dyDescent="0.35">
@@ -4943,13 +4869,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4957,13 +4883,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4971,10 +4897,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>255</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>256</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>1</v>
@@ -4985,13 +4911,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4999,13 +4925,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5013,10 +4939,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>1</v>
@@ -5027,13 +4953,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>261</v>
-      </c>
       <c r="D22" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5041,13 +4967,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>263</v>
-      </c>
       <c r="D23" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5055,13 +4981,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>265</v>
-      </c>
       <c r="D24" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5069,13 +4995,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>267</v>
-      </c>
       <c r="D25" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -5083,10 +5009,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>1</v>
@@ -5097,10 +5023,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>269</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>270</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>1</v>
@@ -5111,13 +5037,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -5125,24 +5051,24 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="C29" s="25" t="s">
-        <v>273</v>
-      </c>
       <c r="D29" s="19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A30" s="7">
         <v>29</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D30" s="20" t="s">
         <v>1</v>
@@ -5153,10 +5079,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C31" s="14" t="s">
         <v>275</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>276</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>1</v>
@@ -5167,13 +5093,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5181,13 +5107,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="C33" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>279</v>
-      </c>
       <c r="D33" s="17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5195,10 +5121,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>1</v>
@@ -5209,10 +5135,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>0</v>
@@ -5223,10 +5149,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>0</v>
@@ -5237,13 +5163,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5251,10 +5177,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>1</v>
@@ -5265,10 +5191,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D39" s="12" t="s">
         <v>1</v>
@@ -5279,10 +5205,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D40" s="17" t="s">
         <v>0</v>
@@ -5293,10 +5219,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="C41" s="14" t="s">
         <v>287</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>288</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>1</v>
@@ -5307,10 +5233,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="C42" s="14" t="s">
         <v>289</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>290</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>1</v>
@@ -5321,10 +5247,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C43" s="14" t="s">
         <v>291</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>292</v>
       </c>
       <c r="D43" s="17" t="s">
         <v>1</v>
@@ -5335,10 +5261,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>1</v>
@@ -5349,10 +5275,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>0</v>
@@ -5363,10 +5289,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C46" s="14" t="s">
         <v>295</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>296</v>
       </c>
       <c r="D46" s="21" t="s">
         <v>0</v>
@@ -5377,13 +5303,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5391,10 +5317,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>1</v>
@@ -5405,10 +5331,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C49" s="14" t="s">
         <v>299</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>300</v>
       </c>
       <c r="D49" s="17" t="s">
         <v>1</v>
@@ -5419,10 +5345,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>0</v>
@@ -5433,10 +5359,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>0</v>
@@ -5447,13 +5373,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5461,13 +5387,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C53" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="C53" s="14" t="s">
-        <v>305</v>
-      </c>
       <c r="D53" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5475,10 +5401,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>1</v>
@@ -5489,10 +5415,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>1</v>
@@ -5503,10 +5429,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="C56" s="14" t="s">
         <v>308</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>309</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>1</v>
@@ -5517,13 +5443,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="C57" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="C57" s="14" t="s">
-        <v>311</v>
-      </c>
       <c r="D57" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5531,10 +5457,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="11" t="s">
+        <v>311</v>
+      </c>
+      <c r="C58" s="14" t="s">
         <v>312</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>313</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>1</v>
@@ -5545,13 +5471,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5559,13 +5485,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5573,13 +5499,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5587,10 +5513,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D62" s="22" t="s">
         <v>0</v>
@@ -5601,13 +5527,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
+        <v>317</v>
+      </c>
+      <c r="C63" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="C63" s="14" t="s">
-        <v>319</v>
-      </c>
       <c r="D63" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5615,13 +5541,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="C64" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="C64" s="14" t="s">
-        <v>321</v>
-      </c>
       <c r="D64" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5629,13 +5555,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="C65" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="C65" s="14" t="s">
-        <v>323</v>
-      </c>
       <c r="D65" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5643,13 +5569,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5657,13 +5583,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="11" t="s">
+        <v>324</v>
+      </c>
+      <c r="C67" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="C67" s="14" t="s">
-        <v>326</v>
-      </c>
       <c r="D67" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5671,13 +5597,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="C68" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="C68" s="14" t="s">
-        <v>328</v>
-      </c>
       <c r="D68" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5685,13 +5611,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5699,13 +5625,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C70" s="14" t="s">
         <v>330</v>
       </c>
-      <c r="C70" s="14" t="s">
-        <v>331</v>
-      </c>
       <c r="D70" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -5713,10 +5639,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="11" t="s">
+        <v>331</v>
+      </c>
+      <c r="C71" s="14" t="s">
         <v>332</v>
-      </c>
-      <c r="C71" s="14" t="s">
-        <v>333</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>0</v>
@@ -5727,10 +5653,10 @@
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>0</v>
@@ -5741,13 +5667,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="11" t="s">
+        <v>334</v>
+      </c>
+      <c r="C73" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="C73" s="14" t="s">
-        <v>336</v>
-      </c>
       <c r="D73" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5755,10 +5681,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="C74" s="14" t="s">
         <v>337</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>338</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>1</v>
@@ -5769,10 +5695,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="C75" s="14" t="s">
         <v>339</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>340</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>1</v>
@@ -5783,24 +5709,24 @@
         <v>75</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" ht="139.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" ht="155" x14ac:dyDescent="0.35">
       <c r="A77" s="7">
         <v>76</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>343</v>
+        <v>777</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>1</v>
@@ -5811,10 +5737,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>1</v>
@@ -5825,13 +5751,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5839,24 +5765,24 @@
         <v>79</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="D80" s="18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="93" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A81" s="7">
         <v>80</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>349</v>
+        <v>778</v>
       </c>
       <c r="D81" s="19" t="s">
         <v>1</v>
@@ -5867,10 +5793,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D82" s="20" t="s">
         <v>0</v>
@@ -5881,13 +5807,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5895,10 +5821,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D84" s="19" t="s">
         <v>1</v>
@@ -5909,13 +5835,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D85" s="22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5923,10 +5849,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="D86" s="20" t="s">
         <v>1</v>
@@ -5937,13 +5863,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C87" s="14" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5951,10 +5877,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D88" s="20" t="s">
         <v>1</v>
@@ -5965,13 +5891,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5979,13 +5905,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5993,10 +5919,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D91" s="18" t="s">
         <v>0</v>
@@ -6007,13 +5933,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D92" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6021,10 +5947,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D93" s="20" t="s">
         <v>1</v>
@@ -6035,10 +5961,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D94" s="18" t="s">
         <v>0</v>
@@ -6049,10 +5975,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="D95" s="24" t="s">
         <v>1</v>
@@ -6063,13 +5989,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D96" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6077,13 +6003,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="D97" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -6091,13 +6017,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="D98" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6105,16 +6031,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A100" s="10">
         <v>99</v>
       </c>
@@ -6122,7 +6048,7 @@
         <v>4</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>5</v>
+        <v>779</v>
       </c>
       <c r="D100" s="26" t="s">
         <v>1</v>
@@ -6133,13 +6059,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D101" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6147,27 +6073,27 @@
         <v>101</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D102" s="22" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A103" s="10">
         <v>102</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D103" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6175,10 +6101,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="D104" s="24" t="s">
         <v>1</v>
@@ -6189,13 +6115,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D105" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6203,27 +6129,27 @@
         <v>105</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D106" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A107" s="7">
         <v>106</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>387</v>
+        <v>780</v>
       </c>
       <c r="D107" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6231,13 +6157,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6245,13 +6171,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6259,13 +6185,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D110" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6273,13 +6199,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6287,24 +6213,24 @@
         <v>111</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A113" s="4">
         <v>112</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>396</v>
+        <v>781</v>
       </c>
       <c r="D113" s="19" t="s">
         <v>1</v>
@@ -6315,38 +6241,38 @@
         <v>113</v>
       </c>
       <c r="B114" s="30" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C114" s="30" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A115" s="28">
         <v>114</v>
       </c>
       <c r="B115" s="30" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C115" s="30" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D115" s="15" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A116" s="29">
         <v>115</v>
       </c>
       <c r="B116" s="30" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C116" s="30" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D116" s="12" t="s">
         <v>1</v>
@@ -6357,10 +6283,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="30" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C117" s="30" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D117" s="12" t="s">
         <v>1</v>
@@ -6371,13 +6297,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C118" s="30" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6385,10 +6311,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C119" s="30" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>0</v>
@@ -6399,13 +6325,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C120" s="30" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6413,10 +6339,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D121" s="15" t="s">
         <v>1</v>
@@ -6427,10 +6353,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>1</v>
@@ -6441,24 +6367,24 @@
         <v>122</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D123" s="15" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A124" s="7">
         <v>123</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>413</v>
+        <v>782</v>
       </c>
       <c r="D124" s="19" t="s">
         <v>0</v>
@@ -6469,10 +6395,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="D125" s="21" t="s">
         <v>1</v>
@@ -6483,13 +6409,13 @@
         <v>125</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -6497,10 +6423,10 @@
         <v>126</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="D127" s="21" t="s">
         <v>0</v>
@@ -6511,10 +6437,10 @@
         <v>127</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="D128" s="19" t="s">
         <v>0</v>
@@ -6525,10 +6451,10 @@
         <v>128</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="D129" s="19" t="s">
         <v>1</v>
@@ -6539,10 +6465,10 @@
         <v>129</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="D130" s="22" t="s">
         <v>1</v>
@@ -6553,13 +6479,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="D131" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6567,10 +6493,10 @@
         <v>131</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="D132" s="19" t="s">
         <v>1</v>
@@ -6581,10 +6507,10 @@
         <v>132</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D133" s="15" t="s">
         <v>1</v>
@@ -6595,10 +6521,10 @@
         <v>133</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="D134" s="31" t="s">
         <v>0</v>
@@ -6609,13 +6535,13 @@
         <v>134</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="D135" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6623,10 +6549,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="D136" s="21" t="s">
         <v>0</v>
@@ -6637,10 +6563,10 @@
         <v>136</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="D137" s="24" t="s">
         <v>0</v>
@@ -6651,10 +6577,10 @@
         <v>137</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="D138" s="22" t="s">
         <v>1</v>
@@ -6665,27 +6591,27 @@
         <v>138</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="D139" s="22" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A140" s="4">
         <v>139</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>433</v>
+        <v>772</v>
       </c>
       <c r="D140" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -6693,13 +6619,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="D141" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6707,10 +6633,10 @@
         <v>141</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="D142" s="22" t="s">
         <v>1</v>
@@ -6721,13 +6647,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="D143" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6735,41 +6661,41 @@
         <v>143</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A145" s="4">
         <v>144</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>439</v>
+        <v>773</v>
       </c>
       <c r="D145" s="19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A146" s="4">
         <v>145</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>441</v>
+        <v>774</v>
       </c>
       <c r="D146" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6777,10 +6703,10 @@
         <v>146</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="D147" s="24" t="s">
         <v>1</v>
@@ -6791,13 +6717,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="D148" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6805,13 +6731,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="D149" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6819,27 +6745,27 @@
         <v>149</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="D150" s="24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" ht="108.5" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A151" s="7">
         <v>150</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="D151" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6847,10 +6773,10 @@
         <v>151</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="D152" s="22" t="s">
         <v>1</v>
@@ -6861,10 +6787,10 @@
         <v>152</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
       <c r="D153" s="18" t="s">
         <v>0</v>
@@ -6875,10 +6801,10 @@
         <v>153</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="D154" s="18" t="s">
         <v>1</v>
@@ -6889,13 +6815,13 @@
         <v>154</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="D155" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6903,13 +6829,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="D156" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6917,13 +6843,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="D157" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6931,10 +6857,10 @@
         <v>157</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D158" s="18" t="s">
         <v>0</v>
@@ -6945,10 +6871,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="D159" s="18" t="s">
         <v>1</v>
@@ -6959,13 +6885,13 @@
         <v>159</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="D160" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6973,13 +6899,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="D161" s="23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6987,10 +6913,10 @@
         <v>161</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="D162" s="18" t="s">
         <v>0</v>
@@ -7001,24 +6927,24 @@
         <v>162</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="C163" s="14" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="D163" s="18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" ht="93" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A164" s="10">
         <v>163</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>470</v>
+        <v>775</v>
       </c>
       <c r="D164" s="24" t="s">
         <v>1</v>
@@ -7029,13 +6955,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="C165" s="14" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="D165" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7043,13 +6969,13 @@
         <v>165</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="D166" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7057,13 +6983,13 @@
         <v>166</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="D167" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7071,10 +6997,10 @@
         <v>167</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="D168" s="18" t="s">
         <v>0</v>
@@ -7085,10 +7011,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="D169" s="26" t="s">
         <v>1</v>
@@ -7099,13 +7025,13 @@
         <v>169</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="D170" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7113,13 +7039,13 @@
         <v>170</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="D171" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7127,13 +7053,13 @@
         <v>171</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="D172" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7141,10 +7067,10 @@
         <v>172</v>
       </c>
       <c r="B173" s="11" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="D173" s="19" t="s">
         <v>1</v>
@@ -7155,13 +7081,13 @@
         <v>173</v>
       </c>
       <c r="B174" s="11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="D174" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7169,13 +7095,13 @@
         <v>174</v>
       </c>
       <c r="B175" s="11" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="D175" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7183,13 +7109,13 @@
         <v>175</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="D176" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7197,10 +7123,10 @@
         <v>176</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="D177" s="19" t="s">
         <v>0</v>
@@ -7211,13 +7137,13 @@
         <v>177</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="D178" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7225,13 +7151,13 @@
         <v>178</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
       <c r="D179" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7239,13 +7165,13 @@
         <v>179</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="D180" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7253,10 +7179,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
       <c r="D181" s="19" t="s">
         <v>0</v>
@@ -7267,10 +7193,10 @@
         <v>181</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
       <c r="D182" s="19" t="s">
         <v>1</v>
@@ -7281,13 +7207,13 @@
         <v>182</v>
       </c>
       <c r="B183" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C183" s="14" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="D183" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7295,13 +7221,13 @@
         <v>183</v>
       </c>
       <c r="B184" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="D184" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7309,10 +7235,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C185" s="14" t="s">
-        <v>502</v>
+        <v>492</v>
       </c>
       <c r="D185" s="19" t="s">
         <v>0</v>
@@ -7323,13 +7249,13 @@
         <v>185</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>503</v>
+        <v>493</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="D186" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7337,13 +7263,13 @@
         <v>186</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>505</v>
+        <v>495</v>
       </c>
       <c r="C187" s="14" t="s">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="D187" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7351,10 +7277,10 @@
         <v>187</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>507</v>
+        <v>497</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>508</v>
+        <v>498</v>
       </c>
       <c r="D188" s="18" t="s">
         <v>1</v>
@@ -7365,13 +7291,13 @@
         <v>188</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C189" s="14" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="D189" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7379,10 +7305,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D190" s="22" t="s">
         <v>1</v>
@@ -7393,10 +7319,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>512</v>
+        <v>502</v>
       </c>
       <c r="C191" s="14" t="s">
-        <v>513</v>
+        <v>503</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>0</v>
@@ -7407,10 +7333,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="C192" s="14" t="s">
-        <v>515</v>
+        <v>505</v>
       </c>
       <c r="D192" s="18" t="s">
         <v>1</v>
@@ -7421,10 +7347,10 @@
         <v>192</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C193" s="14" t="s">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="D193" s="18" t="s">
         <v>0</v>
@@ -7435,10 +7361,10 @@
         <v>193</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="D194" s="15" t="s">
         <v>1</v>
@@ -7449,10 +7375,10 @@
         <v>194</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>518</v>
+        <v>508</v>
       </c>
       <c r="C195" s="14" t="s">
-        <v>519</v>
+        <v>509</v>
       </c>
       <c r="D195" s="19" t="s">
         <v>1</v>
@@ -7463,13 +7389,13 @@
         <v>195</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>520</v>
+        <v>510</v>
       </c>
       <c r="C196" s="14" t="s">
-        <v>521</v>
+        <v>511</v>
       </c>
       <c r="D196" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -7477,10 +7403,10 @@
         <v>196</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C197" s="14" t="s">
-        <v>522</v>
+        <v>512</v>
       </c>
       <c r="D197" s="19" t="s">
         <v>1</v>
@@ -7491,10 +7417,10 @@
         <v>197</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>523</v>
+        <v>513</v>
       </c>
       <c r="D198" s="18" t="s">
         <v>0</v>
@@ -7505,10 +7431,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>524</v>
+        <v>514</v>
       </c>
       <c r="C199" s="14" t="s">
-        <v>525</v>
+        <v>515</v>
       </c>
       <c r="D199" s="18" t="s">
         <v>0</v>
@@ -7519,10 +7445,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="D200" s="19" t="s">
         <v>1</v>
@@ -7533,10 +7459,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="C201" s="14" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="D201" s="24" t="s">
         <v>1</v>
@@ -7547,27 +7473,27 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="D202" s="23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A203" s="7">
         <v>202</v>
       </c>
       <c r="B203" s="16" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C203" s="14" t="s">
-        <v>531</v>
+        <v>776</v>
       </c>
       <c r="D203" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7575,24 +7501,24 @@
         <v>203</v>
       </c>
       <c r="B204" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="D204" s="24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A205" s="4">
         <v>204</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>533</v>
+        <v>522</v>
       </c>
       <c r="C205" s="14" t="s">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="D205" s="18" t="s">
         <v>0</v>
@@ -7603,10 +7529,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="C206" s="14" t="s">
-        <v>536</v>
+        <v>525</v>
       </c>
       <c r="D206" s="18" t="s">
         <v>1</v>
@@ -7617,13 +7543,13 @@
         <v>206</v>
       </c>
       <c r="B207" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C207" s="14" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="D207" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7631,10 +7557,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="D208" s="18" t="s">
         <v>1</v>
@@ -7645,10 +7571,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="C209" s="14" t="s">
-        <v>541</v>
+        <v>530</v>
       </c>
       <c r="D209" s="18" t="s">
         <v>1</v>
@@ -7659,10 +7585,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>543</v>
+        <v>532</v>
       </c>
       <c r="D210" s="18" t="s">
         <v>0</v>
@@ -7673,13 +7599,13 @@
         <v>210</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="C211" s="14" t="s">
-        <v>545</v>
+        <v>534</v>
       </c>
       <c r="D211" s="32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7687,10 +7613,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>546</v>
+        <v>535</v>
       </c>
       <c r="C212" s="14" t="s">
-        <v>547</v>
+        <v>536</v>
       </c>
       <c r="D212" s="21" t="s">
         <v>0</v>
@@ -7701,13 +7627,13 @@
         <v>212</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>548</v>
+        <v>537</v>
       </c>
       <c r="C213" s="14" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
       <c r="D213" s="32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7715,10 +7641,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="D214" s="21" t="s">
         <v>0</v>
@@ -7729,13 +7655,13 @@
         <v>214</v>
       </c>
       <c r="B215" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C215" s="14" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7743,13 +7669,13 @@
         <v>215</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
       <c r="C216" s="14" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="D216" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7757,10 +7683,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C217" s="14" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="D217" s="18" t="s">
         <v>0</v>
@@ -7771,13 +7697,13 @@
         <v>217</v>
       </c>
       <c r="B218" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>555</v>
+        <v>544</v>
       </c>
       <c r="D218" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7785,13 +7711,13 @@
         <v>218</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>556</v>
+        <v>545</v>
       </c>
       <c r="C219" s="14" t="s">
-        <v>557</v>
+        <v>546</v>
       </c>
       <c r="D219" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7799,13 +7725,13 @@
         <v>219</v>
       </c>
       <c r="B220" s="11" t="s">
-        <v>558</v>
+        <v>547</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>559</v>
+        <v>548</v>
       </c>
       <c r="D220" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7813,13 +7739,13 @@
         <v>220</v>
       </c>
       <c r="B221" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>560</v>
+        <v>549</v>
       </c>
       <c r="D221" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7827,10 +7753,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>561</v>
+        <v>550</v>
       </c>
       <c r="D222" s="18" t="s">
         <v>0</v>
@@ -7841,10 +7767,10 @@
         <v>222</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C223" s="14" t="s">
-        <v>562</v>
+        <v>551</v>
       </c>
       <c r="D223" s="18" t="s">
         <v>0</v>
@@ -7855,10 +7781,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>563</v>
+        <v>552</v>
       </c>
       <c r="D224" s="18" t="s">
         <v>0</v>
@@ -7869,10 +7795,10 @@
         <v>224</v>
       </c>
       <c r="B225" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C225" s="14" t="s">
-        <v>564</v>
+        <v>553</v>
       </c>
       <c r="D225" s="18" t="s">
         <v>0</v>
@@ -7883,10 +7809,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="11" t="s">
-        <v>565</v>
+        <v>554</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="D226" s="18" t="s">
         <v>1</v>
@@ -7897,13 +7823,13 @@
         <v>226</v>
       </c>
       <c r="B227" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C227" s="14" t="s">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="D227" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -7911,10 +7837,10 @@
         <v>227</v>
       </c>
       <c r="B228" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="D228" s="18" t="s">
         <v>0</v>
@@ -7925,13 +7851,13 @@
         <v>228</v>
       </c>
       <c r="B229" s="11" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
       <c r="C229" s="14" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="D229" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7939,13 +7865,13 @@
         <v>229</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="D230" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7953,10 +7879,10 @@
         <v>230</v>
       </c>
       <c r="B231" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C231" s="14" t="s">
-        <v>572</v>
+        <v>561</v>
       </c>
       <c r="D231" s="19" t="s">
         <v>1</v>
@@ -7967,10 +7893,10 @@
         <v>231</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C232" s="14" t="s">
-        <v>573</v>
+        <v>562</v>
       </c>
       <c r="D232" s="19" t="s">
         <v>0</v>
@@ -7981,13 +7907,13 @@
         <v>232</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C233" s="14" t="s">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="D233" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7995,10 +7921,10 @@
         <v>233</v>
       </c>
       <c r="B234" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="D234" s="18" t="s">
         <v>0</v>
@@ -8009,13 +7935,13 @@
         <v>234</v>
       </c>
       <c r="B235" s="11" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="C235" s="14" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
       <c r="D235" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8023,10 +7949,10 @@
         <v>235</v>
       </c>
       <c r="B236" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C236" s="11" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="D236" s="20" t="s">
         <v>0</v>
@@ -8037,10 +7963,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="16" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
       <c r="C237" s="14" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>0</v>
@@ -8051,13 +7977,13 @@
         <v>237</v>
       </c>
       <c r="B238" s="11" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="D238" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8065,24 +7991,24 @@
         <v>238</v>
       </c>
       <c r="B239" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C239" s="14" t="s">
-        <v>583</v>
+        <v>572</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="93" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A240" s="4">
         <v>239</v>
       </c>
       <c r="B240" s="11" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="C240" s="14" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="D240" s="20" t="s">
         <v>0</v>
@@ -8093,10 +8019,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C241" s="14" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
       <c r="D241" s="21" t="s">
         <v>1</v>
@@ -8107,10 +8033,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>587</v>
+        <v>576</v>
       </c>
       <c r="C242" s="14" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="D242" s="33" t="s">
         <v>0</v>
@@ -8121,13 +8047,13 @@
         <v>242</v>
       </c>
       <c r="B243" s="11" t="s">
-        <v>589</v>
+        <v>578</v>
       </c>
       <c r="C243" s="25" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="D243" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -8135,10 +8061,10 @@
         <v>243</v>
       </c>
       <c r="B244" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="D244" s="18" t="s">
         <v>1</v>
@@ -8149,13 +8075,13 @@
         <v>244</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="C245" s="14" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="D245" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8163,13 +8089,13 @@
         <v>245</v>
       </c>
       <c r="B246" s="11" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="D246" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8177,10 +8103,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="C247" s="14" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="D247" s="18" t="s">
         <v>1</v>
@@ -8191,13 +8117,13 @@
         <v>247</v>
       </c>
       <c r="B248" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="D248" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="46.5" x14ac:dyDescent="0.35">
@@ -8205,13 +8131,13 @@
         <v>248</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="C249" s="14" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="D249" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8219,10 +8145,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="D250" s="18" t="s">
         <v>0</v>
@@ -8233,13 +8159,13 @@
         <v>250</v>
       </c>
       <c r="B251" s="11" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="C251" s="14" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="D251" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8247,13 +8173,13 @@
         <v>251</v>
       </c>
       <c r="B252" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C252" s="14" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="D252" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -8261,13 +8187,13 @@
         <v>252</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C253" s="14" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="D253" s="20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8275,10 +8201,10 @@
         <v>253</v>
       </c>
       <c r="B254" s="16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="D254" s="20" t="s">
         <v>1</v>
@@ -8289,13 +8215,13 @@
         <v>254</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>607</v>
+        <v>596</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="D255" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8303,13 +8229,13 @@
         <v>255</v>
       </c>
       <c r="B256" s="11" t="s">
-        <v>609</v>
+        <v>598</v>
       </c>
       <c r="C256" s="14" t="s">
-        <v>610</v>
+        <v>599</v>
       </c>
       <c r="D256" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8317,10 +8243,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C257" s="14" t="s">
-        <v>611</v>
+        <v>600</v>
       </c>
       <c r="D257" s="19" t="s">
         <v>0</v>
@@ -8331,10 +8257,10 @@
         <v>257</v>
       </c>
       <c r="B258" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>612</v>
+        <v>601</v>
       </c>
       <c r="D258" s="18" t="s">
         <v>0</v>
@@ -8345,24 +8271,24 @@
         <v>258</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>613</v>
+        <v>602</v>
       </c>
       <c r="C259" s="14" t="s">
-        <v>614</v>
+        <v>603</v>
       </c>
       <c r="D259" s="19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" ht="139.5" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="124" x14ac:dyDescent="0.35">
       <c r="A260" s="10">
         <v>259</v>
       </c>
       <c r="B260" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>615</v>
+        <v>604</v>
       </c>
       <c r="D260" s="20" t="s">
         <v>1</v>
@@ -8373,10 +8299,10 @@
         <v>260</v>
       </c>
       <c r="B261" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C261" s="14" t="s">
-        <v>616</v>
+        <v>605</v>
       </c>
       <c r="D261" s="18" t="s">
         <v>0</v>
@@ -8387,10 +8313,10 @@
         <v>261</v>
       </c>
       <c r="B262" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C262" s="14" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="D262" s="19" t="s">
         <v>0</v>
@@ -8401,10 +8327,10 @@
         <v>262</v>
       </c>
       <c r="B263" s="34" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C263" s="25" t="s">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="D263" s="21" t="s">
         <v>0</v>
@@ -8415,10 +8341,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="30" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="C264" s="25" t="s">
-        <v>620</v>
+        <v>609</v>
       </c>
       <c r="D264" s="19" t="s">
         <v>1</v>
@@ -8429,10 +8355,10 @@
         <v>264</v>
       </c>
       <c r="B265" s="34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C265" s="25" t="s">
-        <v>621</v>
+        <v>610</v>
       </c>
       <c r="D265" s="18" t="s">
         <v>1</v>
@@ -8443,10 +8369,10 @@
         <v>265</v>
       </c>
       <c r="B266" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C266" s="14" t="s">
-        <v>622</v>
+        <v>611</v>
       </c>
       <c r="D266" s="35" t="s">
         <v>1</v>
@@ -8457,10 +8383,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>623</v>
+        <v>612</v>
       </c>
       <c r="C267" s="14" t="s">
-        <v>624</v>
+        <v>613</v>
       </c>
       <c r="D267" s="18" t="s">
         <v>0</v>
@@ -8471,10 +8397,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="11" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="C268" s="14" t="s">
-        <v>626</v>
+        <v>615</v>
       </c>
       <c r="D268" s="18" t="s">
         <v>1</v>
@@ -8485,10 +8411,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="11" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="C269" s="14" t="s">
-        <v>628</v>
+        <v>617</v>
       </c>
       <c r="D269" s="18" t="s">
         <v>1</v>
@@ -8499,10 +8425,10 @@
         <v>269</v>
       </c>
       <c r="B270" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C270" s="14" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="D270" s="18" t="s">
         <v>1</v>
@@ -8513,10 +8439,10 @@
         <v>270</v>
       </c>
       <c r="B271" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C271" s="14" t="s">
-        <v>630</v>
+        <v>619</v>
       </c>
       <c r="D271" s="18" t="s">
         <v>0</v>
@@ -8527,10 +8453,10 @@
         <v>271</v>
       </c>
       <c r="B272" s="11" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
       <c r="C272" s="14" t="s">
-        <v>632</v>
+        <v>621</v>
       </c>
       <c r="D272" s="18" t="s">
         <v>0</v>
@@ -8541,10 +8467,10 @@
         <v>272</v>
       </c>
       <c r="B273" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C273" s="14" t="s">
-        <v>633</v>
+        <v>622</v>
       </c>
       <c r="D273" s="15" t="s">
         <v>0</v>
@@ -8555,13 +8481,13 @@
         <v>273</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C274" s="14" t="s">
-        <v>634</v>
+        <v>623</v>
       </c>
       <c r="D274" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8569,10 +8495,10 @@
         <v>274</v>
       </c>
       <c r="B275" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C275" s="14" t="s">
-        <v>635</v>
+        <v>624</v>
       </c>
       <c r="D275" s="18" t="s">
         <v>1</v>
@@ -8583,10 +8509,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="11" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
       <c r="C276" s="14" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="D276" s="36" t="s">
         <v>0</v>
@@ -8597,13 +8523,13 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
       <c r="C277" s="14" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="D277" s="36" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8611,27 +8537,27 @@
         <v>277</v>
       </c>
       <c r="B278" s="11" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
       <c r="C278" s="14" t="s">
-        <v>641</v>
+        <v>630</v>
       </c>
       <c r="D278" s="36" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="124" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:4" ht="93" x14ac:dyDescent="0.35">
       <c r="A279" s="10">
         <v>278</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>642</v>
+        <v>771</v>
       </c>
       <c r="C279" s="14" t="s">
-        <v>643</v>
+        <v>631</v>
       </c>
       <c r="D279" s="36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8639,13 +8565,13 @@
         <v>279</v>
       </c>
       <c r="B280" s="11" t="s">
-        <v>644</v>
+        <v>632</v>
       </c>
       <c r="C280" s="14" t="s">
-        <v>645</v>
+        <v>633</v>
       </c>
       <c r="D280" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8653,13 +8579,13 @@
         <v>280</v>
       </c>
       <c r="B281" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C281" s="14" t="s">
-        <v>646</v>
+        <v>634</v>
       </c>
       <c r="D281" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8667,13 +8593,13 @@
         <v>281</v>
       </c>
       <c r="B282" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C282" s="14" t="s">
-        <v>647</v>
+        <v>635</v>
       </c>
       <c r="D282" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8681,13 +8607,13 @@
         <v>282</v>
       </c>
       <c r="B283" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C283" s="14" t="s">
-        <v>648</v>
+        <v>636</v>
       </c>
       <c r="D283" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8695,10 +8621,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>649</v>
+        <v>637</v>
       </c>
       <c r="D284" s="19" t="s">
         <v>0</v>
@@ -8709,13 +8635,13 @@
         <v>284</v>
       </c>
       <c r="B285" s="11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C285" s="14" t="s">
-        <v>650</v>
+        <v>638</v>
       </c>
       <c r="D285" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8723,13 +8649,13 @@
         <v>285</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="D286" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8737,10 +8663,10 @@
         <v>286</v>
       </c>
       <c r="B287" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C287" s="14" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="D287" s="19" t="s">
         <v>0</v>
@@ -8751,13 +8677,13 @@
         <v>287</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C288" s="14" t="s">
-        <v>653</v>
+        <v>641</v>
       </c>
       <c r="D288" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8765,13 +8691,13 @@
         <v>288</v>
       </c>
       <c r="B289" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C289" s="25" t="s">
-        <v>654</v>
+        <v>642</v>
       </c>
       <c r="D289" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8779,13 +8705,13 @@
         <v>289</v>
       </c>
       <c r="B290" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C290" s="14" t="s">
-        <v>655</v>
+        <v>643</v>
       </c>
       <c r="D290" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -8793,13 +8719,13 @@
         <v>290</v>
       </c>
       <c r="B291" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C291" s="14" t="s">
-        <v>656</v>
+        <v>644</v>
       </c>
       <c r="D291" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8807,13 +8733,13 @@
         <v>291</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>657</v>
+        <v>645</v>
       </c>
       <c r="C292" s="14" t="s">
-        <v>658</v>
+        <v>646</v>
       </c>
       <c r="D292" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8821,13 +8747,13 @@
         <v>292</v>
       </c>
       <c r="B293" s="11" t="s">
-        <v>659</v>
+        <v>647</v>
       </c>
       <c r="C293" s="14" t="s">
-        <v>660</v>
+        <v>648</v>
       </c>
       <c r="D293" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="93" x14ac:dyDescent="0.35">
@@ -8835,13 +8761,13 @@
         <v>293</v>
       </c>
       <c r="B294" s="11" t="s">
-        <v>661</v>
+        <v>649</v>
       </c>
       <c r="C294" s="14" t="s">
-        <v>662</v>
+        <v>650</v>
       </c>
       <c r="D294" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8849,13 +8775,13 @@
         <v>294</v>
       </c>
       <c r="B295" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C295" s="14" t="s">
-        <v>663</v>
+        <v>651</v>
       </c>
       <c r="D295" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8863,13 +8789,13 @@
         <v>295</v>
       </c>
       <c r="B296" s="11" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C296" s="14" t="s">
-        <v>664</v>
+        <v>652</v>
       </c>
       <c r="D296" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -8877,10 +8803,10 @@
         <v>296</v>
       </c>
       <c r="B297" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C297" s="14" t="s">
-        <v>665</v>
+        <v>653</v>
       </c>
       <c r="D297" s="19" t="s">
         <v>0</v>
@@ -8891,10 +8817,10 @@
         <v>297</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C298" s="14" t="s">
-        <v>666</v>
+        <v>654</v>
       </c>
       <c r="D298" s="19" t="s">
         <v>1</v>
@@ -8905,10 +8831,10 @@
         <v>298</v>
       </c>
       <c r="B299" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C299" s="14" t="s">
-        <v>667</v>
+        <v>655</v>
       </c>
       <c r="D299" s="19" t="s">
         <v>0</v>
@@ -8919,10 +8845,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="11" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="C300" s="14" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="D300" s="19" t="s">
         <v>1</v>
@@ -8933,13 +8859,13 @@
         <v>300</v>
       </c>
       <c r="B301" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C301" s="14" t="s">
-        <v>670</v>
+        <v>658</v>
       </c>
       <c r="D301" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8947,10 +8873,10 @@
         <v>301</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="C302" s="14" t="s">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="D302" s="19" t="s">
         <v>0</v>
@@ -8961,13 +8887,13 @@
         <v>302</v>
       </c>
       <c r="B303" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C303" s="14" t="s">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="D303" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8975,13 +8901,13 @@
         <v>303</v>
       </c>
       <c r="B304" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C304" s="14" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="D304" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8989,13 +8915,13 @@
         <v>304</v>
       </c>
       <c r="B305" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C305" s="14" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="D305" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9003,13 +8929,13 @@
         <v>305</v>
       </c>
       <c r="B306" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C306" s="14" t="s">
-        <v>676</v>
+        <v>664</v>
       </c>
       <c r="D306" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9017,13 +8943,13 @@
         <v>306</v>
       </c>
       <c r="B307" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C307" s="14" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="D307" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9031,13 +8957,13 @@
         <v>307</v>
       </c>
       <c r="B308" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C308" s="14" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="D308" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9045,13 +8971,13 @@
         <v>308</v>
       </c>
       <c r="B309" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C309" s="14" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="D309" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9059,13 +8985,13 @@
         <v>309</v>
       </c>
       <c r="B310" s="11" t="s">
-        <v>680</v>
+        <v>668</v>
       </c>
       <c r="C310" s="14" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="D310" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9073,13 +8999,13 @@
         <v>310</v>
       </c>
       <c r="B311" s="11" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="C311" s="14" t="s">
-        <v>679</v>
+        <v>667</v>
       </c>
       <c r="D311" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9087,13 +9013,13 @@
         <v>311</v>
       </c>
       <c r="B312" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C312" s="14" t="s">
-        <v>683</v>
+        <v>671</v>
       </c>
       <c r="D312" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9101,13 +9027,13 @@
         <v>312</v>
       </c>
       <c r="B313" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C313" s="14" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="D313" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9115,13 +9041,13 @@
         <v>313</v>
       </c>
       <c r="B314" s="11" t="s">
-        <v>685</v>
+        <v>673</v>
       </c>
       <c r="C314" s="14" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="D314" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9129,10 +9055,10 @@
         <v>314</v>
       </c>
       <c r="B315" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C315" s="14" t="s">
-        <v>687</v>
+        <v>675</v>
       </c>
       <c r="D315" s="19" t="s">
         <v>0</v>
@@ -9143,10 +9069,10 @@
         <v>315</v>
       </c>
       <c r="B316" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C316" s="14" t="s">
-        <v>688</v>
+        <v>676</v>
       </c>
       <c r="D316" s="19" t="s">
         <v>1</v>
@@ -9157,10 +9083,10 @@
         <v>316</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C317" s="14" t="s">
-        <v>689</v>
+        <v>677</v>
       </c>
       <c r="D317" s="18" t="s">
         <v>1</v>
@@ -9171,13 +9097,13 @@
         <v>317</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>690</v>
+        <v>678</v>
       </c>
       <c r="C318" s="14" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="D318" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9185,10 +9111,10 @@
         <v>318</v>
       </c>
       <c r="B319" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C319" s="14" t="s">
-        <v>692</v>
+        <v>680</v>
       </c>
       <c r="D319" s="19" t="s">
         <v>1</v>
@@ -9199,13 +9125,13 @@
         <v>319</v>
       </c>
       <c r="B320" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C320" s="14" t="s">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="D320" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9213,13 +9139,13 @@
         <v>320</v>
       </c>
       <c r="B321" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C321" s="14" t="s">
-        <v>694</v>
+        <v>682</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -9227,10 +9153,10 @@
         <v>321</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C322" s="14" t="s">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="D322" s="23" t="s">
         <v>0</v>
@@ -9241,13 +9167,13 @@
         <v>322</v>
       </c>
       <c r="B323" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C323" s="14" t="s">
-        <v>696</v>
+        <v>684</v>
       </c>
       <c r="D323" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9255,13 +9181,13 @@
         <v>323</v>
       </c>
       <c r="B324" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C324" s="14" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9269,10 +9195,10 @@
         <v>324</v>
       </c>
       <c r="B325" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C325" s="14" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="D325" s="15" t="s">
         <v>1</v>
@@ -9283,13 +9209,13 @@
         <v>325</v>
       </c>
       <c r="B326" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C326" s="14" t="s">
-        <v>699</v>
+        <v>687</v>
       </c>
       <c r="D326" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9297,13 +9223,13 @@
         <v>326</v>
       </c>
       <c r="B327" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C327" s="14" t="s">
-        <v>700</v>
+        <v>688</v>
       </c>
       <c r="D327" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9311,13 +9237,13 @@
         <v>327</v>
       </c>
       <c r="B328" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C328" s="14" t="s">
-        <v>701</v>
+        <v>689</v>
       </c>
       <c r="D328" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9325,13 +9251,13 @@
         <v>328</v>
       </c>
       <c r="B329" s="11" t="s">
-        <v>702</v>
+        <v>690</v>
       </c>
       <c r="C329" s="14" t="s">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="D329" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9339,13 +9265,13 @@
         <v>329</v>
       </c>
       <c r="B330" s="11" t="s">
-        <v>704</v>
+        <v>692</v>
       </c>
       <c r="C330" s="14" t="s">
-        <v>705</v>
+        <v>693</v>
       </c>
       <c r="D330" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9353,10 +9279,10 @@
         <v>330</v>
       </c>
       <c r="B331" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C331" s="14" t="s">
-        <v>706</v>
+        <v>694</v>
       </c>
       <c r="D331" s="19" t="s">
         <v>0</v>
@@ -9367,10 +9293,10 @@
         <v>331</v>
       </c>
       <c r="B332" s="11" t="s">
-        <v>707</v>
+        <v>695</v>
       </c>
       <c r="C332" s="14" t="s">
-        <v>708</v>
+        <v>696</v>
       </c>
       <c r="D332" s="23" t="s">
         <v>0</v>
@@ -9381,13 +9307,13 @@
         <v>332</v>
       </c>
       <c r="B333" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C333" s="14" t="s">
-        <v>709</v>
+        <v>697</v>
       </c>
       <c r="D333" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9395,13 +9321,13 @@
         <v>333</v>
       </c>
       <c r="B334" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C334" s="14" t="s">
-        <v>710</v>
+        <v>698</v>
       </c>
       <c r="D334" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9409,13 +9335,13 @@
         <v>334</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>711</v>
+        <v>699</v>
       </c>
       <c r="C335" s="14" t="s">
-        <v>712</v>
+        <v>700</v>
       </c>
       <c r="D335" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9423,13 +9349,13 @@
         <v>335</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>713</v>
+        <v>701</v>
       </c>
       <c r="C336" s="14" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="D336" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9437,13 +9363,13 @@
         <v>336</v>
       </c>
       <c r="B337" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C337" s="14" t="s">
-        <v>715</v>
+        <v>703</v>
       </c>
       <c r="D337" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9451,10 +9377,10 @@
         <v>337</v>
       </c>
       <c r="B338" s="16" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C338" s="14" t="s">
-        <v>716</v>
+        <v>704</v>
       </c>
       <c r="D338" s="19" t="s">
         <v>1</v>
@@ -9465,13 +9391,13 @@
         <v>338</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C339" s="14" t="s">
-        <v>717</v>
+        <v>705</v>
       </c>
       <c r="D339" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9479,10 +9405,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>718</v>
+        <v>706</v>
       </c>
       <c r="C340" s="14" t="s">
-        <v>719</v>
+        <v>707</v>
       </c>
       <c r="D340" s="19" t="s">
         <v>1</v>
@@ -9493,24 +9419,24 @@
         <v>340</v>
       </c>
       <c r="B341" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C341" s="14" t="s">
-        <v>720</v>
+        <v>708</v>
       </c>
       <c r="D341" s="19" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:4" ht="93" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A342" s="10">
         <v>341</v>
       </c>
       <c r="B342" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C342" s="11" t="s">
-        <v>721</v>
+        <v>709</v>
       </c>
       <c r="D342" s="19" t="s">
         <v>0</v>
@@ -9521,24 +9447,24 @@
         <v>342</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C343" s="11" t="s">
-        <v>722</v>
+        <v>710</v>
       </c>
       <c r="D343" s="19" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A344" s="10">
         <v>343</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C344" s="11" t="s">
-        <v>723</v>
+        <v>783</v>
       </c>
       <c r="D344" s="19" t="s">
         <v>0</v>
@@ -9549,13 +9475,13 @@
         <v>344</v>
       </c>
       <c r="B345" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C345" s="11" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="D345" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9563,13 +9489,13 @@
         <v>345</v>
       </c>
       <c r="B346" s="11" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="C346" s="11" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="D346" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9577,10 +9503,10 @@
         <v>346</v>
       </c>
       <c r="B347" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C347" s="11" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="D347" s="19" t="s">
         <v>0</v>
@@ -9591,24 +9517,24 @@
         <v>347</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C348" s="11" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="D348" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:4" ht="93" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A349" s="10">
         <v>348</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C349" s="11" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="D349" s="19" t="s">
         <v>0</v>
@@ -9619,10 +9545,10 @@
         <v>349</v>
       </c>
       <c r="B350" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C350" s="11" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="D350" s="15" t="s">
         <v>1</v>
@@ -9633,10 +9559,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="C351" s="11" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="D351" s="19" t="s">
         <v>1</v>
@@ -9647,13 +9573,13 @@
         <v>351</v>
       </c>
       <c r="B352" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C352" s="11" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="D352" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9661,10 +9587,10 @@
         <v>352</v>
       </c>
       <c r="B353" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C353" s="11" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="D353" s="19" t="s">
         <v>0</v>
@@ -9675,13 +9601,13 @@
         <v>353</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="C354" s="11" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="D354" s="19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9689,10 +9615,10 @@
         <v>354</v>
       </c>
       <c r="B355" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C355" s="11" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="D355" s="19" t="s">
         <v>0</v>
@@ -9703,10 +9629,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="C356" s="11" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="D356" s="19" t="s">
         <v>1</v>
@@ -9717,13 +9643,13 @@
         <v>356</v>
       </c>
       <c r="B357" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="D357" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9731,13 +9657,13 @@
         <v>357</v>
       </c>
       <c r="B358" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C358" s="11" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="D358" s="34" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9745,13 +9671,13 @@
         <v>358</v>
       </c>
       <c r="B359" s="11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C359" s="30" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="D359" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9759,13 +9685,13 @@
         <v>359</v>
       </c>
       <c r="B360" s="11" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="C360" s="11" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D360" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9773,13 +9699,13 @@
         <v>360</v>
       </c>
       <c r="B361" s="30" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="C361" s="30" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="D361" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9787,13 +9713,13 @@
         <v>361</v>
       </c>
       <c r="B362" s="30" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="C362" s="30" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="D362" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9801,13 +9727,13 @@
         <v>362</v>
       </c>
       <c r="B363" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C363" s="30" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="D363" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9815,10 +9741,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="30" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C364" s="30" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="D364" s="15" t="s">
         <v>0</v>
@@ -9829,10 +9755,10 @@
         <v>364</v>
       </c>
       <c r="B365" s="30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C365" s="30" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="D365" s="15" t="s">
         <v>0</v>
@@ -9843,13 +9769,13 @@
         <v>365</v>
       </c>
       <c r="B366" s="30" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C366" s="30" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="D366" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9857,13 +9783,13 @@
         <v>366</v>
       </c>
       <c r="B367" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C367" s="30" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="D367" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9871,10 +9797,10 @@
         <v>367</v>
       </c>
       <c r="B368" s="11" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="C368" s="30" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="D368" s="15" t="s">
         <v>0</v>
@@ -9885,13 +9811,13 @@
         <v>368</v>
       </c>
       <c r="B369" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C369" s="30" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="D369" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9899,13 +9825,13 @@
         <v>369</v>
       </c>
       <c r="B370" s="30" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="C370" s="30" t="s">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="D370" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -9913,10 +9839,10 @@
         <v>370</v>
       </c>
       <c r="B371" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="D371" s="15" t="s">
         <v>1</v>
@@ -9927,10 +9853,10 @@
         <v>371</v>
       </c>
       <c r="B372" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>760</v>
+        <v>747</v>
       </c>
       <c r="D372" s="15" t="s">
         <v>0</v>
@@ -9941,10 +9867,10 @@
         <v>372</v>
       </c>
       <c r="B373" s="30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C373" s="30" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="D373" s="15" t="s">
         <v>1</v>
@@ -9955,10 +9881,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C374" s="30" t="s">
-        <v>762</v>
+        <v>749</v>
       </c>
       <c r="D374" s="15" t="s">
         <v>0</v>
@@ -9969,10 +9895,10 @@
         <v>374</v>
       </c>
       <c r="B375" s="30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C375" s="30" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="D375" s="15" t="s">
         <v>1</v>
@@ -9983,10 +9909,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="11" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="C376" s="30" t="s">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="D376" s="15" t="s">
         <v>0</v>
@@ -9997,13 +9923,13 @@
         <v>376</v>
       </c>
       <c r="B377" s="30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C377" s="30" t="s">
-        <v>766</v>
+        <v>753</v>
       </c>
       <c r="D377" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -10011,13 +9937,13 @@
         <v>377</v>
       </c>
       <c r="B378" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C378" s="30" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="D378" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -10025,13 +9951,13 @@
         <v>378</v>
       </c>
       <c r="B379" s="30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C379" s="30" t="s">
-        <v>768</v>
+        <v>755</v>
       </c>
       <c r="D379" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -10039,27 +9965,27 @@
         <v>379</v>
       </c>
       <c r="B380" s="30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C380" s="30" t="s">
-        <v>769</v>
+        <v>756</v>
       </c>
       <c r="D380" s="15" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="139.5" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:4" ht="124" x14ac:dyDescent="0.35">
       <c r="A381" s="10">
         <v>380</v>
       </c>
       <c r="B381" s="30" t="s">
-        <v>770</v>
+        <v>757</v>
       </c>
       <c r="C381" s="30" t="s">
-        <v>771</v>
+        <v>758</v>
       </c>
       <c r="D381" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -10067,10 +9993,10 @@
         <v>381</v>
       </c>
       <c r="B382" s="30" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C382" s="30" t="s">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="D382" s="15" t="s">
         <v>1</v>
@@ -10081,10 +10007,10 @@
         <v>382</v>
       </c>
       <c r="B383" s="30" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C383" s="30" t="s">
-        <v>773</v>
+        <v>760</v>
       </c>
       <c r="D383" s="15" t="s">
         <v>0</v>
@@ -10095,10 +10021,10 @@
         <v>383</v>
       </c>
       <c r="B384" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C384" s="30" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="D384" s="15" t="s">
         <v>0</v>
@@ -10109,10 +10035,10 @@
         <v>384</v>
       </c>
       <c r="B385" s="30" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C385" s="30" t="s">
-        <v>775</v>
+        <v>762</v>
       </c>
       <c r="D385" s="15" t="s">
         <v>1</v>
@@ -10123,13 +10049,13 @@
         <v>385</v>
       </c>
       <c r="B386" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C386" s="11" t="s">
-        <v>776</v>
+        <v>763</v>
       </c>
       <c r="D386" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -10137,13 +10063,13 @@
         <v>386</v>
       </c>
       <c r="B387" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C387" s="11" t="s">
-        <v>777</v>
+        <v>764</v>
       </c>
       <c r="D387" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -10151,13 +10077,13 @@
         <v>387</v>
       </c>
       <c r="B388" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C388" s="11" t="s">
-        <v>778</v>
+        <v>765</v>
       </c>
       <c r="D388" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -10165,10 +10091,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="11" t="s">
-        <v>779</v>
+        <v>766</v>
       </c>
       <c r="C389" s="11" t="s">
-        <v>780</v>
+        <v>767</v>
       </c>
       <c r="D389" s="19" t="s">
         <v>1</v>
@@ -10179,10 +10105,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="11" t="s">
-        <v>781</v>
+        <v>768</v>
       </c>
       <c r="C390" s="11" t="s">
-        <v>782</v>
+        <v>769</v>
       </c>
       <c r="D390" s="19" t="s">
         <v>1</v>
@@ -10193,10 +10119,10 @@
         <v>390</v>
       </c>
       <c r="B391" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C391" s="11" t="s">
-        <v>783</v>
+        <v>770</v>
       </c>
       <c r="D391" s="19" t="s">
         <v>1</v>
@@ -10209,12 +10135,11 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6227360e-e60f-4595-9753-ac508485ddd6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10445,17 +10370,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6227360e-e60f-4595-9753-ac508485ddd6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8A0EA2E-6E25-4712-9DB6-6E8798AE1CF1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC35CC7-6F58-4296-A78C-C761A4406030}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="6227360e-e60f-4595-9753-ac508485ddd6"/>
+    <ds:schemaRef ds:uri="bc054b22-9395-4512-bde7-19a23f2dcff6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10480,18 +10415,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC35CC7-6F58-4296-A78C-C761A4406030}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8A0EA2E-6E25-4712-9DB6-6E8798AE1CF1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="6227360e-e60f-4595-9753-ac508485ddd6"/>
-    <ds:schemaRef ds:uri="bc054b22-9395-4512-bde7-19a23f2dcff6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/Ngan-Hang-Cau-Hoi.xlsx
+++ b/data/Ngan-Hang-Cau-Hoi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9f54d0bdb7235122/Documents/My App/trac-nghiem-luat-dau-thau/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B32B0D1-E964-45B5-876C-751CC32868FC}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9945B2BA-DA03-453F-91C4-0EF789E4D547}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0822E189-CD53-41B9-B216-EFA7EF505EBC}"/>
   </bookViews>
@@ -1536,13 +1536,6 @@
 D. Đánh giá năng lực, kinh nghiệm của nhà thầu phụ căn cứ theo phần công việc nhà thầu phụ đảm nhận, nhà thầu tham dự thầu cũng phải đáp ứng về năng lực, kinh nghiệm đối với phần công việc mà nhà thầu phụ đảm nhận</t>
   </si>
   <si>
-    <t>A. Phải tiến hành rút toàn bộ E-HSDT đã nộp trước đó để sửa đổi cho phù hợp và tiến hành nộp lại
-E-HSDT mới
-B. Không phải tiến hành rút toàn bộ E-HSDT đã nộp trước đó, chỉ cần sửa đổi cho phù hợp và tiến hành nộp lại E-HSDT mới
-C. Sửa đổi cho phù hợp E-HSDT đã nộp mà không phải nộp lại E- HSDT mới
-D. Các phương án trên đều sai</t>
-  </si>
-  <si>
     <t>Đối với đấu thầu qua mạng, trường hợp nhà thầu rút E-HSDT sau thời điểm đóng thầu và trong thời gian có hiệu lực của E-HSDT thì
 nhà thầu bị xử lý theo phương án nào sau đây?</t>
   </si>
@@ -3782,13 +3775,6 @@
 D. Phải đảm bảo tổng số lượng hàng hóa mà các nhà thầu trúng thầu chào thầu bằng số lượng hàng hóa nêu trong hồ sơ mời thầu, đồng thời bảo đảm tổng giá đánh giá của gói thầu là thấp nhất</t>
   </si>
   <si>
-    <t>A. Cấm tham gia hoạt động đấu thầu từ 03 năm đến 05 năm đối với thành viên A
-B. Cấm tham gia hoạt động đấu thầu từ 01 năm đến dưới 03 năm đối với thành viên A
-C. Cấm tham gia hoạt động đấu thầu từ 03 năm đến 05 năm đối với tất cả thành viên trong nhà thầu liên danh A-B
-D. Cấm tham gia hoạt động đấu thầu từ 01 năm đến 03 năm đối với tất cả thành viên trong nhà thầu
-liên danh A-B</t>
-  </si>
-  <si>
     <t>A. Từ ngày có thời điểm đóng thầu đến khi có kết quả lựa chọn nhà thầu
 B. Từ ngày phát hành hồ sơ mời sơ tuyển, hồ sơ mời quan tâm, hồ sơ mời thầu, hồ sơ yêu cầu đến trước khi ký kết hợp đồng, thỏa thuận khung đối với mua sắm tập trung
 C. Từ ngày có thời điểm đóng thầu đến khi ký kết hợp đồng, thỏa thuận khung đối với mua sắm tập trung
@@ -3801,13 +3787,6 @@
 D. Nhà thầu đã hoàn thành công trình xây dựng nhà, kết cấu dạng nhà cấp III, có giá trị tối thiểu là 50% x (2X) VND, trong đó phải bao gồm hạng mục hàng rào bảo vệ, nhà bảo vệ</t>
   </si>
   <si>
-    <t>A. Chủ đầu tư phải ghi tỷ lệ % giá trị dành cho nhà thầu phụ trong E-BDL làm cơ sở để nhà thầu lập E-HSDT
-B. Năng lực và kinh nghiệm của nhà thầu phụ sẽ không được xem xét khi đánh giá E-HSDT của nhà thầu
-C. Nhà thầu được ký kết hợp đồng với các nhà thầu phụ trong danh sách các nhà thầu phụ nêu trong
-E-HSDT
-D. Nhà thầu được ký kết hợp đồng với các nhà thầu phụ được chủ đầu tư chấp thuận để tham gia thực hiện cung cấp dịch vụ liên quan</t>
-  </si>
-  <si>
     <t>A. Phải tiến hành rút toàn bộ E-HSDT đã nộp trước đó để sửa đổi cho phù hợp và tiến hành nộp lại E-HSDT mới
 B. Không phải tiến hành rút toàn bộ E-HSDT đã nộp trước đó, chỉ cần sửa đổi cho phù hợp và tiến hành nộp lại E-HSDT mới
 C. Sửa đổi cho phù hợp E-HSDT đã nộp mà không phải nộp lại E- HSDT mới
@@ -3836,6 +3815,24 @@
 B. Hệ thống tự động xếp hạng nhà thầu theo giá dự thầu sau khi trừ đi giá trị giảm giá (nếu có) thấp nhất (không phải phê duyệt danh sách xếp hạng nhà thầu) đối với gói thầu áp dụng quy trình 02
 C. Trường hợp có từ 02 nhà thầu trở lên cùng xếp thứ nhất thì không đánh giá theo quy trình 02 mà phải đánh giá theo quy trình 01
 D. Cả 3 đáp án đều đúng</t>
+  </si>
+  <si>
+    <t>A. Cấm tham gia hoạt động đấu thầu từ 03 năm đến 05 năm đối với thành viên A
+B. Cấm tham gia hoạt động đấu thầu từ 01 năm đến dưới 03 năm đối với thành viên A
+C. Cấm tham gia hoạt động đấu thầu từ 03 năm đến 05 năm đối với tất cả thành viên trong nhà thầu liên danh A-B
+D. Cấm tham gia hoạt động đấu thầu từ 01 năm đến 03 năm đối với tất cả thành viên trong nhà thầu liên danh A-B</t>
+  </si>
+  <si>
+    <t>A. Phải tiến hành rút toàn bộ E-HSDT đã nộp trước đó để sửa đổi cho phù hợp và tiến hành nộp lại E-HSDT mới
+B. Không phải tiến hành rút toàn bộ E-HSDT đã nộp trước đó, chỉ cần sửa đổi cho phù hợp và tiến hành nộp lại E-HSDT mới
+C. Sửa đổi cho phù hợp E-HSDT đã nộp mà không phải nộp lại E- HSDT mới
+D. Các phương án trên đều sai</t>
+  </si>
+  <si>
+    <t>A. Chủ đầu tư phải ghi tỷ lệ % giá trị dành cho nhà thầu phụ trong E-BDL làm cơ sở để nhà thầu lập E-HSDT
+B. Năng lực và kinh nghiệm của nhà thầu phụ sẽ không được xem xét khi đánh giá E-HSDT của nhà thầu
+C. Nhà thầu được ký kết hợp đồng với các nhà thầu phụ trong danh sách các nhà thầu phụ nêu trong E-HSDT
+D. Nhà thầu được ký kết hợp đồng với các nhà thầu phụ được chủ đầu tư chấp thuận để tham gia thực hiện cung cấp dịch vụ liên quan</t>
   </si>
 </sst>
 </file>
@@ -5726,7 +5723,7 @@
         <v>341</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>1</v>
@@ -5746,7 +5743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:4" ht="93" x14ac:dyDescent="0.35">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -5774,7 +5771,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A81" s="7">
         <v>80</v>
       </c>
@@ -5782,7 +5779,7 @@
         <v>58</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>778</v>
+        <v>783</v>
       </c>
       <c r="D81" s="19" t="s">
         <v>1</v>
@@ -6048,13 +6045,13 @@
         <v>4</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D100" s="26" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A101" s="4">
         <v>100</v>
       </c>
@@ -6062,7 +6059,7 @@
         <v>66</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>375</v>
+        <v>782</v>
       </c>
       <c r="D101" s="21" t="s">
         <v>17</v>
@@ -6073,10 +6070,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="C102" s="14" t="s">
         <v>376</v>
-      </c>
-      <c r="C102" s="14" t="s">
-        <v>377</v>
       </c>
       <c r="D102" s="22" t="s">
         <v>0</v>
@@ -6090,7 +6087,7 @@
         <v>67</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D103" s="20" t="s">
         <v>17</v>
@@ -6104,21 +6101,21 @@
         <v>68</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D104" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" ht="93" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:4" ht="108.5" x14ac:dyDescent="0.35">
       <c r="A105" s="10">
         <v>104</v>
       </c>
       <c r="B105" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="C105" s="14" t="s">
         <v>380</v>
-      </c>
-      <c r="C105" s="14" t="s">
-        <v>381</v>
       </c>
       <c r="D105" s="20" t="s">
         <v>17</v>
@@ -6129,10 +6126,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="C106" s="14" t="s">
         <v>382</v>
-      </c>
-      <c r="C106" s="14" t="s">
-        <v>383</v>
       </c>
       <c r="D106" s="18" t="s">
         <v>17</v>
@@ -6146,7 +6143,7 @@
         <v>69</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>20</v>
@@ -6160,7 +6157,7 @@
         <v>70</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D108" s="21" t="s">
         <v>20</v>
@@ -6174,7 +6171,7 @@
         <v>71</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D109" s="21" t="s">
         <v>20</v>
@@ -6188,7 +6185,7 @@
         <v>72</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D110" s="20" t="s">
         <v>17</v>
@@ -6199,10 +6196,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="C111" s="14" t="s">
         <v>387</v>
-      </c>
-      <c r="C111" s="14" t="s">
-        <v>388</v>
       </c>
       <c r="D111" s="19" t="s">
         <v>20</v>
@@ -6213,10 +6210,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="C112" s="14" t="s">
         <v>389</v>
-      </c>
-      <c r="C112" s="14" t="s">
-        <v>390</v>
       </c>
       <c r="D112" s="19" t="s">
         <v>17</v>
@@ -6227,10 +6224,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D113" s="19" t="s">
         <v>1</v>
@@ -6241,38 +6238,38 @@
         <v>113</v>
       </c>
       <c r="B114" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="C114" s="30" t="s">
         <v>392</v>
-      </c>
-      <c r="C114" s="30" t="s">
-        <v>393</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:4" ht="62" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A115" s="28">
         <v>114</v>
       </c>
       <c r="B115" s="30" t="s">
+        <v>393</v>
+      </c>
+      <c r="C115" s="30" t="s">
         <v>394</v>
-      </c>
-      <c r="C115" s="30" t="s">
-        <v>395</v>
       </c>
       <c r="D115" s="15" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" ht="62" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A116" s="29">
         <v>115</v>
       </c>
       <c r="B116" s="30" t="s">
+        <v>395</v>
+      </c>
+      <c r="C116" s="30" t="s">
         <v>396</v>
-      </c>
-      <c r="C116" s="30" t="s">
-        <v>397</v>
       </c>
       <c r="D116" s="12" t="s">
         <v>1</v>
@@ -6283,16 +6280,16 @@
         <v>116</v>
       </c>
       <c r="B117" s="30" t="s">
+        <v>397</v>
+      </c>
+      <c r="C117" s="30" t="s">
         <v>398</v>
-      </c>
-      <c r="C117" s="30" t="s">
-        <v>399</v>
       </c>
       <c r="D117" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" ht="93" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A118" s="28">
         <v>117</v>
       </c>
@@ -6300,7 +6297,7 @@
         <v>73</v>
       </c>
       <c r="C118" s="30" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D118" s="12" t="s">
         <v>20</v>
@@ -6314,7 +6311,7 @@
         <v>74</v>
       </c>
       <c r="C119" s="30" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>0</v>
@@ -6328,7 +6325,7 @@
         <v>75</v>
       </c>
       <c r="C120" s="30" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D120" s="12" t="s">
         <v>20</v>
@@ -6339,10 +6336,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="11" t="s">
+        <v>402</v>
+      </c>
+      <c r="C121" s="14" t="s">
         <v>403</v>
-      </c>
-      <c r="C121" s="14" t="s">
-        <v>404</v>
       </c>
       <c r="D121" s="15" t="s">
         <v>1</v>
@@ -6356,7 +6353,7 @@
         <v>76</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>1</v>
@@ -6370,7 +6367,7 @@
         <v>77</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D123" s="15" t="s">
         <v>1</v>
@@ -6381,10 +6378,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D124" s="19" t="s">
         <v>0</v>
@@ -6398,7 +6395,7 @@
         <v>78</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D125" s="21" t="s">
         <v>1</v>
@@ -6409,10 +6406,10 @@
         <v>125</v>
       </c>
       <c r="B126" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="C126" s="14" t="s">
         <v>409</v>
-      </c>
-      <c r="C126" s="14" t="s">
-        <v>410</v>
       </c>
       <c r="D126" s="21" t="s">
         <v>17</v>
@@ -6426,7 +6423,7 @@
         <v>79</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D127" s="21" t="s">
         <v>0</v>
@@ -6440,7 +6437,7 @@
         <v>80</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D128" s="19" t="s">
         <v>0</v>
@@ -6454,7 +6451,7 @@
         <v>81</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D129" s="19" t="s">
         <v>1</v>
@@ -6468,7 +6465,7 @@
         <v>82</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D130" s="22" t="s">
         <v>1</v>
@@ -6482,7 +6479,7 @@
         <v>83</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D131" s="22" t="s">
         <v>20</v>
@@ -6496,7 +6493,7 @@
         <v>84</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D132" s="19" t="s">
         <v>1</v>
@@ -6507,10 +6504,10 @@
         <v>132</v>
       </c>
       <c r="B133" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="C133" s="14" t="s">
         <v>417</v>
-      </c>
-      <c r="C133" s="14" t="s">
-        <v>418</v>
       </c>
       <c r="D133" s="15" t="s">
         <v>1</v>
@@ -6521,10 +6518,10 @@
         <v>133</v>
       </c>
       <c r="B134" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="C134" s="14" t="s">
         <v>419</v>
-      </c>
-      <c r="C134" s="14" t="s">
-        <v>420</v>
       </c>
       <c r="D134" s="31" t="s">
         <v>0</v>
@@ -6538,7 +6535,7 @@
         <v>85</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D135" s="19" t="s">
         <v>20</v>
@@ -6549,10 +6546,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="11" t="s">
+        <v>421</v>
+      </c>
+      <c r="C136" s="14" t="s">
         <v>422</v>
-      </c>
-      <c r="C136" s="14" t="s">
-        <v>423</v>
       </c>
       <c r="D136" s="21" t="s">
         <v>0</v>
@@ -6566,7 +6563,7 @@
         <v>86</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D137" s="24" t="s">
         <v>0</v>
@@ -6580,7 +6577,7 @@
         <v>87</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D138" s="22" t="s">
         <v>1</v>
@@ -6594,7 +6591,7 @@
         <v>88</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D139" s="22" t="s">
         <v>0</v>
@@ -6608,7 +6605,7 @@
         <v>89</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D140" s="18" t="s">
         <v>17</v>
@@ -6622,7 +6619,7 @@
         <v>90</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D141" s="20" t="s">
         <v>17</v>
@@ -6633,10 +6630,10 @@
         <v>141</v>
       </c>
       <c r="B142" s="11" t="s">
+        <v>427</v>
+      </c>
+      <c r="C142" s="14" t="s">
         <v>428</v>
-      </c>
-      <c r="C142" s="14" t="s">
-        <v>429</v>
       </c>
       <c r="D142" s="22" t="s">
         <v>1</v>
@@ -6650,7 +6647,7 @@
         <v>91</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D143" s="18" t="s">
         <v>20</v>
@@ -6664,7 +6661,7 @@
         <v>92</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>17</v>
@@ -6678,7 +6675,7 @@
         <v>93</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D145" s="19" t="s">
         <v>17</v>
@@ -6689,10 +6686,10 @@
         <v>145</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D146" s="19" t="s">
         <v>20</v>
@@ -6703,10 +6700,10 @@
         <v>146</v>
       </c>
       <c r="B147" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C147" s="14" t="s">
         <v>433</v>
-      </c>
-      <c r="C147" s="14" t="s">
-        <v>434</v>
       </c>
       <c r="D147" s="24" t="s">
         <v>1</v>
@@ -6717,10 +6714,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="11" t="s">
+        <v>434</v>
+      </c>
+      <c r="C148" s="14" t="s">
         <v>435</v>
-      </c>
-      <c r="C148" s="14" t="s">
-        <v>436</v>
       </c>
       <c r="D148" s="19" t="s">
         <v>17</v>
@@ -6734,7 +6731,7 @@
         <v>94</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D149" s="21" t="s">
         <v>20</v>
@@ -6745,10 +6742,10 @@
         <v>149</v>
       </c>
       <c r="B150" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="C150" s="14" t="s">
         <v>438</v>
-      </c>
-      <c r="C150" s="14" t="s">
-        <v>439</v>
       </c>
       <c r="D150" s="24" t="s">
         <v>20</v>
@@ -6762,7 +6759,7 @@
         <v>95</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D151" s="24" t="s">
         <v>17</v>
@@ -6776,7 +6773,7 @@
         <v>96</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D152" s="22" t="s">
         <v>1</v>
@@ -6787,10 +6784,10 @@
         <v>152</v>
       </c>
       <c r="B153" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="C153" s="14" t="s">
         <v>442</v>
-      </c>
-      <c r="C153" s="14" t="s">
-        <v>443</v>
       </c>
       <c r="D153" s="18" t="s">
         <v>0</v>
@@ -6801,10 +6798,10 @@
         <v>153</v>
       </c>
       <c r="B154" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="C154" s="14" t="s">
         <v>444</v>
-      </c>
-      <c r="C154" s="14" t="s">
-        <v>445</v>
       </c>
       <c r="D154" s="18" t="s">
         <v>1</v>
@@ -6818,7 +6815,7 @@
         <v>97</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D155" s="19" t="s">
         <v>17</v>
@@ -6829,10 +6826,10 @@
         <v>155</v>
       </c>
       <c r="B156" s="11" t="s">
+        <v>446</v>
+      </c>
+      <c r="C156" s="14" t="s">
         <v>447</v>
-      </c>
-      <c r="C156" s="14" t="s">
-        <v>448</v>
       </c>
       <c r="D156" s="18" t="s">
         <v>17</v>
@@ -6843,10 +6840,10 @@
         <v>156</v>
       </c>
       <c r="B157" s="11" t="s">
+        <v>448</v>
+      </c>
+      <c r="C157" s="14" t="s">
         <v>449</v>
-      </c>
-      <c r="C157" s="14" t="s">
-        <v>450</v>
       </c>
       <c r="D157" s="15" t="s">
         <v>17</v>
@@ -6860,7 +6857,7 @@
         <v>98</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D158" s="18" t="s">
         <v>0</v>
@@ -6871,10 +6868,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="11" t="s">
+        <v>451</v>
+      </c>
+      <c r="C159" s="14" t="s">
         <v>452</v>
-      </c>
-      <c r="C159" s="14" t="s">
-        <v>453</v>
       </c>
       <c r="D159" s="18" t="s">
         <v>1</v>
@@ -6888,7 +6885,7 @@
         <v>99</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D160" s="18" t="s">
         <v>17</v>
@@ -6899,10 +6896,10 @@
         <v>160</v>
       </c>
       <c r="B161" s="11" t="s">
+        <v>454</v>
+      </c>
+      <c r="C161" s="14" t="s">
         <v>455</v>
-      </c>
-      <c r="C161" s="14" t="s">
-        <v>456</v>
       </c>
       <c r="D161" s="23" t="s">
         <v>20</v>
@@ -6916,7 +6913,7 @@
         <v>100</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D162" s="18" t="s">
         <v>0</v>
@@ -6927,24 +6924,24 @@
         <v>162</v>
       </c>
       <c r="B163" s="11" t="s">
+        <v>457</v>
+      </c>
+      <c r="C163" s="14" t="s">
         <v>458</v>
-      </c>
-      <c r="C163" s="14" t="s">
-        <v>459</v>
       </c>
       <c r="D163" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="164" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A164" s="10">
         <v>163</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>775</v>
+        <v>781</v>
       </c>
       <c r="D164" s="24" t="s">
         <v>1</v>
@@ -6955,10 +6952,10 @@
         <v>164</v>
       </c>
       <c r="B165" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="C165" s="14" t="s">
         <v>461</v>
-      </c>
-      <c r="C165" s="14" t="s">
-        <v>462</v>
       </c>
       <c r="D165" s="21" t="s">
         <v>17</v>
@@ -6969,10 +6966,10 @@
         <v>165</v>
       </c>
       <c r="B166" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="C166" s="14" t="s">
         <v>463</v>
-      </c>
-      <c r="C166" s="14" t="s">
-        <v>464</v>
       </c>
       <c r="D166" s="18" t="s">
         <v>20</v>
@@ -6983,10 +6980,10 @@
         <v>166</v>
       </c>
       <c r="B167" s="11" t="s">
+        <v>464</v>
+      </c>
+      <c r="C167" s="14" t="s">
         <v>465</v>
-      </c>
-      <c r="C167" s="14" t="s">
-        <v>466</v>
       </c>
       <c r="D167" s="20" t="s">
         <v>20</v>
@@ -6997,10 +6994,10 @@
         <v>167</v>
       </c>
       <c r="B168" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="C168" s="14" t="s">
         <v>467</v>
-      </c>
-      <c r="C168" s="14" t="s">
-        <v>468</v>
       </c>
       <c r="D168" s="18" t="s">
         <v>0</v>
@@ -7014,7 +7011,7 @@
         <v>101</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D169" s="26" t="s">
         <v>1</v>
@@ -7025,10 +7022,10 @@
         <v>169</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D170" s="21" t="s">
         <v>17</v>
@@ -7042,7 +7039,7 @@
         <v>102</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D171" s="20" t="s">
         <v>17</v>
@@ -7056,7 +7053,7 @@
         <v>103</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D172" s="19" t="s">
         <v>20</v>
@@ -7067,10 +7064,10 @@
         <v>172</v>
       </c>
       <c r="B173" s="11" t="s">
+        <v>472</v>
+      </c>
+      <c r="C173" s="14" t="s">
         <v>473</v>
-      </c>
-      <c r="C173" s="14" t="s">
-        <v>474</v>
       </c>
       <c r="D173" s="19" t="s">
         <v>1</v>
@@ -7084,7 +7081,7 @@
         <v>104</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D174" s="19" t="s">
         <v>17</v>
@@ -7095,10 +7092,10 @@
         <v>174</v>
       </c>
       <c r="B175" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="C175" s="14" t="s">
         <v>476</v>
-      </c>
-      <c r="C175" s="14" t="s">
-        <v>477</v>
       </c>
       <c r="D175" s="19" t="s">
         <v>17</v>
@@ -7112,7 +7109,7 @@
         <v>105</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D176" s="19" t="s">
         <v>17</v>
@@ -7123,10 +7120,10 @@
         <v>176</v>
       </c>
       <c r="B177" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="C177" s="14" t="s">
         <v>479</v>
-      </c>
-      <c r="C177" s="14" t="s">
-        <v>480</v>
       </c>
       <c r="D177" s="19" t="s">
         <v>0</v>
@@ -7137,10 +7134,10 @@
         <v>177</v>
       </c>
       <c r="B178" s="11" t="s">
+        <v>480</v>
+      </c>
+      <c r="C178" s="14" t="s">
         <v>481</v>
-      </c>
-      <c r="C178" s="14" t="s">
-        <v>482</v>
       </c>
       <c r="D178" s="19" t="s">
         <v>17</v>
@@ -7151,10 +7148,10 @@
         <v>178</v>
       </c>
       <c r="B179" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="C179" s="14" t="s">
         <v>483</v>
-      </c>
-      <c r="C179" s="14" t="s">
-        <v>484</v>
       </c>
       <c r="D179" s="19" t="s">
         <v>20</v>
@@ -7165,10 +7162,10 @@
         <v>179</v>
       </c>
       <c r="B180" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="C180" s="14" t="s">
         <v>485</v>
-      </c>
-      <c r="C180" s="14" t="s">
-        <v>486</v>
       </c>
       <c r="D180" s="19" t="s">
         <v>17</v>
@@ -7179,10 +7176,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D181" s="19" t="s">
         <v>0</v>
@@ -7193,10 +7190,10 @@
         <v>181</v>
       </c>
       <c r="B182" s="11" t="s">
+        <v>487</v>
+      </c>
+      <c r="C182" s="14" t="s">
         <v>488</v>
-      </c>
-      <c r="C182" s="14" t="s">
-        <v>489</v>
       </c>
       <c r="D182" s="19" t="s">
         <v>1</v>
@@ -7210,7 +7207,7 @@
         <v>106</v>
       </c>
       <c r="C183" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D183" s="19" t="s">
         <v>20</v>
@@ -7224,7 +7221,7 @@
         <v>107</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D184" s="19" t="s">
         <v>17</v>
@@ -7238,7 +7235,7 @@
         <v>108</v>
       </c>
       <c r="C185" s="14" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D185" s="19" t="s">
         <v>0</v>
@@ -7249,10 +7246,10 @@
         <v>185</v>
       </c>
       <c r="B186" s="11" t="s">
+        <v>492</v>
+      </c>
+      <c r="C186" s="14" t="s">
         <v>493</v>
-      </c>
-      <c r="C186" s="14" t="s">
-        <v>494</v>
       </c>
       <c r="D186" s="19" t="s">
         <v>17</v>
@@ -7263,10 +7260,10 @@
         <v>186</v>
       </c>
       <c r="B187" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="C187" s="14" t="s">
         <v>495</v>
-      </c>
-      <c r="C187" s="14" t="s">
-        <v>496</v>
       </c>
       <c r="D187" s="19" t="s">
         <v>20</v>
@@ -7277,10 +7274,10 @@
         <v>187</v>
       </c>
       <c r="B188" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="C188" s="14" t="s">
         <v>497</v>
-      </c>
-      <c r="C188" s="14" t="s">
-        <v>498</v>
       </c>
       <c r="D188" s="18" t="s">
         <v>1</v>
@@ -7294,7 +7291,7 @@
         <v>109</v>
       </c>
       <c r="C189" s="14" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D189" s="18" t="s">
         <v>20</v>
@@ -7305,10 +7302,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="C190" s="14" t="s">
         <v>500</v>
-      </c>
-      <c r="C190" s="14" t="s">
-        <v>501</v>
       </c>
       <c r="D190" s="22" t="s">
         <v>1</v>
@@ -7319,10 +7316,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="11" t="s">
+        <v>501</v>
+      </c>
+      <c r="C191" s="14" t="s">
         <v>502</v>
-      </c>
-      <c r="C191" s="14" t="s">
-        <v>503</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>0</v>
@@ -7333,10 +7330,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="C192" s="14" t="s">
         <v>504</v>
-      </c>
-      <c r="C192" s="14" t="s">
-        <v>505</v>
       </c>
       <c r="D192" s="18" t="s">
         <v>1</v>
@@ -7350,7 +7347,7 @@
         <v>110</v>
       </c>
       <c r="C193" s="14" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D193" s="18" t="s">
         <v>0</v>
@@ -7364,7 +7361,7 @@
         <v>111</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D194" s="15" t="s">
         <v>1</v>
@@ -7375,10 +7372,10 @@
         <v>194</v>
       </c>
       <c r="B195" s="5" t="s">
+        <v>507</v>
+      </c>
+      <c r="C195" s="14" t="s">
         <v>508</v>
-      </c>
-      <c r="C195" s="14" t="s">
-        <v>509</v>
       </c>
       <c r="D195" s="19" t="s">
         <v>1</v>
@@ -7389,10 +7386,10 @@
         <v>195</v>
       </c>
       <c r="B196" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="C196" s="14" t="s">
         <v>510</v>
-      </c>
-      <c r="C196" s="14" t="s">
-        <v>511</v>
       </c>
       <c r="D196" s="20" t="s">
         <v>17</v>
@@ -7406,7 +7403,7 @@
         <v>112</v>
       </c>
       <c r="C197" s="14" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D197" s="19" t="s">
         <v>1</v>
@@ -7420,21 +7417,21 @@
         <v>113</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D198" s="18" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:4" ht="62" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A199" s="10">
         <v>198</v>
       </c>
       <c r="B199" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="C199" s="14" t="s">
         <v>514</v>
-      </c>
-      <c r="C199" s="14" t="s">
-        <v>515</v>
       </c>
       <c r="D199" s="18" t="s">
         <v>0</v>
@@ -7445,10 +7442,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C200" s="14" t="s">
         <v>516</v>
-      </c>
-      <c r="C200" s="14" t="s">
-        <v>517</v>
       </c>
       <c r="D200" s="19" t="s">
         <v>1</v>
@@ -7459,10 +7456,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="C201" s="14" t="s">
         <v>518</v>
-      </c>
-      <c r="C201" s="14" t="s">
-        <v>519</v>
       </c>
       <c r="D201" s="24" t="s">
         <v>1</v>
@@ -7476,7 +7473,7 @@
         <v>114</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D202" s="23" t="s">
         <v>20</v>
@@ -7490,7 +7487,7 @@
         <v>115</v>
       </c>
       <c r="C203" s="14" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D203" s="24" t="s">
         <v>17</v>
@@ -7504,21 +7501,21 @@
         <v>116</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D204" s="24" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="205" spans="1:4" ht="62" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A205" s="4">
         <v>204</v>
       </c>
       <c r="B205" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="C205" s="14" t="s">
         <v>522</v>
-      </c>
-      <c r="C205" s="14" t="s">
-        <v>523</v>
       </c>
       <c r="D205" s="18" t="s">
         <v>0</v>
@@ -7529,10 +7526,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="11" t="s">
+        <v>523</v>
+      </c>
+      <c r="C206" s="14" t="s">
         <v>524</v>
-      </c>
-      <c r="C206" s="14" t="s">
-        <v>525</v>
       </c>
       <c r="D206" s="18" t="s">
         <v>1</v>
@@ -7546,7 +7543,7 @@
         <v>117</v>
       </c>
       <c r="C207" s="14" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D207" s="19" t="s">
         <v>20</v>
@@ -7557,10 +7554,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="11" t="s">
+        <v>526</v>
+      </c>
+      <c r="C208" s="14" t="s">
         <v>527</v>
-      </c>
-      <c r="C208" s="14" t="s">
-        <v>528</v>
       </c>
       <c r="D208" s="18" t="s">
         <v>1</v>
@@ -7571,10 +7568,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="11" t="s">
+        <v>528</v>
+      </c>
+      <c r="C209" s="14" t="s">
         <v>529</v>
-      </c>
-      <c r="C209" s="14" t="s">
-        <v>530</v>
       </c>
       <c r="D209" s="18" t="s">
         <v>1</v>
@@ -7585,10 +7582,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="11" t="s">
+        <v>530</v>
+      </c>
+      <c r="C210" s="14" t="s">
         <v>531</v>
-      </c>
-      <c r="C210" s="14" t="s">
-        <v>532</v>
       </c>
       <c r="D210" s="18" t="s">
         <v>0</v>
@@ -7599,10 +7596,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="11" t="s">
+        <v>532</v>
+      </c>
+      <c r="C211" s="14" t="s">
         <v>533</v>
-      </c>
-      <c r="C211" s="14" t="s">
-        <v>534</v>
       </c>
       <c r="D211" s="32" t="s">
         <v>17</v>
@@ -7613,10 +7610,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="11" t="s">
+        <v>534</v>
+      </c>
+      <c r="C212" s="14" t="s">
         <v>535</v>
-      </c>
-      <c r="C212" s="14" t="s">
-        <v>536</v>
       </c>
       <c r="D212" s="21" t="s">
         <v>0</v>
@@ -7627,10 +7624,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="11" t="s">
+        <v>536</v>
+      </c>
+      <c r="C213" s="14" t="s">
         <v>537</v>
-      </c>
-      <c r="C213" s="14" t="s">
-        <v>538</v>
       </c>
       <c r="D213" s="32" t="s">
         <v>20</v>
@@ -7644,7 +7641,7 @@
         <v>118</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D214" s="21" t="s">
         <v>0</v>
@@ -7658,7 +7655,7 @@
         <v>119</v>
       </c>
       <c r="C215" s="14" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D215" s="15" t="s">
         <v>20</v>
@@ -7669,10 +7666,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="11" t="s">
+        <v>540</v>
+      </c>
+      <c r="C216" s="14" t="s">
         <v>541</v>
-      </c>
-      <c r="C216" s="14" t="s">
-        <v>542</v>
       </c>
       <c r="D216" s="19" t="s">
         <v>20</v>
@@ -7686,7 +7683,7 @@
         <v>120</v>
       </c>
       <c r="C217" s="14" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D217" s="18" t="s">
         <v>0</v>
@@ -7700,7 +7697,7 @@
         <v>121</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D218" s="20" t="s">
         <v>20</v>
@@ -7711,10 +7708,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="11" t="s">
+        <v>544</v>
+      </c>
+      <c r="C219" s="14" t="s">
         <v>545</v>
-      </c>
-      <c r="C219" s="14" t="s">
-        <v>546</v>
       </c>
       <c r="D219" s="20" t="s">
         <v>17</v>
@@ -7725,10 +7722,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="11" t="s">
+        <v>546</v>
+      </c>
+      <c r="C220" s="14" t="s">
         <v>547</v>
-      </c>
-      <c r="C220" s="14" t="s">
-        <v>548</v>
       </c>
       <c r="D220" s="19" t="s">
         <v>20</v>
@@ -7742,7 +7739,7 @@
         <v>122</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="D221" s="18" t="s">
         <v>17</v>
@@ -7756,7 +7753,7 @@
         <v>123</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D222" s="18" t="s">
         <v>0</v>
@@ -7770,7 +7767,7 @@
         <v>124</v>
       </c>
       <c r="C223" s="14" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D223" s="18" t="s">
         <v>0</v>
@@ -7784,7 +7781,7 @@
         <v>125</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="D224" s="18" t="s">
         <v>0</v>
@@ -7798,7 +7795,7 @@
         <v>126</v>
       </c>
       <c r="C225" s="14" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="D225" s="18" t="s">
         <v>0</v>
@@ -7809,10 +7806,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="11" t="s">
+        <v>553</v>
+      </c>
+      <c r="C226" s="14" t="s">
         <v>554</v>
-      </c>
-      <c r="C226" s="14" t="s">
-        <v>555</v>
       </c>
       <c r="D226" s="18" t="s">
         <v>1</v>
@@ -7826,7 +7823,7 @@
         <v>127</v>
       </c>
       <c r="C227" s="14" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="D227" s="20" t="s">
         <v>17</v>
@@ -7840,7 +7837,7 @@
         <v>128</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D228" s="18" t="s">
         <v>0</v>
@@ -7851,10 +7848,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="11" t="s">
+        <v>557</v>
+      </c>
+      <c r="C229" s="14" t="s">
         <v>558</v>
-      </c>
-      <c r="C229" s="14" t="s">
-        <v>559</v>
       </c>
       <c r="D229" s="20" t="s">
         <v>20</v>
@@ -7868,7 +7865,7 @@
         <v>129</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="D230" s="20" t="s">
         <v>20</v>
@@ -7882,7 +7879,7 @@
         <v>130</v>
       </c>
       <c r="C231" s="14" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="D231" s="19" t="s">
         <v>1</v>
@@ -7896,7 +7893,7 @@
         <v>131</v>
       </c>
       <c r="C232" s="14" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="D232" s="19" t="s">
         <v>0</v>
@@ -7910,7 +7907,7 @@
         <v>132</v>
       </c>
       <c r="C233" s="14" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="D233" s="20" t="s">
         <v>20</v>
@@ -7924,7 +7921,7 @@
         <v>133</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D234" s="18" t="s">
         <v>0</v>
@@ -7935,10 +7932,10 @@
         <v>234</v>
       </c>
       <c r="B235" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="C235" s="14" t="s">
         <v>565</v>
-      </c>
-      <c r="C235" s="14" t="s">
-        <v>566</v>
       </c>
       <c r="D235" s="20" t="s">
         <v>17</v>
@@ -7952,7 +7949,7 @@
         <v>134</v>
       </c>
       <c r="C236" s="11" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D236" s="20" t="s">
         <v>0</v>
@@ -7963,10 +7960,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="C237" s="14" t="s">
         <v>568</v>
-      </c>
-      <c r="C237" s="14" t="s">
-        <v>569</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>0</v>
@@ -7977,10 +7974,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="11" t="s">
+        <v>569</v>
+      </c>
+      <c r="C238" s="14" t="s">
         <v>570</v>
-      </c>
-      <c r="C238" s="14" t="s">
-        <v>571</v>
       </c>
       <c r="D238" s="18" t="s">
         <v>20</v>
@@ -7994,7 +7991,7 @@
         <v>135</v>
       </c>
       <c r="C239" s="14" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>0</v>
@@ -8005,10 +8002,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="11" t="s">
+        <v>572</v>
+      </c>
+      <c r="C240" s="14" t="s">
         <v>573</v>
-      </c>
-      <c r="C240" s="14" t="s">
-        <v>574</v>
       </c>
       <c r="D240" s="20" t="s">
         <v>0</v>
@@ -8022,7 +8019,7 @@
         <v>136</v>
       </c>
       <c r="C241" s="14" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="D241" s="21" t="s">
         <v>1</v>
@@ -8033,10 +8030,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="C242" s="14" t="s">
         <v>576</v>
-      </c>
-      <c r="C242" s="14" t="s">
-        <v>577</v>
       </c>
       <c r="D242" s="33" t="s">
         <v>0</v>
@@ -8047,10 +8044,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="11" t="s">
+        <v>577</v>
+      </c>
+      <c r="C243" s="25" t="s">
         <v>578</v>
-      </c>
-      <c r="C243" s="25" t="s">
-        <v>579</v>
       </c>
       <c r="D243" s="20" t="s">
         <v>20</v>
@@ -8064,7 +8061,7 @@
         <v>137</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D244" s="18" t="s">
         <v>1</v>
@@ -8075,10 +8072,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="C245" s="14" t="s">
         <v>581</v>
-      </c>
-      <c r="C245" s="14" t="s">
-        <v>582</v>
       </c>
       <c r="D245" s="18" t="s">
         <v>17</v>
@@ -8089,10 +8086,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="11" t="s">
+        <v>582</v>
+      </c>
+      <c r="C246" s="14" t="s">
         <v>583</v>
-      </c>
-      <c r="C246" s="14" t="s">
-        <v>584</v>
       </c>
       <c r="D246" s="18" t="s">
         <v>17</v>
@@ -8103,10 +8100,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="C247" s="14" t="s">
         <v>585</v>
-      </c>
-      <c r="C247" s="14" t="s">
-        <v>586</v>
       </c>
       <c r="D247" s="18" t="s">
         <v>1</v>
@@ -8120,7 +8117,7 @@
         <v>138</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D248" s="18" t="s">
         <v>20</v>
@@ -8131,10 +8128,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="11" t="s">
+        <v>587</v>
+      </c>
+      <c r="C249" s="14" t="s">
         <v>588</v>
-      </c>
-      <c r="C249" s="14" t="s">
-        <v>589</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>20</v>
@@ -8148,7 +8145,7 @@
         <v>139</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="D250" s="18" t="s">
         <v>0</v>
@@ -8159,10 +8156,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="11" t="s">
+        <v>590</v>
+      </c>
+      <c r="C251" s="14" t="s">
         <v>591</v>
-      </c>
-      <c r="C251" s="14" t="s">
-        <v>592</v>
       </c>
       <c r="D251" s="19" t="s">
         <v>20</v>
@@ -8176,7 +8173,7 @@
         <v>140</v>
       </c>
       <c r="C252" s="14" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D252" s="20" t="s">
         <v>20</v>
@@ -8190,7 +8187,7 @@
         <v>141</v>
       </c>
       <c r="C253" s="14" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D253" s="20" t="s">
         <v>20</v>
@@ -8204,7 +8201,7 @@
         <v>142</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D254" s="20" t="s">
         <v>1</v>
@@ -8215,10 +8212,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="11" t="s">
+        <v>595</v>
+      </c>
+      <c r="C255" s="14" t="s">
         <v>596</v>
-      </c>
-      <c r="C255" s="14" t="s">
-        <v>597</v>
       </c>
       <c r="D255" s="18" t="s">
         <v>20</v>
@@ -8229,10 +8226,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="11" t="s">
+        <v>597</v>
+      </c>
+      <c r="C256" s="14" t="s">
         <v>598</v>
-      </c>
-      <c r="C256" s="14" t="s">
-        <v>599</v>
       </c>
       <c r="D256" s="18" t="s">
         <v>17</v>
@@ -8246,7 +8243,7 @@
         <v>143</v>
       </c>
       <c r="C257" s="14" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D257" s="19" t="s">
         <v>0</v>
@@ -8260,7 +8257,7 @@
         <v>144</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D258" s="18" t="s">
         <v>0</v>
@@ -8271,10 +8268,10 @@
         <v>258</v>
       </c>
       <c r="B259" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="C259" s="14" t="s">
         <v>602</v>
-      </c>
-      <c r="C259" s="14" t="s">
-        <v>603</v>
       </c>
       <c r="D259" s="19" t="s">
         <v>20</v>
@@ -8288,7 +8285,7 @@
         <v>145</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D260" s="20" t="s">
         <v>1</v>
@@ -8302,7 +8299,7 @@
         <v>146</v>
       </c>
       <c r="C261" s="14" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D261" s="18" t="s">
         <v>0</v>
@@ -8316,7 +8313,7 @@
         <v>147</v>
       </c>
       <c r="C262" s="14" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D262" s="19" t="s">
         <v>0</v>
@@ -8330,7 +8327,7 @@
         <v>148</v>
       </c>
       <c r="C263" s="25" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D263" s="21" t="s">
         <v>0</v>
@@ -8341,10 +8338,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="30" t="s">
+        <v>607</v>
+      </c>
+      <c r="C264" s="25" t="s">
         <v>608</v>
-      </c>
-      <c r="C264" s="25" t="s">
-        <v>609</v>
       </c>
       <c r="D264" s="19" t="s">
         <v>1</v>
@@ -8358,7 +8355,7 @@
         <v>149</v>
       </c>
       <c r="C265" s="25" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="D265" s="18" t="s">
         <v>1</v>
@@ -8372,7 +8369,7 @@
         <v>150</v>
       </c>
       <c r="C266" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D266" s="35" t="s">
         <v>1</v>
@@ -8383,10 +8380,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="11" t="s">
+        <v>611</v>
+      </c>
+      <c r="C267" s="14" t="s">
         <v>612</v>
-      </c>
-      <c r="C267" s="14" t="s">
-        <v>613</v>
       </c>
       <c r="D267" s="18" t="s">
         <v>0</v>
@@ -8397,10 +8394,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="11" t="s">
+        <v>613</v>
+      </c>
+      <c r="C268" s="14" t="s">
         <v>614</v>
-      </c>
-      <c r="C268" s="14" t="s">
-        <v>615</v>
       </c>
       <c r="D268" s="18" t="s">
         <v>1</v>
@@ -8411,10 +8408,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="11" t="s">
+        <v>615</v>
+      </c>
+      <c r="C269" s="14" t="s">
         <v>616</v>
-      </c>
-      <c r="C269" s="14" t="s">
-        <v>617</v>
       </c>
       <c r="D269" s="18" t="s">
         <v>1</v>
@@ -8428,7 +8425,7 @@
         <v>151</v>
       </c>
       <c r="C270" s="14" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D270" s="18" t="s">
         <v>1</v>
@@ -8442,7 +8439,7 @@
         <v>152</v>
       </c>
       <c r="C271" s="14" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D271" s="18" t="s">
         <v>0</v>
@@ -8453,10 +8450,10 @@
         <v>271</v>
       </c>
       <c r="B272" s="11" t="s">
+        <v>619</v>
+      </c>
+      <c r="C272" s="14" t="s">
         <v>620</v>
-      </c>
-      <c r="C272" s="14" t="s">
-        <v>621</v>
       </c>
       <c r="D272" s="18" t="s">
         <v>0</v>
@@ -8470,7 +8467,7 @@
         <v>153</v>
       </c>
       <c r="C273" s="14" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D273" s="15" t="s">
         <v>0</v>
@@ -8484,7 +8481,7 @@
         <v>154</v>
       </c>
       <c r="C274" s="14" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D274" s="19" t="s">
         <v>20</v>
@@ -8498,7 +8495,7 @@
         <v>155</v>
       </c>
       <c r="C275" s="14" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D275" s="18" t="s">
         <v>1</v>
@@ -8509,10 +8506,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="C276" s="14" t="s">
         <v>625</v>
-      </c>
-      <c r="C276" s="14" t="s">
-        <v>626</v>
       </c>
       <c r="D276" s="36" t="s">
         <v>0</v>
@@ -8523,10 +8520,10 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="C277" s="14" t="s">
         <v>627</v>
-      </c>
-      <c r="C277" s="14" t="s">
-        <v>628</v>
       </c>
       <c r="D277" s="36" t="s">
         <v>20</v>
@@ -8537,24 +8534,24 @@
         <v>277</v>
       </c>
       <c r="B278" s="11" t="s">
+        <v>628</v>
+      </c>
+      <c r="C278" s="14" t="s">
         <v>629</v>
-      </c>
-      <c r="C278" s="14" t="s">
-        <v>630</v>
       </c>
       <c r="D278" s="36" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:4" ht="93" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:4" ht="108.5" x14ac:dyDescent="0.35">
       <c r="A279" s="10">
         <v>278</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C279" s="14" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D279" s="36" t="s">
         <v>17</v>
@@ -8565,10 +8562,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="C280" s="14" t="s">
         <v>632</v>
-      </c>
-      <c r="C280" s="14" t="s">
-        <v>633</v>
       </c>
       <c r="D280" s="19" t="s">
         <v>20</v>
@@ -8582,7 +8579,7 @@
         <v>156</v>
       </c>
       <c r="C281" s="14" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D281" s="19" t="s">
         <v>20</v>
@@ -8596,7 +8593,7 @@
         <v>157</v>
       </c>
       <c r="C282" s="14" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D282" s="19" t="s">
         <v>17</v>
@@ -8610,7 +8607,7 @@
         <v>158</v>
       </c>
       <c r="C283" s="14" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D283" s="19" t="s">
         <v>20</v>
@@ -8624,7 +8621,7 @@
         <v>159</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D284" s="19" t="s">
         <v>0</v>
@@ -8638,7 +8635,7 @@
         <v>160</v>
       </c>
       <c r="C285" s="14" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D285" s="19" t="s">
         <v>17</v>
@@ -8652,7 +8649,7 @@
         <v>161</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D286" s="19" t="s">
         <v>17</v>
@@ -8666,7 +8663,7 @@
         <v>162</v>
       </c>
       <c r="C287" s="14" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D287" s="19" t="s">
         <v>0</v>
@@ -8680,7 +8677,7 @@
         <v>163</v>
       </c>
       <c r="C288" s="14" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D288" s="19" t="s">
         <v>17</v>
@@ -8694,7 +8691,7 @@
         <v>164</v>
       </c>
       <c r="C289" s="25" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D289" s="19" t="s">
         <v>17</v>
@@ -8708,7 +8705,7 @@
         <v>165</v>
       </c>
       <c r="C290" s="14" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D290" s="19" t="s">
         <v>17</v>
@@ -8722,7 +8719,7 @@
         <v>166</v>
       </c>
       <c r="C291" s="14" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D291" s="19" t="s">
         <v>17</v>
@@ -8733,10 +8730,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="11" t="s">
+        <v>644</v>
+      </c>
+      <c r="C292" s="14" t="s">
         <v>645</v>
-      </c>
-      <c r="C292" s="14" t="s">
-        <v>646</v>
       </c>
       <c r="D292" s="8" t="s">
         <v>17</v>
@@ -8747,10 +8744,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="C293" s="14" t="s">
         <v>647</v>
-      </c>
-      <c r="C293" s="14" t="s">
-        <v>648</v>
       </c>
       <c r="D293" s="19" t="s">
         <v>17</v>
@@ -8761,10 +8758,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="C294" s="14" t="s">
         <v>649</v>
-      </c>
-      <c r="C294" s="14" t="s">
-        <v>650</v>
       </c>
       <c r="D294" s="19" t="s">
         <v>20</v>
@@ -8778,7 +8775,7 @@
         <v>167</v>
       </c>
       <c r="C295" s="14" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D295" s="19" t="s">
         <v>20</v>
@@ -8792,7 +8789,7 @@
         <v>168</v>
       </c>
       <c r="C296" s="14" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D296" s="19" t="s">
         <v>20</v>
@@ -8806,7 +8803,7 @@
         <v>145</v>
       </c>
       <c r="C297" s="14" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D297" s="19" t="s">
         <v>0</v>
@@ -8820,7 +8817,7 @@
         <v>169</v>
       </c>
       <c r="C298" s="14" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D298" s="19" t="s">
         <v>1</v>
@@ -8834,7 +8831,7 @@
         <v>170</v>
       </c>
       <c r="C299" s="14" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D299" s="19" t="s">
         <v>0</v>
@@ -8845,10 +8842,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="C300" s="14" t="s">
         <v>656</v>
-      </c>
-      <c r="C300" s="14" t="s">
-        <v>657</v>
       </c>
       <c r="D300" s="19" t="s">
         <v>1</v>
@@ -8862,7 +8859,7 @@
         <v>171</v>
       </c>
       <c r="C301" s="14" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D301" s="15" t="s">
         <v>20</v>
@@ -8873,10 +8870,10 @@
         <v>301</v>
       </c>
       <c r="B302" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="C302" s="14" t="s">
         <v>659</v>
-      </c>
-      <c r="C302" s="14" t="s">
-        <v>660</v>
       </c>
       <c r="D302" s="19" t="s">
         <v>0</v>
@@ -8890,7 +8887,7 @@
         <v>172</v>
       </c>
       <c r="C303" s="14" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D303" s="15" t="s">
         <v>17</v>
@@ -8904,7 +8901,7 @@
         <v>173</v>
       </c>
       <c r="C304" s="14" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D304" s="19" t="s">
         <v>17</v>
@@ -8918,7 +8915,7 @@
         <v>174</v>
       </c>
       <c r="C305" s="14" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D305" s="19" t="s">
         <v>17</v>
@@ -8932,7 +8929,7 @@
         <v>175</v>
       </c>
       <c r="C306" s="14" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D306" s="19" t="s">
         <v>17</v>
@@ -8946,7 +8943,7 @@
         <v>176</v>
       </c>
       <c r="C307" s="14" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D307" s="15" t="s">
         <v>17</v>
@@ -8960,7 +8957,7 @@
         <v>177</v>
       </c>
       <c r="C308" s="14" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D308" s="19" t="s">
         <v>17</v>
@@ -8974,7 +8971,7 @@
         <v>178</v>
       </c>
       <c r="C309" s="14" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D309" s="19" t="s">
         <v>17</v>
@@ -8985,10 +8982,10 @@
         <v>309</v>
       </c>
       <c r="B310" s="11" t="s">
+        <v>667</v>
+      </c>
+      <c r="C310" s="14" t="s">
         <v>668</v>
-      </c>
-      <c r="C310" s="14" t="s">
-        <v>669</v>
       </c>
       <c r="D310" s="19" t="s">
         <v>17</v>
@@ -8999,10 +8996,10 @@
         <v>310</v>
       </c>
       <c r="B311" s="11" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C311" s="14" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D311" s="19" t="s">
         <v>17</v>
@@ -9016,7 +9013,7 @@
         <v>179</v>
       </c>
       <c r="C312" s="14" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D312" s="19" t="s">
         <v>17</v>
@@ -9030,7 +9027,7 @@
         <v>180</v>
       </c>
       <c r="C313" s="14" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D313" s="19" t="s">
         <v>17</v>
@@ -9041,10 +9038,10 @@
         <v>313</v>
       </c>
       <c r="B314" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="C314" s="14" t="s">
         <v>673</v>
-      </c>
-      <c r="C314" s="14" t="s">
-        <v>674</v>
       </c>
       <c r="D314" s="19" t="s">
         <v>17</v>
@@ -9058,7 +9055,7 @@
         <v>181</v>
       </c>
       <c r="C315" s="14" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D315" s="19" t="s">
         <v>0</v>
@@ -9072,7 +9069,7 @@
         <v>182</v>
       </c>
       <c r="C316" s="14" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D316" s="19" t="s">
         <v>1</v>
@@ -9086,7 +9083,7 @@
         <v>183</v>
       </c>
       <c r="C317" s="14" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D317" s="18" t="s">
         <v>1</v>
@@ -9097,10 +9094,10 @@
         <v>317</v>
       </c>
       <c r="B318" s="11" t="s">
+        <v>677</v>
+      </c>
+      <c r="C318" s="14" t="s">
         <v>678</v>
-      </c>
-      <c r="C318" s="14" t="s">
-        <v>679</v>
       </c>
       <c r="D318" s="20" t="s">
         <v>17</v>
@@ -9114,7 +9111,7 @@
         <v>184</v>
       </c>
       <c r="C319" s="14" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D319" s="19" t="s">
         <v>1</v>
@@ -9128,7 +9125,7 @@
         <v>185</v>
       </c>
       <c r="C320" s="14" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D320" s="19" t="s">
         <v>20</v>
@@ -9142,7 +9139,7 @@
         <v>186</v>
       </c>
       <c r="C321" s="14" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D321" s="18" t="s">
         <v>20</v>
@@ -9156,7 +9153,7 @@
         <v>187</v>
       </c>
       <c r="C322" s="14" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D322" s="23" t="s">
         <v>0</v>
@@ -9170,7 +9167,7 @@
         <v>188</v>
       </c>
       <c r="C323" s="14" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D323" s="22" t="s">
         <v>20</v>
@@ -9184,7 +9181,7 @@
         <v>189</v>
       </c>
       <c r="C324" s="14" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D324" s="22" t="s">
         <v>20</v>
@@ -9198,7 +9195,7 @@
         <v>190</v>
       </c>
       <c r="C325" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D325" s="15" t="s">
         <v>1</v>
@@ -9212,7 +9209,7 @@
         <v>191</v>
       </c>
       <c r="C326" s="14" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D326" s="19" t="s">
         <v>20</v>
@@ -9226,7 +9223,7 @@
         <v>192</v>
       </c>
       <c r="C327" s="14" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D327" s="19" t="s">
         <v>20</v>
@@ -9240,7 +9237,7 @@
         <v>193</v>
       </c>
       <c r="C328" s="14" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D328" s="19" t="s">
         <v>17</v>
@@ -9251,10 +9248,10 @@
         <v>328</v>
       </c>
       <c r="B329" s="11" t="s">
+        <v>689</v>
+      </c>
+      <c r="C329" s="14" t="s">
         <v>690</v>
-      </c>
-      <c r="C329" s="14" t="s">
-        <v>691</v>
       </c>
       <c r="D329" s="19" t="s">
         <v>17</v>
@@ -9265,10 +9262,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="11" t="s">
+        <v>691</v>
+      </c>
+      <c r="C330" s="14" t="s">
         <v>692</v>
-      </c>
-      <c r="C330" s="14" t="s">
-        <v>693</v>
       </c>
       <c r="D330" s="19" t="s">
         <v>17</v>
@@ -9282,7 +9279,7 @@
         <v>194</v>
       </c>
       <c r="C331" s="14" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D331" s="19" t="s">
         <v>0</v>
@@ -9293,10 +9290,10 @@
         <v>331</v>
       </c>
       <c r="B332" s="11" t="s">
+        <v>694</v>
+      </c>
+      <c r="C332" s="14" t="s">
         <v>695</v>
-      </c>
-      <c r="C332" s="14" t="s">
-        <v>696</v>
       </c>
       <c r="D332" s="23" t="s">
         <v>0</v>
@@ -9310,7 +9307,7 @@
         <v>5</v>
       </c>
       <c r="C333" s="14" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D333" s="19" t="s">
         <v>20</v>
@@ -9324,7 +9321,7 @@
         <v>195</v>
       </c>
       <c r="C334" s="14" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D334" s="19" t="s">
         <v>20</v>
@@ -9335,10 +9332,10 @@
         <v>334</v>
       </c>
       <c r="B335" s="11" t="s">
+        <v>698</v>
+      </c>
+      <c r="C335" s="14" t="s">
         <v>699</v>
-      </c>
-      <c r="C335" s="14" t="s">
-        <v>700</v>
       </c>
       <c r="D335" s="19" t="s">
         <v>20</v>
@@ -9349,10 +9346,10 @@
         <v>335</v>
       </c>
       <c r="B336" s="11" t="s">
+        <v>700</v>
+      </c>
+      <c r="C336" s="14" t="s">
         <v>701</v>
-      </c>
-      <c r="C336" s="14" t="s">
-        <v>702</v>
       </c>
       <c r="D336" s="19" t="s">
         <v>20</v>
@@ -9366,7 +9363,7 @@
         <v>196</v>
       </c>
       <c r="C337" s="14" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D337" s="15" t="s">
         <v>20</v>
@@ -9380,7 +9377,7 @@
         <v>197</v>
       </c>
       <c r="C338" s="14" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D338" s="19" t="s">
         <v>1</v>
@@ -9394,7 +9391,7 @@
         <v>198</v>
       </c>
       <c r="C339" s="14" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D339" s="19" t="s">
         <v>17</v>
@@ -9405,10 +9402,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="11" t="s">
+        <v>705</v>
+      </c>
+      <c r="C340" s="14" t="s">
         <v>706</v>
-      </c>
-      <c r="C340" s="14" t="s">
-        <v>707</v>
       </c>
       <c r="D340" s="19" t="s">
         <v>1</v>
@@ -9422,7 +9419,7 @@
         <v>199</v>
       </c>
       <c r="C341" s="14" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D341" s="19" t="s">
         <v>1</v>
@@ -9436,7 +9433,7 @@
         <v>200</v>
       </c>
       <c r="C342" s="11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D342" s="19" t="s">
         <v>0</v>
@@ -9450,7 +9447,7 @@
         <v>201</v>
       </c>
       <c r="C343" s="11" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D343" s="19" t="s">
         <v>1</v>
@@ -9464,7 +9461,7 @@
         <v>202</v>
       </c>
       <c r="C344" s="11" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D344" s="19" t="s">
         <v>0</v>
@@ -9478,7 +9475,7 @@
         <v>203</v>
       </c>
       <c r="C345" s="11" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D345" s="19" t="s">
         <v>17</v>
@@ -9489,10 +9486,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="C346" s="11" t="s">
         <v>712</v>
-      </c>
-      <c r="C346" s="11" t="s">
-        <v>713</v>
       </c>
       <c r="D346" s="19" t="s">
         <v>17</v>
@@ -9506,7 +9503,7 @@
         <v>204</v>
       </c>
       <c r="C347" s="11" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D347" s="19" t="s">
         <v>0</v>
@@ -9520,7 +9517,7 @@
         <v>205</v>
       </c>
       <c r="C348" s="11" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="D348" s="19" t="s">
         <v>0</v>
@@ -9534,7 +9531,7 @@
         <v>206</v>
       </c>
       <c r="C349" s="11" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="D349" s="19" t="s">
         <v>0</v>
@@ -9548,7 +9545,7 @@
         <v>207</v>
       </c>
       <c r="C350" s="11" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D350" s="15" t="s">
         <v>1</v>
@@ -9559,10 +9556,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="11" t="s">
+        <v>717</v>
+      </c>
+      <c r="C351" s="11" t="s">
         <v>718</v>
-      </c>
-      <c r="C351" s="11" t="s">
-        <v>719</v>
       </c>
       <c r="D351" s="19" t="s">
         <v>1</v>
@@ -9576,7 +9573,7 @@
         <v>208</v>
       </c>
       <c r="C352" s="11" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D352" s="19" t="s">
         <v>20</v>
@@ -9590,7 +9587,7 @@
         <v>209</v>
       </c>
       <c r="C353" s="11" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D353" s="19" t="s">
         <v>0</v>
@@ -9601,10 +9598,10 @@
         <v>353</v>
       </c>
       <c r="B354" s="11" t="s">
+        <v>721</v>
+      </c>
+      <c r="C354" s="11" t="s">
         <v>722</v>
-      </c>
-      <c r="C354" s="11" t="s">
-        <v>723</v>
       </c>
       <c r="D354" s="19" t="s">
         <v>20</v>
@@ -9618,7 +9615,7 @@
         <v>210</v>
       </c>
       <c r="C355" s="11" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D355" s="19" t="s">
         <v>0</v>
@@ -9629,10 +9626,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="11" t="s">
+        <v>724</v>
+      </c>
+      <c r="C356" s="11" t="s">
         <v>725</v>
-      </c>
-      <c r="C356" s="11" t="s">
-        <v>726</v>
       </c>
       <c r="D356" s="19" t="s">
         <v>1</v>
@@ -9646,7 +9643,7 @@
         <v>211</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D357" s="15" t="s">
         <v>20</v>
@@ -9660,7 +9657,7 @@
         <v>6</v>
       </c>
       <c r="C358" s="11" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D358" s="34" t="s">
         <v>17</v>
@@ -9674,7 +9671,7 @@
         <v>7</v>
       </c>
       <c r="C359" s="30" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D359" s="30" t="s">
         <v>20</v>
@@ -9685,10 +9682,10 @@
         <v>359</v>
       </c>
       <c r="B360" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="C360" s="11" t="s">
         <v>730</v>
-      </c>
-      <c r="C360" s="11" t="s">
-        <v>731</v>
       </c>
       <c r="D360" s="19" t="s">
         <v>17</v>
@@ -9699,10 +9696,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="30" t="s">
+        <v>731</v>
+      </c>
+      <c r="C361" s="30" t="s">
         <v>732</v>
-      </c>
-      <c r="C361" s="30" t="s">
-        <v>733</v>
       </c>
       <c r="D361" s="15" t="s">
         <v>20</v>
@@ -9713,10 +9710,10 @@
         <v>361</v>
       </c>
       <c r="B362" s="30" t="s">
+        <v>733</v>
+      </c>
+      <c r="C362" s="30" t="s">
         <v>734</v>
-      </c>
-      <c r="C362" s="30" t="s">
-        <v>735</v>
       </c>
       <c r="D362" s="15" t="s">
         <v>17</v>
@@ -9730,7 +9727,7 @@
         <v>212</v>
       </c>
       <c r="C363" s="30" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D363" s="15" t="s">
         <v>20</v>
@@ -9744,7 +9741,7 @@
         <v>213</v>
       </c>
       <c r="C364" s="30" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D364" s="15" t="s">
         <v>0</v>
@@ -9758,7 +9755,7 @@
         <v>214</v>
       </c>
       <c r="C365" s="30" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D365" s="15" t="s">
         <v>0</v>
@@ -9772,7 +9769,7 @@
         <v>215</v>
       </c>
       <c r="C366" s="30" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D366" s="15" t="s">
         <v>20</v>
@@ -9786,7 +9783,7 @@
         <v>216</v>
       </c>
       <c r="C367" s="30" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D367" s="15" t="s">
         <v>20</v>
@@ -9797,10 +9794,10 @@
         <v>367</v>
       </c>
       <c r="B368" s="11" t="s">
+        <v>740</v>
+      </c>
+      <c r="C368" s="30" t="s">
         <v>741</v>
-      </c>
-      <c r="C368" s="30" t="s">
-        <v>742</v>
       </c>
       <c r="D368" s="15" t="s">
         <v>0</v>
@@ -9814,21 +9811,21 @@
         <v>217</v>
       </c>
       <c r="C369" s="30" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D369" s="15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="370" spans="1:4" ht="62" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A370" s="10">
         <v>369</v>
       </c>
       <c r="B370" s="30" t="s">
+        <v>743</v>
+      </c>
+      <c r="C370" s="30" t="s">
         <v>744</v>
-      </c>
-      <c r="C370" s="30" t="s">
-        <v>745</v>
       </c>
       <c r="D370" s="15" t="s">
         <v>17</v>
@@ -9842,7 +9839,7 @@
         <v>8</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D371" s="15" t="s">
         <v>1</v>
@@ -9856,7 +9853,7 @@
         <v>218</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D372" s="15" t="s">
         <v>0</v>
@@ -9870,7 +9867,7 @@
         <v>219</v>
       </c>
       <c r="C373" s="30" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D373" s="15" t="s">
         <v>1</v>
@@ -9884,7 +9881,7 @@
         <v>220</v>
       </c>
       <c r="C374" s="30" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D374" s="15" t="s">
         <v>0</v>
@@ -9898,7 +9895,7 @@
         <v>221</v>
       </c>
       <c r="C375" s="30" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D375" s="15" t="s">
         <v>1</v>
@@ -9909,10 +9906,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="11" t="s">
+        <v>750</v>
+      </c>
+      <c r="C376" s="30" t="s">
         <v>751</v>
-      </c>
-      <c r="C376" s="30" t="s">
-        <v>752</v>
       </c>
       <c r="D376" s="15" t="s">
         <v>0</v>
@@ -9926,7 +9923,7 @@
         <v>222</v>
       </c>
       <c r="C377" s="30" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D377" s="15" t="s">
         <v>20</v>
@@ -9940,7 +9937,7 @@
         <v>223</v>
       </c>
       <c r="C378" s="30" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D378" s="15" t="s">
         <v>17</v>
@@ -9954,7 +9951,7 @@
         <v>224</v>
       </c>
       <c r="C379" s="30" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D379" s="15" t="s">
         <v>20</v>
@@ -9968,21 +9965,21 @@
         <v>9</v>
       </c>
       <c r="C380" s="30" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D380" s="15" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:4" ht="124" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:4" ht="139.5" x14ac:dyDescent="0.35">
       <c r="A381" s="10">
         <v>380</v>
       </c>
       <c r="B381" s="30" t="s">
+        <v>756</v>
+      </c>
+      <c r="C381" s="30" t="s">
         <v>757</v>
-      </c>
-      <c r="C381" s="30" t="s">
-        <v>758</v>
       </c>
       <c r="D381" s="15" t="s">
         <v>17</v>
@@ -9996,7 +9993,7 @@
         <v>225</v>
       </c>
       <c r="C382" s="30" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D382" s="15" t="s">
         <v>1</v>
@@ -10010,7 +10007,7 @@
         <v>226</v>
       </c>
       <c r="C383" s="30" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D383" s="15" t="s">
         <v>0</v>
@@ -10024,7 +10021,7 @@
         <v>227</v>
       </c>
       <c r="C384" s="30" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D384" s="15" t="s">
         <v>0</v>
@@ -10038,7 +10035,7 @@
         <v>228</v>
       </c>
       <c r="C385" s="30" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D385" s="15" t="s">
         <v>1</v>
@@ -10052,7 +10049,7 @@
         <v>229</v>
       </c>
       <c r="C386" s="11" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D386" s="15" t="s">
         <v>17</v>
@@ -10066,7 +10063,7 @@
         <v>230</v>
       </c>
       <c r="C387" s="11" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D387" s="15" t="s">
         <v>20</v>
@@ -10080,7 +10077,7 @@
         <v>231</v>
       </c>
       <c r="C388" s="11" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D388" s="15" t="s">
         <v>17</v>
@@ -10091,10 +10088,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="11" t="s">
+        <v>765</v>
+      </c>
+      <c r="C389" s="11" t="s">
         <v>766</v>
-      </c>
-      <c r="C389" s="11" t="s">
-        <v>767</v>
       </c>
       <c r="D389" s="19" t="s">
         <v>1</v>
@@ -10105,10 +10102,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="C390" s="11" t="s">
         <v>768</v>
-      </c>
-      <c r="C390" s="11" t="s">
-        <v>769</v>
       </c>
       <c r="D390" s="19" t="s">
         <v>1</v>
@@ -10122,7 +10119,7 @@
         <v>232</v>
       </c>
       <c r="C391" s="11" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D391" s="19" t="s">
         <v>1</v>
@@ -10135,11 +10132,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="6227360e-e60f-4595-9753-ac508485ddd6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10370,27 +10368,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="6227360e-e60f-4595-9753-ac508485ddd6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC35CC7-6F58-4296-A78C-C761A4406030}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8A0EA2E-6E25-4712-9DB6-6E8798AE1CF1}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="6227360e-e60f-4595-9753-ac508485ddd6"/>
-    <ds:schemaRef ds:uri="bc054b22-9395-4512-bde7-19a23f2dcff6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -10415,9 +10403,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8A0EA2E-6E25-4712-9DB6-6E8798AE1CF1}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BC35CC7-6F58-4296-A78C-C761A4406030}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="6227360e-e60f-4595-9753-ac508485ddd6"/>
+    <ds:schemaRef ds:uri="bc054b22-9395-4512-bde7-19a23f2dcff6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/data/Ngan-Hang-Cau-Hoi.xlsx
+++ b/data/Ngan-Hang-Cau-Hoi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9f54d0bdb7235122/Documents/My App/trac-nghiem-luat-dau-thau/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9945B2BA-DA03-453F-91C4-0EF789E4D547}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6669B6E6-5ED4-4F8F-B91B-022AC5ED8FA7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0822E189-CD53-41B9-B216-EFA7EF505EBC}"/>
   </bookViews>
@@ -1523,13 +1523,6 @@
 không đề xuất cụ thể ký mã hiệu, nhãn hiệu, xuất xứ, hãng sản xuất thì xử lý như thế nào?</t>
   </si>
   <si>
-    <t>A. Chủ đầu tư yêu cầu nhà thầu làm rõ các thông tin này để làm cơ sở đánh giá trên cơ sở không được thay đổi giá dự thầu
-B. Tổ chuyên gia căn cứ theo cataloge, đề xuất kỹ thuật kèm theo để làm cơ sở đánh giá
-C. Hồ sơ dự thầu của nhà thầu không được xem xét, đánh giá
-D. Tiếp tục đánh giá hồ sơ dự thầu, trường hơp nhà thầu trúng thầu thì yêu cầu nhà thầu bổ sung, làm
-rõ các thông tin này</t>
-  </si>
-  <si>
     <t>A. Đánh giá năng lực, kinh nghiệm của nhà thầu phụ căn cứ theo phần công việc nhà thầu phụ đảm nhận, nhà thầu tham dự thầu không phải đáp ứng về năng lực, kinh nghiệm đối với phần công việc mà nhà thầu phụ đảm nhận
 B. Không đánh giá năng lực, kinh nghiệm của nhà thầu phụ, nhà thầu tham dự thầu vẫn phải đáp ứng về năng lực, kinh nghiệm đối với phần công việc mà nhà thầu phụ đảm nhận
 C. Do chủ đầu tư quyết định đánh giá hoặc không đánh giá năng lực, kinh nghiệm nhà thầu phụ
@@ -1714,13 +1707,6 @@
 đây?</t>
   </si>
   <si>
-    <t>A. Được đăng tải trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 24 giờ kể từ thời điểm mở thầu
-B. Được đăng tải trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 02 giờ kể từ thời điểm mở thầu
-C. Được đăng tải trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 04 giờ kể từ thời điểm mở thầu
-D. Được đăng tải trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 03 ngày làm việc kể từ thời
-điểm mở thầu</t>
-  </si>
-  <si>
     <t>Chủ đầu tư A và nhà thầu B đã ký kết hợp đồng cung cấp 11000 đơn vị hàng hóa, loại hợp đồng theo đơn giá cố định. Trong quá trình thực hiện hợp đồng, nhu cầu sử dụng thực tế mà nhà thầu phải cung cấp cho chủ đầu tư chỉ là 10500 đơn vị hàng hóa.  Hãy lựa chọn phương án đúng về sửa đổi hợp
 đồng trong trường hợp này?</t>
   </si>
@@ -1729,13 +1715,6 @@
 B. Chủ đầu tư A và nhà thầu B không cần thực hiện thủ tục sửa đổi hợp đồng, không phải ký kết văn bản sửa đổi hợp đồng
 C. Chủ đầu tư A và nhà thầu B bắt buộc phải thực hiện thủ tục ký phụ lục hợp đồng để điều chỉnh khối lượng
 D. Phương án A và C đều đúng</t>
-  </si>
-  <si>
-    <t>A. Khi có sự thay đổi về chính sách, pháp luật làm ảnh hưởng trực tiếp đến việc thực hiện hợp đồng
-B. Khi có sự kiện bất khả kháng
-C. Khi thay đổi phương thức vận chuyển, địa điểm giao hàng, dịch vụ liên quan đối với gói thầu mua sắm hàng hóa
-D. Tăng, giảm thời gian đối với hợp đồng theo thời gian; tăng, giảm chi phí trực tiếp thực hiện đối với hợp đồng chi phí cộng phí; tăng, giảm giá trị cơ sở để tính phần trăm chi phí đối với hợp đồng theo tỷ lệ phần trăm; tăng, giảm mức giảm trừ thanh toán, mức tăng giá trị thanh toán đối với hợp
-đồng theo kết quả đầu ra</t>
   </si>
   <si>
     <t xml:space="preserve">A. Hồ sơ mời quan tâm, hồ sơ mời sơ tuyển, hồ sơ mời thầu được phát hành sau 01 ngày kể từ khi thông báo mời quan tâm, thông báo mời sơ tuyển, thông báo mời thầu được đăng tải thành công trên Hệ thống mạng đấu thầu quốc gia
@@ -3833,6 +3812,24 @@
 B. Năng lực và kinh nghiệm của nhà thầu phụ sẽ không được xem xét khi đánh giá E-HSDT của nhà thầu
 C. Nhà thầu được ký kết hợp đồng với các nhà thầu phụ trong danh sách các nhà thầu phụ nêu trong E-HSDT
 D. Nhà thầu được ký kết hợp đồng với các nhà thầu phụ được chủ đầu tư chấp thuận để tham gia thực hiện cung cấp dịch vụ liên quan</t>
+  </si>
+  <si>
+    <t>A. Được đăng tải trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 24 giờ kể từ thời điểm mở thầu
+B. Được đăng tải trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 02 giờ kể từ thời điểm mở thầu
+C. Được đăng tải trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 04 giờ kể từ thời điểm mở thầu
+D. Được đăng tải trên Hệ thống mạng đấu thầu quốc gia trong thời hạn 03 ngày làm việc kể từ thời điểm mở thầu</t>
+  </si>
+  <si>
+    <t>A. Khi có sự thay đổi về chính sách, pháp luật làm ảnh hưởng trực tiếp đến việc thực hiện hợp đồng
+B. Khi có sự kiện bất khả kháng
+C. Khi thay đổi phương thức vận chuyển, địa điểm giao hàng, dịch vụ liên quan đối với gói thầu mua sắm hàng hóa
+D. Tăng, giảm thời gian đối với hợp đồng theo thời gian; tăng, giảm chi phí trực tiếp thực hiện đối với hợp đồng chi phí cộng phí; tăng, giảm giá trị cơ sở để tính phần trăm chi phí đối với hợp đồng theo tỷ lệ phần trăm; tăng, giảm mức giảm trừ thanh toán, mức tăng giá trị thanh toán đối với hợp đồng theo kết quả đầu ra</t>
+  </si>
+  <si>
+    <t>A. Chủ đầu tư yêu cầu nhà thầu làm rõ các thông tin này để làm cơ sở đánh giá trên cơ sở không được thay đổi giá dự thầu
+B. Tổ chuyên gia căn cứ theo cataloge, đề xuất kỹ thuật kèm theo để làm cơ sở đánh giá
+C. Hồ sơ dự thầu của nhà thầu không được xem xét, đánh giá
+D. Tiếp tục đánh giá hồ sơ dự thầu, trường hơp nhà thầu trúng thầu thì yêu cầu nhà thầu bổ sung, làm rõ các thông tin này</t>
   </si>
 </sst>
 </file>
@@ -5723,7 +5720,7 @@
         <v>341</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>1</v>
@@ -5779,7 +5776,7 @@
         <v>58</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D81" s="19" t="s">
         <v>1</v>
@@ -6009,7 +6006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="98" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A98" s="10">
         <v>97</v>
       </c>
@@ -6017,7 +6014,7 @@
         <v>372</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>373</v>
+        <v>783</v>
       </c>
       <c r="D98" s="20" t="s">
         <v>20</v>
@@ -6031,7 +6028,7 @@
         <v>65</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D99" s="19" t="s">
         <v>17</v>
@@ -6045,7 +6042,7 @@
         <v>4</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="D100" s="26" t="s">
         <v>1</v>
@@ -6059,7 +6056,7 @@
         <v>66</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D101" s="21" t="s">
         <v>17</v>
@@ -6070,10 +6067,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="C102" s="14" t="s">
         <v>375</v>
-      </c>
-      <c r="C102" s="14" t="s">
-        <v>376</v>
       </c>
       <c r="D102" s="22" t="s">
         <v>0</v>
@@ -6087,7 +6084,7 @@
         <v>67</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D103" s="20" t="s">
         <v>17</v>
@@ -6101,7 +6098,7 @@
         <v>68</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D104" s="24" t="s">
         <v>1</v>
@@ -6112,10 +6109,10 @@
         <v>104</v>
       </c>
       <c r="B105" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="C105" s="14" t="s">
         <v>379</v>
-      </c>
-      <c r="C105" s="14" t="s">
-        <v>380</v>
       </c>
       <c r="D105" s="20" t="s">
         <v>17</v>
@@ -6126,10 +6123,10 @@
         <v>105</v>
       </c>
       <c r="B106" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="C106" s="14" t="s">
         <v>381</v>
-      </c>
-      <c r="C106" s="14" t="s">
-        <v>382</v>
       </c>
       <c r="D106" s="18" t="s">
         <v>17</v>
@@ -6143,7 +6140,7 @@
         <v>69</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>20</v>
@@ -6157,7 +6154,7 @@
         <v>70</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D108" s="21" t="s">
         <v>20</v>
@@ -6171,7 +6168,7 @@
         <v>71</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D109" s="21" t="s">
         <v>20</v>
@@ -6185,7 +6182,7 @@
         <v>72</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D110" s="20" t="s">
         <v>17</v>
@@ -6196,10 +6193,10 @@
         <v>110</v>
       </c>
       <c r="B111" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="C111" s="14" t="s">
         <v>386</v>
-      </c>
-      <c r="C111" s="14" t="s">
-        <v>387</v>
       </c>
       <c r="D111" s="19" t="s">
         <v>20</v>
@@ -6210,10 +6207,10 @@
         <v>111</v>
       </c>
       <c r="B112" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="C112" s="14" t="s">
         <v>388</v>
-      </c>
-      <c r="C112" s="14" t="s">
-        <v>389</v>
       </c>
       <c r="D112" s="19" t="s">
         <v>17</v>
@@ -6224,10 +6221,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="D113" s="19" t="s">
         <v>1</v>
@@ -6238,10 +6235,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="C114" s="30" t="s">
         <v>391</v>
-      </c>
-      <c r="C114" s="30" t="s">
-        <v>392</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>0</v>
@@ -6252,10 +6249,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="30" t="s">
+        <v>392</v>
+      </c>
+      <c r="C115" s="30" t="s">
         <v>393</v>
-      </c>
-      <c r="C115" s="30" t="s">
-        <v>394</v>
       </c>
       <c r="D115" s="15" t="s">
         <v>1</v>
@@ -6266,10 +6263,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="C116" s="30" t="s">
         <v>395</v>
-      </c>
-      <c r="C116" s="30" t="s">
-        <v>396</v>
       </c>
       <c r="D116" s="12" t="s">
         <v>1</v>
@@ -6280,10 +6277,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="30" t="s">
+        <v>396</v>
+      </c>
+      <c r="C117" s="30" t="s">
         <v>397</v>
-      </c>
-      <c r="C117" s="30" t="s">
-        <v>398</v>
       </c>
       <c r="D117" s="12" t="s">
         <v>1</v>
@@ -6297,7 +6294,7 @@
         <v>73</v>
       </c>
       <c r="C118" s="30" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D118" s="12" t="s">
         <v>20</v>
@@ -6311,7 +6308,7 @@
         <v>74</v>
       </c>
       <c r="C119" s="30" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>0</v>
@@ -6325,7 +6322,7 @@
         <v>75</v>
       </c>
       <c r="C120" s="30" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D120" s="12" t="s">
         <v>20</v>
@@ -6336,10 +6333,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="11" t="s">
+        <v>401</v>
+      </c>
+      <c r="C121" s="14" t="s">
         <v>402</v>
-      </c>
-      <c r="C121" s="14" t="s">
-        <v>403</v>
       </c>
       <c r="D121" s="15" t="s">
         <v>1</v>
@@ -6353,7 +6350,7 @@
         <v>76</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>1</v>
@@ -6367,7 +6364,7 @@
         <v>77</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D123" s="15" t="s">
         <v>1</v>
@@ -6378,16 +6375,16 @@
         <v>123</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D124" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A125" s="7">
         <v>124</v>
       </c>
@@ -6395,7 +6392,7 @@
         <v>78</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>407</v>
+        <v>781</v>
       </c>
       <c r="D125" s="21" t="s">
         <v>1</v>
@@ -6406,16 +6403,16 @@
         <v>125</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D126" s="21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="127" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A127" s="7">
         <v>126</v>
       </c>
@@ -6423,7 +6420,7 @@
         <v>79</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>410</v>
+        <v>782</v>
       </c>
       <c r="D127" s="21" t="s">
         <v>0</v>
@@ -6437,7 +6434,7 @@
         <v>80</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="D128" s="19" t="s">
         <v>0</v>
@@ -6451,7 +6448,7 @@
         <v>81</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D129" s="19" t="s">
         <v>1</v>
@@ -6465,7 +6462,7 @@
         <v>82</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D130" s="22" t="s">
         <v>1</v>
@@ -6479,7 +6476,7 @@
         <v>83</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D131" s="22" t="s">
         <v>20</v>
@@ -6493,7 +6490,7 @@
         <v>84</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="D132" s="19" t="s">
         <v>1</v>
@@ -6504,10 +6501,10 @@
         <v>132</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="D133" s="15" t="s">
         <v>1</v>
@@ -6518,10 +6515,10 @@
         <v>133</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D134" s="31" t="s">
         <v>0</v>
@@ -6535,7 +6532,7 @@
         <v>85</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="D135" s="19" t="s">
         <v>20</v>
@@ -6546,10 +6543,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D136" s="21" t="s">
         <v>0</v>
@@ -6563,7 +6560,7 @@
         <v>86</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D137" s="24" t="s">
         <v>0</v>
@@ -6577,7 +6574,7 @@
         <v>87</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D138" s="22" t="s">
         <v>1</v>
@@ -6591,7 +6588,7 @@
         <v>88</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D139" s="22" t="s">
         <v>0</v>
@@ -6605,7 +6602,7 @@
         <v>89</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="D140" s="18" t="s">
         <v>17</v>
@@ -6619,7 +6616,7 @@
         <v>90</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D141" s="20" t="s">
         <v>17</v>
@@ -6630,10 +6627,10 @@
         <v>141</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D142" s="22" t="s">
         <v>1</v>
@@ -6647,7 +6644,7 @@
         <v>91</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="D143" s="18" t="s">
         <v>20</v>
@@ -6661,7 +6658,7 @@
         <v>92</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>17</v>
@@ -6675,7 +6672,7 @@
         <v>93</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D145" s="19" t="s">
         <v>17</v>
@@ -6686,10 +6683,10 @@
         <v>145</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D146" s="19" t="s">
         <v>20</v>
@@ -6700,10 +6697,10 @@
         <v>146</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D147" s="24" t="s">
         <v>1</v>
@@ -6714,10 +6711,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="D148" s="19" t="s">
         <v>17</v>
@@ -6731,7 +6728,7 @@
         <v>94</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D149" s="21" t="s">
         <v>20</v>
@@ -6742,10 +6739,10 @@
         <v>149</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D150" s="24" t="s">
         <v>20</v>
@@ -6759,7 +6756,7 @@
         <v>95</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="D151" s="24" t="s">
         <v>17</v>
@@ -6773,7 +6770,7 @@
         <v>96</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D152" s="22" t="s">
         <v>1</v>
@@ -6784,10 +6781,10 @@
         <v>152</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="D153" s="18" t="s">
         <v>0</v>
@@ -6798,10 +6795,10 @@
         <v>153</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="D154" s="18" t="s">
         <v>1</v>
@@ -6815,7 +6812,7 @@
         <v>97</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="D155" s="19" t="s">
         <v>17</v>
@@ -6826,10 +6823,10 @@
         <v>155</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="D156" s="18" t="s">
         <v>17</v>
@@ -6840,10 +6837,10 @@
         <v>156</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="D157" s="15" t="s">
         <v>17</v>
@@ -6857,7 +6854,7 @@
         <v>98</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="D158" s="18" t="s">
         <v>0</v>
@@ -6868,10 +6865,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="D159" s="18" t="s">
         <v>1</v>
@@ -6885,7 +6882,7 @@
         <v>99</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D160" s="18" t="s">
         <v>17</v>
@@ -6896,10 +6893,10 @@
         <v>160</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D161" s="23" t="s">
         <v>20</v>
@@ -6913,7 +6910,7 @@
         <v>100</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="D162" s="18" t="s">
         <v>0</v>
@@ -6924,10 +6921,10 @@
         <v>162</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C163" s="14" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="D163" s="18" t="s">
         <v>20</v>
@@ -6938,10 +6935,10 @@
         <v>163</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D164" s="24" t="s">
         <v>1</v>
@@ -6952,10 +6949,10 @@
         <v>164</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="C165" s="14" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D165" s="21" t="s">
         <v>17</v>
@@ -6966,10 +6963,10 @@
         <v>165</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D166" s="18" t="s">
         <v>20</v>
@@ -6980,10 +6977,10 @@
         <v>166</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="D167" s="20" t="s">
         <v>20</v>
@@ -6994,10 +6991,10 @@
         <v>167</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="D168" s="18" t="s">
         <v>0</v>
@@ -7011,7 +7008,7 @@
         <v>101</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D169" s="26" t="s">
         <v>1</v>
@@ -7022,10 +7019,10 @@
         <v>169</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="D170" s="21" t="s">
         <v>17</v>
@@ -7039,7 +7036,7 @@
         <v>102</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="D171" s="20" t="s">
         <v>17</v>
@@ -7053,7 +7050,7 @@
         <v>103</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="D172" s="19" t="s">
         <v>20</v>
@@ -7064,10 +7061,10 @@
         <v>172</v>
       </c>
       <c r="B173" s="11" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D173" s="19" t="s">
         <v>1</v>
@@ -7081,7 +7078,7 @@
         <v>104</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="D174" s="19" t="s">
         <v>17</v>
@@ -7092,10 +7089,10 @@
         <v>174</v>
       </c>
       <c r="B175" s="11" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D175" s="19" t="s">
         <v>17</v>
@@ -7109,7 +7106,7 @@
         <v>105</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="D176" s="19" t="s">
         <v>17</v>
@@ -7120,10 +7117,10 @@
         <v>176</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D177" s="19" t="s">
         <v>0</v>
@@ -7134,10 +7131,10 @@
         <v>177</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D178" s="19" t="s">
         <v>17</v>
@@ -7148,10 +7145,10 @@
         <v>178</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D179" s="19" t="s">
         <v>20</v>
@@ -7162,10 +7159,10 @@
         <v>179</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D180" s="19" t="s">
         <v>17</v>
@@ -7176,10 +7173,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D181" s="19" t="s">
         <v>0</v>
@@ -7190,10 +7187,10 @@
         <v>181</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D182" s="19" t="s">
         <v>1</v>
@@ -7207,7 +7204,7 @@
         <v>106</v>
       </c>
       <c r="C183" s="14" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="D183" s="19" t="s">
         <v>20</v>
@@ -7221,7 +7218,7 @@
         <v>107</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D184" s="19" t="s">
         <v>17</v>
@@ -7235,7 +7232,7 @@
         <v>108</v>
       </c>
       <c r="C185" s="14" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D185" s="19" t="s">
         <v>0</v>
@@ -7246,10 +7243,10 @@
         <v>185</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="D186" s="19" t="s">
         <v>17</v>
@@ -7260,10 +7257,10 @@
         <v>186</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="C187" s="14" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="D187" s="19" t="s">
         <v>20</v>
@@ -7274,10 +7271,10 @@
         <v>187</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D188" s="18" t="s">
         <v>1</v>
@@ -7291,7 +7288,7 @@
         <v>109</v>
       </c>
       <c r="C189" s="14" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D189" s="18" t="s">
         <v>20</v>
@@ -7302,10 +7299,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D190" s="22" t="s">
         <v>1</v>
@@ -7316,10 +7313,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="C191" s="14" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>0</v>
@@ -7330,10 +7327,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C192" s="14" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D192" s="18" t="s">
         <v>1</v>
@@ -7347,7 +7344,7 @@
         <v>110</v>
       </c>
       <c r="C193" s="14" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D193" s="18" t="s">
         <v>0</v>
@@ -7361,7 +7358,7 @@
         <v>111</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D194" s="15" t="s">
         <v>1</v>
@@ -7372,10 +7369,10 @@
         <v>194</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="C195" s="14" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D195" s="19" t="s">
         <v>1</v>
@@ -7386,10 +7383,10 @@
         <v>195</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C196" s="14" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D196" s="20" t="s">
         <v>17</v>
@@ -7403,7 +7400,7 @@
         <v>112</v>
       </c>
       <c r="C197" s="14" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D197" s="19" t="s">
         <v>1</v>
@@ -7417,7 +7414,7 @@
         <v>113</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D198" s="18" t="s">
         <v>0</v>
@@ -7428,10 +7425,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C199" s="14" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D199" s="18" t="s">
         <v>0</v>
@@ -7442,10 +7439,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D200" s="19" t="s">
         <v>1</v>
@@ -7456,10 +7453,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C201" s="14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D201" s="24" t="s">
         <v>1</v>
@@ -7473,7 +7470,7 @@
         <v>114</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="D202" s="23" t="s">
         <v>20</v>
@@ -7487,7 +7484,7 @@
         <v>115</v>
       </c>
       <c r="C203" s="14" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="D203" s="24" t="s">
         <v>17</v>
@@ -7501,7 +7498,7 @@
         <v>116</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D204" s="24" t="s">
         <v>20</v>
@@ -7512,10 +7509,10 @@
         <v>204</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C205" s="14" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D205" s="18" t="s">
         <v>0</v>
@@ -7526,10 +7523,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C206" s="14" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D206" s="18" t="s">
         <v>1</v>
@@ -7543,7 +7540,7 @@
         <v>117</v>
       </c>
       <c r="C207" s="14" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D207" s="19" t="s">
         <v>20</v>
@@ -7554,10 +7551,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D208" s="18" t="s">
         <v>1</v>
@@ -7568,10 +7565,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C209" s="14" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D209" s="18" t="s">
         <v>1</v>
@@ -7582,10 +7579,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="D210" s="18" t="s">
         <v>0</v>
@@ -7596,10 +7593,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C211" s="14" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="D211" s="32" t="s">
         <v>17</v>
@@ -7610,10 +7607,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="C212" s="14" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D212" s="21" t="s">
         <v>0</v>
@@ -7624,10 +7621,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C213" s="14" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="D213" s="32" t="s">
         <v>20</v>
@@ -7641,7 +7638,7 @@
         <v>118</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D214" s="21" t="s">
         <v>0</v>
@@ -7655,7 +7652,7 @@
         <v>119</v>
       </c>
       <c r="C215" s="14" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="D215" s="15" t="s">
         <v>20</v>
@@ -7666,10 +7663,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="C216" s="14" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D216" s="19" t="s">
         <v>20</v>
@@ -7683,7 +7680,7 @@
         <v>120</v>
       </c>
       <c r="C217" s="14" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D217" s="18" t="s">
         <v>0</v>
@@ -7697,7 +7694,7 @@
         <v>121</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="D218" s="20" t="s">
         <v>20</v>
@@ -7708,10 +7705,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="C219" s="14" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="D219" s="20" t="s">
         <v>17</v>
@@ -7722,10 +7719,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="11" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D220" s="19" t="s">
         <v>20</v>
@@ -7739,7 +7736,7 @@
         <v>122</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="D221" s="18" t="s">
         <v>17</v>
@@ -7753,7 +7750,7 @@
         <v>123</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D222" s="18" t="s">
         <v>0</v>
@@ -7767,7 +7764,7 @@
         <v>124</v>
       </c>
       <c r="C223" s="14" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D223" s="18" t="s">
         <v>0</v>
@@ -7781,7 +7778,7 @@
         <v>125</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D224" s="18" t="s">
         <v>0</v>
@@ -7795,7 +7792,7 @@
         <v>126</v>
       </c>
       <c r="C225" s="14" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="D225" s="18" t="s">
         <v>0</v>
@@ -7806,10 +7803,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="11" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="D226" s="18" t="s">
         <v>1</v>
@@ -7823,7 +7820,7 @@
         <v>127</v>
       </c>
       <c r="C227" s="14" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="D227" s="20" t="s">
         <v>17</v>
@@ -7837,7 +7834,7 @@
         <v>128</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D228" s="18" t="s">
         <v>0</v>
@@ -7848,10 +7845,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="11" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="C229" s="14" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D229" s="20" t="s">
         <v>20</v>
@@ -7865,7 +7862,7 @@
         <v>129</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="D230" s="20" t="s">
         <v>20</v>
@@ -7879,7 +7876,7 @@
         <v>130</v>
       </c>
       <c r="C231" s="14" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D231" s="19" t="s">
         <v>1</v>
@@ -7893,7 +7890,7 @@
         <v>131</v>
       </c>
       <c r="C232" s="14" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="D232" s="19" t="s">
         <v>0</v>
@@ -7907,7 +7904,7 @@
         <v>132</v>
       </c>
       <c r="C233" s="14" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="D233" s="20" t="s">
         <v>20</v>
@@ -7921,7 +7918,7 @@
         <v>133</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D234" s="18" t="s">
         <v>0</v>
@@ -7932,10 +7929,10 @@
         <v>234</v>
       </c>
       <c r="B235" s="11" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="C235" s="14" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D235" s="20" t="s">
         <v>17</v>
@@ -7949,7 +7946,7 @@
         <v>134</v>
       </c>
       <c r="C236" s="11" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D236" s="20" t="s">
         <v>0</v>
@@ -7960,10 +7957,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="16" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="C237" s="14" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>0</v>
@@ -7974,10 +7971,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="11" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="D238" s="18" t="s">
         <v>20</v>
@@ -7991,7 +7988,7 @@
         <v>135</v>
       </c>
       <c r="C239" s="14" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>0</v>
@@ -8002,10 +7999,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="11" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="C240" s="14" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D240" s="20" t="s">
         <v>0</v>
@@ -8019,7 +8016,7 @@
         <v>136</v>
       </c>
       <c r="C241" s="14" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D241" s="21" t="s">
         <v>1</v>
@@ -8030,10 +8027,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="C242" s="14" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="D242" s="33" t="s">
         <v>0</v>
@@ -8044,10 +8041,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="11" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C243" s="25" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="D243" s="20" t="s">
         <v>20</v>
@@ -8061,7 +8058,7 @@
         <v>137</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="D244" s="18" t="s">
         <v>1</v>
@@ -8072,10 +8069,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C245" s="14" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D245" s="18" t="s">
         <v>17</v>
@@ -8086,10 +8083,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="11" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="D246" s="18" t="s">
         <v>17</v>
@@ -8100,10 +8097,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="C247" s="14" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="D247" s="18" t="s">
         <v>1</v>
@@ -8117,7 +8114,7 @@
         <v>138</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="D248" s="18" t="s">
         <v>20</v>
@@ -8128,10 +8125,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="C249" s="14" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>20</v>
@@ -8145,7 +8142,7 @@
         <v>139</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D250" s="18" t="s">
         <v>0</v>
@@ -8156,10 +8153,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="11" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="C251" s="14" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="D251" s="19" t="s">
         <v>20</v>
@@ -8173,7 +8170,7 @@
         <v>140</v>
       </c>
       <c r="C252" s="14" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="D252" s="20" t="s">
         <v>20</v>
@@ -8187,7 +8184,7 @@
         <v>141</v>
       </c>
       <c r="C253" s="14" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="D253" s="20" t="s">
         <v>20</v>
@@ -8201,7 +8198,7 @@
         <v>142</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="D254" s="20" t="s">
         <v>1</v>
@@ -8212,10 +8209,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="D255" s="18" t="s">
         <v>20</v>
@@ -8226,10 +8223,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="11" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="C256" s="14" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D256" s="18" t="s">
         <v>17</v>
@@ -8243,7 +8240,7 @@
         <v>143</v>
       </c>
       <c r="C257" s="14" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="D257" s="19" t="s">
         <v>0</v>
@@ -8257,7 +8254,7 @@
         <v>144</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="D258" s="18" t="s">
         <v>0</v>
@@ -8268,10 +8265,10 @@
         <v>258</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="C259" s="14" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="D259" s="19" t="s">
         <v>20</v>
@@ -8285,7 +8282,7 @@
         <v>145</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="D260" s="20" t="s">
         <v>1</v>
@@ -8299,7 +8296,7 @@
         <v>146</v>
       </c>
       <c r="C261" s="14" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="D261" s="18" t="s">
         <v>0</v>
@@ -8313,7 +8310,7 @@
         <v>147</v>
       </c>
       <c r="C262" s="14" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="D262" s="19" t="s">
         <v>0</v>
@@ -8327,7 +8324,7 @@
         <v>148</v>
       </c>
       <c r="C263" s="25" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D263" s="21" t="s">
         <v>0</v>
@@ -8338,10 +8335,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="30" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="C264" s="25" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="D264" s="19" t="s">
         <v>1</v>
@@ -8355,7 +8352,7 @@
         <v>149</v>
       </c>
       <c r="C265" s="25" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="D265" s="18" t="s">
         <v>1</v>
@@ -8369,7 +8366,7 @@
         <v>150</v>
       </c>
       <c r="C266" s="14" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="D266" s="35" t="s">
         <v>1</v>
@@ -8380,10 +8377,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="C267" s="14" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="D267" s="18" t="s">
         <v>0</v>
@@ -8394,10 +8391,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="11" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C268" s="14" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="D268" s="18" t="s">
         <v>1</v>
@@ -8408,10 +8405,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="11" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C269" s="14" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="D269" s="18" t="s">
         <v>1</v>
@@ -8425,7 +8422,7 @@
         <v>151</v>
       </c>
       <c r="C270" s="14" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="D270" s="18" t="s">
         <v>1</v>
@@ -8439,7 +8436,7 @@
         <v>152</v>
       </c>
       <c r="C271" s="14" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="D271" s="18" t="s">
         <v>0</v>
@@ -8450,10 +8447,10 @@
         <v>271</v>
       </c>
       <c r="B272" s="11" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C272" s="14" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="D272" s="18" t="s">
         <v>0</v>
@@ -8467,7 +8464,7 @@
         <v>153</v>
       </c>
       <c r="C273" s="14" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D273" s="15" t="s">
         <v>0</v>
@@ -8481,7 +8478,7 @@
         <v>154</v>
       </c>
       <c r="C274" s="14" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="D274" s="19" t="s">
         <v>20</v>
@@ -8495,7 +8492,7 @@
         <v>155</v>
       </c>
       <c r="C275" s="14" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="D275" s="18" t="s">
         <v>1</v>
@@ -8506,10 +8503,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="11" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C276" s="14" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="D276" s="36" t="s">
         <v>0</v>
@@ -8520,10 +8517,10 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C277" s="14" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="D277" s="36" t="s">
         <v>20</v>
@@ -8534,10 +8531,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="11" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C278" s="14" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D278" s="36" t="s">
         <v>0</v>
@@ -8548,10 +8545,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C279" s="14" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="D279" s="36" t="s">
         <v>17</v>
@@ -8562,10 +8559,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="11" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C280" s="14" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="D280" s="19" t="s">
         <v>20</v>
@@ -8579,7 +8576,7 @@
         <v>156</v>
       </c>
       <c r="C281" s="14" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="D281" s="19" t="s">
         <v>20</v>
@@ -8593,7 +8590,7 @@
         <v>157</v>
       </c>
       <c r="C282" s="14" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="D282" s="19" t="s">
         <v>17</v>
@@ -8607,7 +8604,7 @@
         <v>158</v>
       </c>
       <c r="C283" s="14" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="D283" s="19" t="s">
         <v>20</v>
@@ -8621,7 +8618,7 @@
         <v>159</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D284" s="19" t="s">
         <v>0</v>
@@ -8635,7 +8632,7 @@
         <v>160</v>
       </c>
       <c r="C285" s="14" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="D285" s="19" t="s">
         <v>17</v>
@@ -8649,7 +8646,7 @@
         <v>161</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="D286" s="19" t="s">
         <v>17</v>
@@ -8663,7 +8660,7 @@
         <v>162</v>
       </c>
       <c r="C287" s="14" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="D287" s="19" t="s">
         <v>0</v>
@@ -8677,7 +8674,7 @@
         <v>163</v>
       </c>
       <c r="C288" s="14" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="D288" s="19" t="s">
         <v>17</v>
@@ -8691,7 +8688,7 @@
         <v>164</v>
       </c>
       <c r="C289" s="25" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D289" s="19" t="s">
         <v>17</v>
@@ -8705,7 +8702,7 @@
         <v>165</v>
       </c>
       <c r="C290" s="14" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D290" s="19" t="s">
         <v>17</v>
@@ -8719,7 +8716,7 @@
         <v>166</v>
       </c>
       <c r="C291" s="14" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D291" s="19" t="s">
         <v>17</v>
@@ -8730,10 +8727,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C292" s="14" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D292" s="8" t="s">
         <v>17</v>
@@ -8744,10 +8741,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="11" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C293" s="14" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D293" s="19" t="s">
         <v>17</v>
@@ -8758,10 +8755,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="11" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C294" s="14" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D294" s="19" t="s">
         <v>20</v>
@@ -8775,7 +8772,7 @@
         <v>167</v>
       </c>
       <c r="C295" s="14" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D295" s="19" t="s">
         <v>20</v>
@@ -8789,7 +8786,7 @@
         <v>168</v>
       </c>
       <c r="C296" s="14" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D296" s="19" t="s">
         <v>20</v>
@@ -8803,7 +8800,7 @@
         <v>145</v>
       </c>
       <c r="C297" s="14" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="D297" s="19" t="s">
         <v>0</v>
@@ -8817,7 +8814,7 @@
         <v>169</v>
       </c>
       <c r="C298" s="14" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D298" s="19" t="s">
         <v>1</v>
@@ -8831,7 +8828,7 @@
         <v>170</v>
       </c>
       <c r="C299" s="14" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="D299" s="19" t="s">
         <v>0</v>
@@ -8842,10 +8839,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="11" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C300" s="14" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="D300" s="19" t="s">
         <v>1</v>
@@ -8859,7 +8856,7 @@
         <v>171</v>
       </c>
       <c r="C301" s="14" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D301" s="15" t="s">
         <v>20</v>
@@ -8870,10 +8867,10 @@
         <v>301</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="C302" s="14" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="D302" s="19" t="s">
         <v>0</v>
@@ -8887,7 +8884,7 @@
         <v>172</v>
       </c>
       <c r="C303" s="14" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D303" s="15" t="s">
         <v>17</v>
@@ -8901,7 +8898,7 @@
         <v>173</v>
       </c>
       <c r="C304" s="14" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="D304" s="19" t="s">
         <v>17</v>
@@ -8915,7 +8912,7 @@
         <v>174</v>
       </c>
       <c r="C305" s="14" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D305" s="19" t="s">
         <v>17</v>
@@ -8929,7 +8926,7 @@
         <v>175</v>
       </c>
       <c r="C306" s="14" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="D306" s="19" t="s">
         <v>17</v>
@@ -8943,7 +8940,7 @@
         <v>176</v>
       </c>
       <c r="C307" s="14" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="D307" s="15" t="s">
         <v>17</v>
@@ -8957,7 +8954,7 @@
         <v>177</v>
       </c>
       <c r="C308" s="14" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D308" s="19" t="s">
         <v>17</v>
@@ -8971,7 +8968,7 @@
         <v>178</v>
       </c>
       <c r="C309" s="14" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D309" s="19" t="s">
         <v>17</v>
@@ -8982,10 +8979,10 @@
         <v>309</v>
       </c>
       <c r="B310" s="11" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C310" s="14" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D310" s="19" t="s">
         <v>17</v>
@@ -8996,10 +8993,10 @@
         <v>310</v>
       </c>
       <c r="B311" s="11" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="C311" s="14" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="D311" s="19" t="s">
         <v>17</v>
@@ -9013,7 +9010,7 @@
         <v>179</v>
       </c>
       <c r="C312" s="14" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D312" s="19" t="s">
         <v>17</v>
@@ -9027,7 +9024,7 @@
         <v>180</v>
       </c>
       <c r="C313" s="14" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D313" s="19" t="s">
         <v>17</v>
@@ -9038,10 +9035,10 @@
         <v>313</v>
       </c>
       <c r="B314" s="11" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C314" s="14" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D314" s="19" t="s">
         <v>17</v>
@@ -9055,7 +9052,7 @@
         <v>181</v>
       </c>
       <c r="C315" s="14" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="D315" s="19" t="s">
         <v>0</v>
@@ -9069,7 +9066,7 @@
         <v>182</v>
       </c>
       <c r="C316" s="14" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D316" s="19" t="s">
         <v>1</v>
@@ -9083,7 +9080,7 @@
         <v>183</v>
       </c>
       <c r="C317" s="14" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="D317" s="18" t="s">
         <v>1</v>
@@ -9094,10 +9091,10 @@
         <v>317</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="C318" s="14" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="D318" s="20" t="s">
         <v>17</v>
@@ -9111,7 +9108,7 @@
         <v>184</v>
       </c>
       <c r="C319" s="14" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="D319" s="19" t="s">
         <v>1</v>
@@ -9125,7 +9122,7 @@
         <v>185</v>
       </c>
       <c r="C320" s="14" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D320" s="19" t="s">
         <v>20</v>
@@ -9139,7 +9136,7 @@
         <v>186</v>
       </c>
       <c r="C321" s="14" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="D321" s="18" t="s">
         <v>20</v>
@@ -9153,7 +9150,7 @@
         <v>187</v>
       </c>
       <c r="C322" s="14" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D322" s="23" t="s">
         <v>0</v>
@@ -9167,7 +9164,7 @@
         <v>188</v>
       </c>
       <c r="C323" s="14" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="D323" s="22" t="s">
         <v>20</v>
@@ -9181,7 +9178,7 @@
         <v>189</v>
       </c>
       <c r="C324" s="14" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="D324" s="22" t="s">
         <v>20</v>
@@ -9195,7 +9192,7 @@
         <v>190</v>
       </c>
       <c r="C325" s="14" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D325" s="15" t="s">
         <v>1</v>
@@ -9209,7 +9206,7 @@
         <v>191</v>
       </c>
       <c r="C326" s="14" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="D326" s="19" t="s">
         <v>20</v>
@@ -9223,7 +9220,7 @@
         <v>192</v>
       </c>
       <c r="C327" s="14" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="D327" s="19" t="s">
         <v>20</v>
@@ -9237,7 +9234,7 @@
         <v>193</v>
       </c>
       <c r="C328" s="14" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D328" s="19" t="s">
         <v>17</v>
@@ -9248,10 +9245,10 @@
         <v>328</v>
       </c>
       <c r="B329" s="11" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C329" s="14" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D329" s="19" t="s">
         <v>17</v>
@@ -9262,10 +9259,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="11" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C330" s="14" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D330" s="19" t="s">
         <v>17</v>
@@ -9279,7 +9276,7 @@
         <v>194</v>
       </c>
       <c r="C331" s="14" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D331" s="19" t="s">
         <v>0</v>
@@ -9290,10 +9287,10 @@
         <v>331</v>
       </c>
       <c r="B332" s="11" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="C332" s="14" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="D332" s="23" t="s">
         <v>0</v>
@@ -9307,7 +9304,7 @@
         <v>5</v>
       </c>
       <c r="C333" s="14" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="D333" s="19" t="s">
         <v>20</v>
@@ -9321,7 +9318,7 @@
         <v>195</v>
       </c>
       <c r="C334" s="14" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="D334" s="19" t="s">
         <v>20</v>
@@ -9332,10 +9329,10 @@
         <v>334</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C335" s="14" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D335" s="19" t="s">
         <v>20</v>
@@ -9346,10 +9343,10 @@
         <v>335</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C336" s="14" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D336" s="19" t="s">
         <v>20</v>
@@ -9363,7 +9360,7 @@
         <v>196</v>
       </c>
       <c r="C337" s="14" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="D337" s="15" t="s">
         <v>20</v>
@@ -9377,7 +9374,7 @@
         <v>197</v>
       </c>
       <c r="C338" s="14" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D338" s="19" t="s">
         <v>1</v>
@@ -9391,7 +9388,7 @@
         <v>198</v>
       </c>
       <c r="C339" s="14" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="D339" s="19" t="s">
         <v>17</v>
@@ -9402,10 +9399,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C340" s="14" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D340" s="19" t="s">
         <v>1</v>
@@ -9419,7 +9416,7 @@
         <v>199</v>
       </c>
       <c r="C341" s="14" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D341" s="19" t="s">
         <v>1</v>
@@ -9433,7 +9430,7 @@
         <v>200</v>
       </c>
       <c r="C342" s="11" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D342" s="19" t="s">
         <v>0</v>
@@ -9447,7 +9444,7 @@
         <v>201</v>
       </c>
       <c r="C343" s="11" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D343" s="19" t="s">
         <v>1</v>
@@ -9461,7 +9458,7 @@
         <v>202</v>
       </c>
       <c r="C344" s="11" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D344" s="19" t="s">
         <v>0</v>
@@ -9475,7 +9472,7 @@
         <v>203</v>
       </c>
       <c r="C345" s="11" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="D345" s="19" t="s">
         <v>17</v>
@@ -9486,10 +9483,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="11" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C346" s="11" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D346" s="19" t="s">
         <v>17</v>
@@ -9503,7 +9500,7 @@
         <v>204</v>
       </c>
       <c r="C347" s="11" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D347" s="19" t="s">
         <v>0</v>
@@ -9517,7 +9514,7 @@
         <v>205</v>
       </c>
       <c r="C348" s="11" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D348" s="19" t="s">
         <v>0</v>
@@ -9531,7 +9528,7 @@
         <v>206</v>
       </c>
       <c r="C349" s="11" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D349" s="19" t="s">
         <v>0</v>
@@ -9545,7 +9542,7 @@
         <v>207</v>
       </c>
       <c r="C350" s="11" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D350" s="15" t="s">
         <v>1</v>
@@ -9556,10 +9553,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C351" s="11" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D351" s="19" t="s">
         <v>1</v>
@@ -9573,7 +9570,7 @@
         <v>208</v>
       </c>
       <c r="C352" s="11" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D352" s="19" t="s">
         <v>20</v>
@@ -9587,7 +9584,7 @@
         <v>209</v>
       </c>
       <c r="C353" s="11" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D353" s="19" t="s">
         <v>0</v>
@@ -9598,10 +9595,10 @@
         <v>353</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C354" s="11" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D354" s="19" t="s">
         <v>20</v>
@@ -9615,7 +9612,7 @@
         <v>210</v>
       </c>
       <c r="C355" s="11" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D355" s="19" t="s">
         <v>0</v>
@@ -9626,10 +9623,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C356" s="11" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="D356" s="19" t="s">
         <v>1</v>
@@ -9643,7 +9640,7 @@
         <v>211</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="D357" s="15" t="s">
         <v>20</v>
@@ -9657,7 +9654,7 @@
         <v>6</v>
       </c>
       <c r="C358" s="11" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D358" s="34" t="s">
         <v>17</v>
@@ -9671,7 +9668,7 @@
         <v>7</v>
       </c>
       <c r="C359" s="30" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D359" s="30" t="s">
         <v>20</v>
@@ -9682,10 +9679,10 @@
         <v>359</v>
       </c>
       <c r="B360" s="11" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="C360" s="11" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D360" s="19" t="s">
         <v>17</v>
@@ -9696,10 +9693,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="30" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C361" s="30" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D361" s="15" t="s">
         <v>20</v>
@@ -9710,10 +9707,10 @@
         <v>361</v>
       </c>
       <c r="B362" s="30" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C362" s="30" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D362" s="15" t="s">
         <v>17</v>
@@ -9727,7 +9724,7 @@
         <v>212</v>
       </c>
       <c r="C363" s="30" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D363" s="15" t="s">
         <v>20</v>
@@ -9741,7 +9738,7 @@
         <v>213</v>
       </c>
       <c r="C364" s="30" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D364" s="15" t="s">
         <v>0</v>
@@ -9755,7 +9752,7 @@
         <v>214</v>
       </c>
       <c r="C365" s="30" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D365" s="15" t="s">
         <v>0</v>
@@ -9769,7 +9766,7 @@
         <v>215</v>
       </c>
       <c r="C366" s="30" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="D366" s="15" t="s">
         <v>20</v>
@@ -9783,7 +9780,7 @@
         <v>216</v>
       </c>
       <c r="C367" s="30" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D367" s="15" t="s">
         <v>20</v>
@@ -9794,10 +9791,10 @@
         <v>367</v>
       </c>
       <c r="B368" s="11" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="C368" s="30" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D368" s="15" t="s">
         <v>0</v>
@@ -9811,7 +9808,7 @@
         <v>217</v>
       </c>
       <c r="C369" s="30" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D369" s="15" t="s">
         <v>20</v>
@@ -9822,10 +9819,10 @@
         <v>369</v>
       </c>
       <c r="B370" s="30" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C370" s="30" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D370" s="15" t="s">
         <v>17</v>
@@ -9839,7 +9836,7 @@
         <v>8</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="D371" s="15" t="s">
         <v>1</v>
@@ -9853,7 +9850,7 @@
         <v>218</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D372" s="15" t="s">
         <v>0</v>
@@ -9867,7 +9864,7 @@
         <v>219</v>
       </c>
       <c r="C373" s="30" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D373" s="15" t="s">
         <v>1</v>
@@ -9881,7 +9878,7 @@
         <v>220</v>
       </c>
       <c r="C374" s="30" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D374" s="15" t="s">
         <v>0</v>
@@ -9895,7 +9892,7 @@
         <v>221</v>
       </c>
       <c r="C375" s="30" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D375" s="15" t="s">
         <v>1</v>
@@ -9906,10 +9903,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="11" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C376" s="30" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="D376" s="15" t="s">
         <v>0</v>
@@ -9923,7 +9920,7 @@
         <v>222</v>
       </c>
       <c r="C377" s="30" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D377" s="15" t="s">
         <v>20</v>
@@ -9937,7 +9934,7 @@
         <v>223</v>
       </c>
       <c r="C378" s="30" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D378" s="15" t="s">
         <v>17</v>
@@ -9951,7 +9948,7 @@
         <v>224</v>
       </c>
       <c r="C379" s="30" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D379" s="15" t="s">
         <v>20</v>
@@ -9965,7 +9962,7 @@
         <v>9</v>
       </c>
       <c r="C380" s="30" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D380" s="15" t="s">
         <v>0</v>
@@ -9976,10 +9973,10 @@
         <v>380</v>
       </c>
       <c r="B381" s="30" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="C381" s="30" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D381" s="15" t="s">
         <v>17</v>
@@ -9993,7 +9990,7 @@
         <v>225</v>
       </c>
       <c r="C382" s="30" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D382" s="15" t="s">
         <v>1</v>
@@ -10007,7 +10004,7 @@
         <v>226</v>
       </c>
       <c r="C383" s="30" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D383" s="15" t="s">
         <v>0</v>
@@ -10021,7 +10018,7 @@
         <v>227</v>
       </c>
       <c r="C384" s="30" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D384" s="15" t="s">
         <v>0</v>
@@ -10035,7 +10032,7 @@
         <v>228</v>
       </c>
       <c r="C385" s="30" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D385" s="15" t="s">
         <v>1</v>
@@ -10049,7 +10046,7 @@
         <v>229</v>
       </c>
       <c r="C386" s="11" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D386" s="15" t="s">
         <v>17</v>
@@ -10063,7 +10060,7 @@
         <v>230</v>
       </c>
       <c r="C387" s="11" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="D387" s="15" t="s">
         <v>20</v>
@@ -10077,7 +10074,7 @@
         <v>231</v>
       </c>
       <c r="C388" s="11" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D388" s="15" t="s">
         <v>17</v>
@@ -10088,10 +10085,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="11" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="C389" s="11" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="D389" s="19" t="s">
         <v>1</v>
@@ -10102,10 +10099,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="11" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="C390" s="11" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D390" s="19" t="s">
         <v>1</v>
@@ -10119,7 +10116,7 @@
         <v>232</v>
       </c>
       <c r="C391" s="11" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="D391" s="19" t="s">
         <v>1</v>

--- a/data/Ngan-Hang-Cau-Hoi.xlsx
+++ b/data/Ngan-Hang-Cau-Hoi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9f54d0bdb7235122/Documents/My App/trac-nghiem-luat-dau-thau/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6669B6E6-5ED4-4F8F-B91B-022AC5ED8FA7}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C69DD5D-4D78-4F88-9C95-3657EB0C4F3D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0822E189-CD53-41B9-B216-EFA7EF505EBC}"/>
   </bookViews>
@@ -2243,36 +2243,8 @@
 đấu thầu?</t>
   </si>
   <si>
-    <t>A. Chủ đầu tư quyết định xử lý tình huống sau khi có ý kiến của người có thẩm quyền
-B. Người có thẩm quyền quyết định xử lý tình huống sau khi có ý kiến của Tổ chuyên gia
-C. Người có thẩm quyền quyết định xử lý tình huống sau khi có ý kiến của chủ đầu tư
-D. Người có thẩm quyền quyết định xử lý tình huống sau khi có ý kiến của chủ đầu tư và Tổ chuyên
-gia</t>
-  </si>
-  <si>
     <t>Trường hợp một hoặc một số thành viên liên danh vi phạm hợp đồng, không còn năng lực để tiếp tục thực hiện hợp đồng, làm ảnh
 hưởng nghiêm trọng đến tiến độ, chất lượng, hiệu quả của gói thầu thì việc đánh giá uy tín của nhà thầu trong việc thực hiện hợp đồng được xử lý như nào?</t>
-  </si>
-  <si>
-    <t>A. Nhà thầu liên danh vi phạm hợp đồng bị coi là không hoàn thành hợp đồng và bị chủ đầu tư đăng tải thông tin nhà thầu liên danh vi phạm hợp đồng trên Hệ thống mạng đấu thầu quốc gia
-B.  Chỉ một hoặc một số thành viên liên danh vi phạm hợp đồng bị coi là không hoàn thành hợp đồng và bị chủ đầu tư đăng tải thông tin thành viên liên danh vi phạm hợp đồng trên Hệ thống mạng đấu thầu quốc gia
-C. Chỉ một hoặc một số thành viên liên danh vi phạm hợp đồng bị coi là không hoàn thành hợp đồng và bị bên mời thầu đăng tải thông tin thành viên liên danh vi phạm hợp đồng trên Hệ thống mạng đấu thầu quốc gia
-D. Nhà thầu liên danh vi phạm hợp đồng bị coi là không hoàn thành hợp đồng và bị bên mời thầu
-đăng tải thông tin nhà thầu liên danh vi phạm hợp đồng trên Hệ thống mạng đấu thầu quốc gia</t>
-  </si>
-  <si>
-    <t>A. Bằng giá trị ghi trong hợp đồng trừ đi giá trị của phần công việc đã thực hiện, được nghiệm thu trước đó
-B. Bằng giá trị ghi trong hợp đồng được cập nhật giá tại thời điểm áp dụng hình thức chỉ định thầu trừ đi giá trị của phần công việc đã thực hiện, được nghiệm thu trước đó
-C. Bằng giá trị của phần công việc còn lại được cập nhật giá tại thời điểm áp dụng hình thức chỉ định thầu
-D. Bằng giá trị ghi trong hợp đồng trừ đi giá trị của phần công việc đã thực hiện trước đó theo dự
-toán được duyệt</t>
-  </si>
-  <si>
-    <t>A. Các thành viên liên danh thỏa thuận, điều chỉnh về phạm vi công việc, tiến độ được rút ngắn và không phải thông báo cho chủ đầu tư
-B. Các thành viên liên danh thỏa thuận, điều chỉnh về phạm vi công việc, tiến độ được rút ngắn và thông báo cho chủ đầu tư
-C. Phải được người có thẩm quyền cho phép chủ đầu tư và nhà thầu thỏa thuận, điều chỉnh phạm vi công việc giữa các thành viên liên danh phù hợp với tiến độ hoặc tiến độ được rút ngắn
-D. Chủ đầu tư và nhà thầu được thỏa thuận điều chỉnh phạm vi công việc giữa các thành viên liên
-danh phù hợp với tiến độ hoặc tiến độ được rút ngắn</t>
   </si>
   <si>
     <t>Trường hợp nhà thầu có nhân sự (ký kết hợp đồng lao động với nhà thầu tại thời điểm nhân sự thực hiện hành vi vi phạm) bị cơ quan điều tra kết luận có hành vi vi phạm quy định về đấu thầu gây hậu quả nghiêm trọng theo quy định pháp luật về hình sự nhằm mục đích cho nhà thầu trúng thầu nhưng nhân sự của nhà thầu chưa bị
@@ -2536,13 +2508,6 @@
 D. Các đáp án trên đều sai</t>
   </si>
   <si>
-    <t>A. Chịu trách nhiệm về tính chính xác của các thông tin kê khai trên webform và file tài liệu đính
-kèm
-B. Chỉ nộp một bộ E-HSDT đối với một E-TBMT
-C. Chỉ được rút, sửa đổi, nộp lại E-HSDT trước thời điểm đóng thầu
-D. Cả 3 đáp án trên đều đúng</t>
-  </si>
-  <si>
     <t>A. Khi Tổ chuyên gia phát hiện E-HSDT bị lỗi kỹ thuật không mở được
 B. Khi Hệ thống mạng đấu thầu quốc gia gặp sự cố phải tự động gia hạn
 C. Khi E-HSMT được sửa đổi
@@ -2601,20 +2566,6 @@
 nội dung do Hệ thống mạng đấu thầu quốc gia đánh giá "không đạt" thì Tổ chuyên gia không thể sửa đổi kết quả đánh giá từ "không đạt" thành "đạt". Phương án nào sau đây là đúng?</t>
   </si>
   <si>
-    <t>A. Tư cách hợp lệ, nhà thầu không có nhân sự bị tòa án kết án có hành vi vi phạm quy định về đấu thầu gây hậu quả nghiêm trọng, trạng thái bị tạm ngừng, chấm dứt tham gia Hệ thống mạng đấu thầu quốc gia, doanh thu bình quân hằng năm.
-B. Tư cách hợp lệ, bảo đảm dự thầu, thực hiện nghĩa vụ kê khai thuế và nộp thuế, kết quả hoạt động tài chính, doanh thu bình quân hằng năm
-C. Tư cách hợp lệ, nhà thầu không có nhân sự bị tòa án kết án có hành vi vi phạm quy định về đấu thầu gây hậu quả nghiêm trọng, trạng thái bị tạm ngừng, chấm dứt tham gia Hệ thống mạng đấu thầu quốc gia, thực hiện nghĩa vụ kê khai thuế và nộp thuế, kết quả hoạt động tài chính, doanh thu bình quân hằng năm
-D. Tư cách hợp lệ, nhà thầu không có nhân sự bị tòa án kết án có hành vi vi phạm quy định về đấu thầu gây hậu quả nghiêm trọng, lịch sử không hoàn thành hợp đồng do lỗi của nhà thầu, thực hiện
-nghĩa vụ kê khai thuế và nộp thuế, kết quả hoạt động tài chính, doanh thu bình quân hằng năm</t>
-  </si>
-  <si>
-    <t>A. Gói thầu mua sắm hàng hóa áp dụng phương thức một giai đoạn một túi hồ sơ, sử dụng phương pháp “giá thấp nhất” và các nhà thầu, E-HSDT đều không có bất kỳ ưu đãi nào
-B. Gói thầu dịch vụ phi tư vấn áp dụng phương thức một giai đoạn một túi hồ sơ, sử dụng phương pháp “giá đánh giá” và các nhà thầu, E-HSDT chào ưu đãi như nhau
-C. Gói thầu xây lắp áp dụng phương thức một giai đoạn một túi hồ sơ, sử dụng phương pháp “giá thấp nhất” và các nhà thầu, E-HSDT đều không có bất kỳ ưu đãi nào
-D. Gói thầu máy đặt, máy mượn áp dụng phương thức một giai đoạn một túi hồ sơ, sử dụng
-phương pháp “giá thấp nhất” và các nhà thầu, E-HSDT chào ưu đãi như nhau</t>
-  </si>
-  <si>
     <t>Chủ đầu tư yêu cầu gia hạn hiệu lực hồ sơ dự thầu, bảo đảm dự thầu trong trường hợp nào
 sau đây?</t>
   </si>
@@ -2635,13 +2586,6 @@
 D. Phương án A và B đều đúng</t>
   </si>
   <si>
-    <t>A. Thời điểm bắt đầu và kết thúc phải trong giờ hành chính.
-B. Thời điểm bắt đầu không bắt buộc trong giờ hành chính nhưng kết thúc phải trong giờ hành
-chính.
-C. Thời điểm bắt đầu và kết thúc không bắt buộc trong giờ hành chính.
-D. Tất cả phương án trên đều sai</t>
-  </si>
-  <si>
     <t>Đối với gói thầu chào giá trực tuyến rút gọn, nhà thầu xác nhận về việc chấp thuận được
 trao hợp đồng trong thời gian tối đa bao lâu kể từ ngày chủ đầu tư mời nhà thầu xác nhận trên
 Hệ thống mạng đấu thầu quốc gia?</t>
@@ -2684,10 +2628,6 @@
 nhiêu %?</t>
   </si>
   <si>
-    <t>A.80% B.85% C.90%
-D.95%</t>
-  </si>
-  <si>
     <t>A. 5% giá gói thầu
 B. 10% giá gói thầu
 C. 1-3% giá gói thầu
@@ -2698,24 +2638,10 @@
 thế nào?</t>
   </si>
   <si>
-    <t>A. Đề  xuất về tài chính của nhà thầu sẽ bị đánh giá là không đạt
-B. Nhà thầu sẽ bị loại và bị khóa tài khoản trên Hệ thống mạng đấu thầu quốc gia trong vòng 06
-tháng
-C. Hồ sơ dự thầu của nhà thầu sẽ tiếp tục được đánh giá về tài chính căn cứ theo hồ sơ dự thầu đã nộp trước thời điểm đóng thầu
-D. Phương án A và B đều đúng</t>
-  </si>
-  <si>
     <t>A. 100 triệu đồng
 B. 300 triệu đồng
 C. 500 triệu đồng
 D. 01 tỷ đồng</t>
-  </si>
-  <si>
-    <t>A. Đơn vị mua sắm tập trung và các nhà thầu trúng thầu (trong trường hợp không ký thỏa thuận
-khung)
-B. Đơn vị có nhu cầu mua sắm với các nhà thầu trúng thầu (trong trường hợp đơn vị mua sắm tập trung ký thỏa thuận khung với nhà thầu trúng thầu)
-C. Phương án A và B đều đúng
-D. Phương án A và B đều sai</t>
   </si>
   <si>
     <t>A. Gói thầu mua sắm hàng hóa, dịch vụ thuộc dự toán mua sắm có giá gói thầu không quá 500 triệu đồng; gói thầu mua sắm hàng hóa, dịch vụ thuộc dự án có giá gói thầu không quá 01 tỷ đồng
@@ -2810,13 +2736,6 @@
 D. Tất cả các gói thầu áp dụng đấu thầu qua mạng và không qua mạng</t>
   </si>
   <si>
-    <t>A. Đính kèm bản scan báo cáo đánh giá E-HSDT (có chữ ký của tất cả thành viên trong tổ chuyên
-gia)
-B. Đính kèm bản scan báo cáo đánh giá E-HSDT (không cần có chữ ký của tất cả thành viên trong tổ chuyên gia)
-C. Đính kèm bản scan báo cáo đánh giá E-HSDT (chỉ cần chữ ký của tổ trưởng tổ chuyên gia)
-D. Tất cả các phương án đều sai</t>
-  </si>
-  <si>
     <t>Gói thầu hàng hóa có giá gói thầu 02 tỷ đồng thực hiện chào giá trực tuyến theo quy trình rút gọn, trường hợp chủ đầu tư đăng tải thông báo mời thầu vào 11h00 ngày Thứ 2 (15/9/2025), thời điểm nào sau đây là thời
 điểm kết thúc chào giá trực tuyến sớm nhất?</t>
   </si>
@@ -2994,13 +2913,6 @@
 B. Không vượt giá gói thầu, không vượt thời gian thực hiện gói thầu ghi trong hợp đồng và phương pháp, công thức, hạng mục và các nội dung cần thiết để điều chỉnh đã quy định trong hợp đồng
 C. Không vượt thời gian thực hiện gói thầu ghi trong hợp đồng nhưng có thể vượt giá gói thầu
 D. Khi thay đổi thời gian thực hiện hợp đồng nhưng không làm vượt thời gian thực hiện dự án hoặc vượt giá gói thầu (bao gồm dự phòng) được duyệt nhưng không làm vượt tổng mức đầu tư</t>
-  </si>
-  <si>
-    <t>A. Hợp đồng theo đơn giá cố định áp dụng cho gói thầu có thời gian thực hiện dài, hợp đồng theo đơn giá điều chỉnh áp dụng cho gói thầu có thời gian thực hiện ngắn
-B. Đơn giá trong hợp đồng đơn giá cố định không thay đổi, còn đơn giá trong hợp đồng đơn giá điều chỉnh có thể thay đổi
-C. Hợp đồng theo đơn giá cố định không có chi phí dự phòng, còn hợp đồng theo đơn giá điều chỉnh có chi phí dự phòng
-D. Hợp đồng theo đơn giá cố định chỉ áp dụng cho gói thầu dịch vụ tư vấn, hợp đồng theo đơn giá điều chỉnh
-áp dụng cho gói thầu xây lắp</t>
   </si>
   <si>
     <t>So sánh hai tình huống sửa đổi hợp đồng:
@@ -3678,13 +3590,6 @@
 D. Tất cả các phương án trên đều đúng</t>
   </si>
   <si>
-    <t>A. Nhà thầu liên danh trong đó có thành viên liên danh là nhà thầu Nhật Bản và thành viên này đảm nhận từ 50% trở lên giá trị công việc của gói thầu
-B. Nhà thầu liên danh trong đó có thành viên liên danh là nhà thầu nội khối và thành viên này đảm nhận từ 25% trở lên giá trị công việc của gói thầu
-C. Nhà thầu liên danh trong đó có thành viên liên danh là nhà thầu Hoa Kỳ và thành viên này đảm nhận từ 50% trở
-lên giá trị công việc của gói thầu
-D. Nhà thầu liên danh trong đó có thành viên liên danh là nhà thầu nội khối và thành viên này đảm nhận từ 40% trở lên giá trị công việc của gói thầu</t>
-  </si>
-  <si>
     <t>A. Không ghi rõ số lượng gói thầu
 B.  Không được chia nhỏ gói thầu để tránh áp dụng Nghị định này
 C.  Phải ghi toàn bộ phương thức lựa chọn nhà thầu là đấu thầu qua mạng
@@ -3830,6 +3735,90 @@
 B. Tổ chuyên gia căn cứ theo cataloge, đề xuất kỹ thuật kèm theo để làm cơ sở đánh giá
 C. Hồ sơ dự thầu của nhà thầu không được xem xét, đánh giá
 D. Tiếp tục đánh giá hồ sơ dự thầu, trường hơp nhà thầu trúng thầu thì yêu cầu nhà thầu bổ sung, làm rõ các thông tin này</t>
+  </si>
+  <si>
+    <t>A. Nhà thầu liên danh vi phạm hợp đồng bị coi là không hoàn thành hợp đồng và bị chủ đầu tư đăng tải thông tin nhà thầu liên danh vi phạm hợp đồng trên Hệ thống mạng đấu thầu quốc gia
+B.  Chỉ một hoặc một số thành viên liên danh vi phạm hợp đồng bị coi là không hoàn thành hợp đồng và bị chủ đầu tư đăng tải thông tin thành viên liên danh vi phạm hợp đồng trên Hệ thống mạng đấu thầu quốc gia
+C. Chỉ một hoặc một số thành viên liên danh vi phạm hợp đồng bị coi là không hoàn thành hợp đồng và bị bên mời thầu đăng tải thông tin thành viên liên danh vi phạm hợp đồng trên Hệ thống mạng đấu thầu quốc gia
+D. Nhà thầu liên danh vi phạm hợp đồng bị coi là không hoàn thành hợp đồng và bị bên mời thầu đăng tải thông tin nhà thầu liên danh vi phạm hợp đồng trên Hệ thống mạng đấu thầu quốc gia</t>
+  </si>
+  <si>
+    <t>A. Bằng giá trị ghi trong hợp đồng trừ đi giá trị của phần công việc đã thực hiện, được nghiệm thu trước đó
+B. Bằng giá trị ghi trong hợp đồng được cập nhật giá tại thời điểm áp dụng hình thức chỉ định thầu trừ đi giá trị của phần công việc đã thực hiện, được nghiệm thu trước đó
+C. Bằng giá trị của phần công việc còn lại được cập nhật giá tại thời điểm áp dụng hình thức chỉ định thầu
+D. Bằng giá trị ghi trong hợp đồng trừ đi giá trị của phần công việc đã thực hiện trước đó theo dự toán được duyệt</t>
+  </si>
+  <si>
+    <t>A. Chủ đầu tư quyết định xử lý tình huống sau khi có ý kiến của người có thẩm quyền
+B. Người có thẩm quyền quyết định xử lý tình huống sau khi có ý kiến của Tổ chuyên gia
+C. Người có thẩm quyền quyết định xử lý tình huống sau khi có ý kiến của chủ đầu tư
+D. Người có thẩm quyền quyết định xử lý tình huống sau khi có ý kiến của chủ đầu tư và Tổ chuyên gia</t>
+  </si>
+  <si>
+    <t>A. Các thành viên liên danh thỏa thuận, điều chỉnh về phạm vi công việc, tiến độ được rút ngắn và không phải thông báo cho chủ đầu tư
+B. Các thành viên liên danh thỏa thuận, điều chỉnh về phạm vi công việc, tiến độ được rút ngắn và thông báo cho chủ đầu tư
+C. Phải được người có thẩm quyền cho phép chủ đầu tư và nhà thầu thỏa thuận, điều chỉnh phạm vi công việc giữa các thành viên liên danh phù hợp với tiến độ hoặc tiến độ được rút ngắn
+D. Chủ đầu tư và nhà thầu được thỏa thuận điều chỉnh phạm vi công việc giữa các thành viên liên danh phù hợp với tiến độ hoặc tiến độ được rút ngắn</t>
+  </si>
+  <si>
+    <t>A. Chịu trách nhiệm về tính chính xác của các thông tin kê khai trên webform và file tài liệu đính kèm
+B. Chỉ nộp một bộ E-HSDT đối với một E-TBMT
+C. Chỉ được rút, sửa đổi, nộp lại E-HSDT trước thời điểm đóng thầu
+D. Cả 3 đáp án trên đều đúng</t>
+  </si>
+  <si>
+    <t>A. Tư cách hợp lệ, nhà thầu không có nhân sự bị tòa án kết án có hành vi vi phạm quy định về đấu thầu gây hậu quả nghiêm trọng, trạng thái bị tạm ngừng, chấm dứt tham gia Hệ thống mạng đấu thầu quốc gia, doanh thu bình quân hằng năm.
+B. Tư cách hợp lệ, bảo đảm dự thầu, thực hiện nghĩa vụ kê khai thuế và nộp thuế, kết quả hoạt động tài chính, doanh thu bình quân hằng năm
+C. Tư cách hợp lệ, nhà thầu không có nhân sự bị tòa án kết án có hành vi vi phạm quy định về đấu thầu gây hậu quả nghiêm trọng, trạng thái bị tạm ngừng, chấm dứt tham gia Hệ thống mạng đấu thầu quốc gia, thực hiện nghĩa vụ kê khai thuế và nộp thuế, kết quả hoạt động tài chính, doanh thu bình quân hằng năm
+D. Tư cách hợp lệ, nhà thầu không có nhân sự bị tòa án kết án có hành vi vi phạm quy định về đấu thầu gây hậu quả nghiêm trọng, lịch sử không hoàn thành hợp đồng do lỗi của nhà thầu, thực hiện nghĩa vụ kê khai thuế và nộp thuế, kết quả hoạt động tài chính, doanh thu bình quân hằng năm</t>
+  </si>
+  <si>
+    <t>A. Gói thầu mua sắm hàng hóa áp dụng phương thức một giai đoạn một túi hồ sơ, sử dụng phương pháp “giá thấp nhất” và các nhà thầu, E-HSDT đều không có bất kỳ ưu đãi nào
+B. Gói thầu dịch vụ phi tư vấn áp dụng phương thức một giai đoạn một túi hồ sơ, sử dụng phương pháp “giá đánh giá” và các nhà thầu, E-HSDT chào ưu đãi như nhau
+C. Gói thầu xây lắp áp dụng phương thức một giai đoạn một túi hồ sơ, sử dụng phương pháp “giá thấp nhất” và các nhà thầu, E-HSDT đều không có bất kỳ ưu đãi nào
+D. Gói thầu máy đặt, máy mượn áp dụng phương thức một giai đoạn một túi hồ sơ, sử dụng phương pháp “giá thấp nhất” và các nhà thầu, E-HSDT chào ưu đãi như nhau</t>
+  </si>
+  <si>
+    <t>A. Thời điểm bắt đầu và kết thúc phải trong giờ hành chính.
+B. Thời điểm bắt đầu không bắt buộc trong giờ hành chính nhưng kết thúc phải trong giờ hành chính.
+C. Thời điểm bắt đầu và kết thúc không bắt buộc trong giờ hành chính.
+D. Tất cả phương án trên đều sai</t>
+  </si>
+  <si>
+    <t>A.80%
+B.85%
+C.90%
+D.95%</t>
+  </si>
+  <si>
+    <t>A. Đề  xuất về tài chính của nhà thầu sẽ bị đánh giá là không đạt
+B. Nhà thầu sẽ bị loại và bị khóa tài khoản trên Hệ thống mạng đấu thầu quốc gia trong vòng 06 tháng
+C. Hồ sơ dự thầu của nhà thầu sẽ tiếp tục được đánh giá về tài chính căn cứ theo hồ sơ dự thầu đã nộp trước thời điểm đóng thầu
+D. Phương án A và B đều đúng</t>
+  </si>
+  <si>
+    <t>A. Đơn vị mua sắm tập trung và các nhà thầu trúng thầu (trong trường hợp không ký thỏa thuận khung)
+B. Đơn vị có nhu cầu mua sắm với các nhà thầu trúng thầu (trong trường hợp đơn vị mua sắm tập trung ký thỏa thuận khung với nhà thầu trúng thầu)
+C. Phương án A và B đều đúng
+D. Phương án A và B đều sai</t>
+  </si>
+  <si>
+    <t>A. Đính kèm bản scan báo cáo đánh giá E-HSDT (có chữ ký của tất cả thành viên trong tổ chuyên gia)
+B. Đính kèm bản scan báo cáo đánh giá E-HSDT (không cần có chữ ký của tất cả thành viên trong tổ chuyên gia)
+C. Đính kèm bản scan báo cáo đánh giá E-HSDT (chỉ cần chữ ký của tổ trưởng tổ chuyên gia)
+D. Tất cả các phương án đều sai</t>
+  </si>
+  <si>
+    <t>A. Hợp đồng theo đơn giá cố định áp dụng cho gói thầu có thời gian thực hiện dài, hợp đồng theo đơn giá điều chỉnh áp dụng cho gói thầu có thời gian thực hiện ngắn
+B. Đơn giá trong hợp đồng đơn giá cố định không thay đổi, còn đơn giá trong hợp đồng đơn giá điều chỉnh có thể thay đổi
+C. Hợp đồng theo đơn giá cố định không có chi phí dự phòng, còn hợp đồng theo đơn giá điều chỉnh có chi phí dự phòng
+D. Hợp đồng theo đơn giá cố định chỉ áp dụng cho gói thầu dịch vụ tư vấn, hợp đồng theo đơn giá điều chỉnh áp dụng cho gói thầu xây lắp</t>
+  </si>
+  <si>
+    <t>A. Nhà thầu liên danh trong đó có thành viên liên danh là nhà thầu Nhật Bản và thành viên này đảm nhận từ 50% trở lên giá trị công việc của gói thầu
+B. Nhà thầu liên danh trong đó có thành viên liên danh là nhà thầu nội khối và thành viên này đảm nhận từ 25% trở lên giá trị công việc của gói thầu
+C. Nhà thầu liên danh trong đó có thành viên liên danh là nhà thầu Hoa Kỳ và thành viên này đảm nhận từ 50% trở lên giá trị công việc của gói thầu
+D. Nhà thầu liên danh trong đó có thành viên liên danh là nhà thầu nội khối và thành viên này đảm nhận từ 40% trở lên giá trị công việc của gói thầu</t>
   </si>
 </sst>
 </file>
@@ -4185,66 +4174,6 @@
               </a:lnTo>
               <a:lnTo>
                 <a:pt x="96011" y="0"/>
-              </a:lnTo>
-              <a:close/>
-            </a:path>
-          </a:pathLst>
-        </a:custGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFF00">
-            <a:alpha val="50000"/>
-          </a:srgbClr>
-        </a:solidFill>
-      </xdr:spPr>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>7482458</xdr:colOff>
-      <xdr:row>374</xdr:row>
-      <xdr:rowOff>490854</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="105410" cy="175260"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="Shape 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72FA2F2F-3E30-499B-A18A-D2F82EB7C1DE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="11292458" y="2700654"/>
-          <a:ext cx="105410" cy="175260"/>
-        </a:xfrm>
-        <a:custGeom>
-          <a:avLst/>
-          <a:gdLst/>
-          <a:ahLst/>
-          <a:cxnLst/>
-          <a:rect l="0" t="0" r="0" b="0"/>
-          <a:pathLst>
-            <a:path w="105410" h="175260">
-              <a:moveTo>
-                <a:pt x="105155" y="0"/>
-              </a:moveTo>
-              <a:lnTo>
-                <a:pt x="0" y="0"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="0" y="175260"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="105155" y="175260"/>
-              </a:lnTo>
-              <a:lnTo>
-                <a:pt x="105155" y="0"/>
               </a:lnTo>
               <a:close/>
             </a:path>
@@ -5720,7 +5649,7 @@
         <v>341</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>772</v>
+        <v>758</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>1</v>
@@ -5776,7 +5705,7 @@
         <v>58</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>780</v>
+        <v>766</v>
       </c>
       <c r="D81" s="19" t="s">
         <v>1</v>
@@ -6014,7 +5943,7 @@
         <v>372</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>783</v>
+        <v>769</v>
       </c>
       <c r="D98" s="20" t="s">
         <v>20</v>
@@ -6042,7 +5971,7 @@
         <v>4</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>773</v>
+        <v>759</v>
       </c>
       <c r="D100" s="26" t="s">
         <v>1</v>
@@ -6056,7 +5985,7 @@
         <v>66</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>779</v>
+        <v>765</v>
       </c>
       <c r="D101" s="21" t="s">
         <v>17</v>
@@ -6140,7 +6069,7 @@
         <v>69</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>774</v>
+        <v>760</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>20</v>
@@ -6224,7 +6153,7 @@
         <v>389</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>775</v>
+        <v>761</v>
       </c>
       <c r="D113" s="19" t="s">
         <v>1</v>
@@ -6378,7 +6307,7 @@
         <v>405</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="D124" s="19" t="s">
         <v>0</v>
@@ -6392,7 +6321,7 @@
         <v>78</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>781</v>
+        <v>767</v>
       </c>
       <c r="D125" s="21" t="s">
         <v>1</v>
@@ -6420,7 +6349,7 @@
         <v>79</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>782</v>
+        <v>768</v>
       </c>
       <c r="D127" s="21" t="s">
         <v>0</v>
@@ -6602,7 +6531,7 @@
         <v>89</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>768</v>
+        <v>754</v>
       </c>
       <c r="D140" s="18" t="s">
         <v>17</v>
@@ -6672,7 +6601,7 @@
         <v>93</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>769</v>
+        <v>755</v>
       </c>
       <c r="D145" s="19" t="s">
         <v>17</v>
@@ -6686,7 +6615,7 @@
         <v>428</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="D146" s="19" t="s">
         <v>20</v>
@@ -6938,7 +6867,7 @@
         <v>456</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>778</v>
+        <v>764</v>
       </c>
       <c r="D164" s="24" t="s">
         <v>1</v>
@@ -7364,7 +7293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A195" s="7">
         <v>194</v>
       </c>
@@ -7372,27 +7301,27 @@
         <v>504</v>
       </c>
       <c r="C195" s="14" t="s">
-        <v>505</v>
+        <v>772</v>
       </c>
       <c r="D195" s="19" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A196" s="7">
         <v>195</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C196" s="14" t="s">
-        <v>507</v>
+        <v>770</v>
       </c>
       <c r="D196" s="20" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="197" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A197" s="7">
         <v>196</v>
       </c>
@@ -7400,13 +7329,13 @@
         <v>112</v>
       </c>
       <c r="C197" s="14" t="s">
-        <v>508</v>
+        <v>771</v>
       </c>
       <c r="D197" s="19" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A198" s="10">
         <v>197</v>
       </c>
@@ -7414,7 +7343,7 @@
         <v>113</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>509</v>
+        <v>773</v>
       </c>
       <c r="D198" s="18" t="s">
         <v>0</v>
@@ -7425,10 +7354,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C199" s="14" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="D199" s="18" t="s">
         <v>0</v>
@@ -7439,10 +7368,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D200" s="19" t="s">
         <v>1</v>
@@ -7453,10 +7382,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C201" s="14" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="D201" s="24" t="s">
         <v>1</v>
@@ -7470,7 +7399,7 @@
         <v>114</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D202" s="23" t="s">
         <v>20</v>
@@ -7484,7 +7413,7 @@
         <v>115</v>
       </c>
       <c r="C203" s="14" t="s">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="D203" s="24" t="s">
         <v>17</v>
@@ -7498,7 +7427,7 @@
         <v>116</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="D204" s="24" t="s">
         <v>20</v>
@@ -7509,10 +7438,10 @@
         <v>204</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C205" s="14" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="D205" s="18" t="s">
         <v>0</v>
@@ -7523,10 +7452,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C206" s="14" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D206" s="18" t="s">
         <v>1</v>
@@ -7540,7 +7469,7 @@
         <v>117</v>
       </c>
       <c r="C207" s="14" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D207" s="19" t="s">
         <v>20</v>
@@ -7551,10 +7480,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D208" s="18" t="s">
         <v>1</v>
@@ -7565,10 +7494,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C209" s="14" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D209" s="18" t="s">
         <v>1</v>
@@ -7579,10 +7508,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="D210" s="18" t="s">
         <v>0</v>
@@ -7593,10 +7522,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C211" s="14" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D211" s="32" t="s">
         <v>17</v>
@@ -7607,10 +7536,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="C212" s="14" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D212" s="21" t="s">
         <v>0</v>
@@ -7621,10 +7550,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C213" s="14" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D213" s="32" t="s">
         <v>20</v>
@@ -7638,7 +7567,7 @@
         <v>118</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="D214" s="21" t="s">
         <v>0</v>
@@ -7652,7 +7581,7 @@
         <v>119</v>
       </c>
       <c r="C215" s="14" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D215" s="15" t="s">
         <v>20</v>
@@ -7663,10 +7592,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C216" s="14" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D216" s="19" t="s">
         <v>20</v>
@@ -7680,7 +7609,7 @@
         <v>120</v>
       </c>
       <c r="C217" s="14" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D217" s="18" t="s">
         <v>0</v>
@@ -7694,7 +7623,7 @@
         <v>121</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D218" s="20" t="s">
         <v>20</v>
@@ -7705,10 +7634,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C219" s="14" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D219" s="20" t="s">
         <v>17</v>
@@ -7719,10 +7648,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="11" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D220" s="19" t="s">
         <v>20</v>
@@ -7736,7 +7665,7 @@
         <v>122</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D221" s="18" t="s">
         <v>17</v>
@@ -7750,7 +7679,7 @@
         <v>123</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D222" s="18" t="s">
         <v>0</v>
@@ -7764,7 +7693,7 @@
         <v>124</v>
       </c>
       <c r="C223" s="14" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D223" s="18" t="s">
         <v>0</v>
@@ -7778,7 +7707,7 @@
         <v>125</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D224" s="18" t="s">
         <v>0</v>
@@ -7792,7 +7721,7 @@
         <v>126</v>
       </c>
       <c r="C225" s="14" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D225" s="18" t="s">
         <v>0</v>
@@ -7803,10 +7732,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="11" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D226" s="18" t="s">
         <v>1</v>
@@ -7820,7 +7749,7 @@
         <v>127</v>
       </c>
       <c r="C227" s="14" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="D227" s="20" t="s">
         <v>17</v>
@@ -7834,7 +7763,7 @@
         <v>128</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="D228" s="18" t="s">
         <v>0</v>
@@ -7845,10 +7774,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="11" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C229" s="14" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="D229" s="20" t="s">
         <v>20</v>
@@ -7862,7 +7791,7 @@
         <v>129</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="D230" s="20" t="s">
         <v>20</v>
@@ -7876,13 +7805,13 @@
         <v>130</v>
       </c>
       <c r="C231" s="14" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="D231" s="19" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A232" s="4">
         <v>231</v>
       </c>
@@ -7890,7 +7819,7 @@
         <v>131</v>
       </c>
       <c r="C232" s="14" t="s">
-        <v>558</v>
+        <v>774</v>
       </c>
       <c r="D232" s="19" t="s">
         <v>0</v>
@@ -7904,7 +7833,7 @@
         <v>132</v>
       </c>
       <c r="C233" s="14" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="D233" s="20" t="s">
         <v>20</v>
@@ -7918,7 +7847,7 @@
         <v>133</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="D234" s="18" t="s">
         <v>0</v>
@@ -7929,10 +7858,10 @@
         <v>234</v>
       </c>
       <c r="B235" s="11" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="C235" s="14" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="D235" s="20" t="s">
         <v>17</v>
@@ -7946,7 +7875,7 @@
         <v>134</v>
       </c>
       <c r="C236" s="11" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="D236" s="20" t="s">
         <v>0</v>
@@ -7957,10 +7886,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="16" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="C237" s="14" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>0</v>
@@ -7971,10 +7900,10 @@
         <v>237</v>
       </c>
       <c r="B238" s="11" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="D238" s="18" t="s">
         <v>20</v>
@@ -7988,27 +7917,27 @@
         <v>135</v>
       </c>
       <c r="C239" s="14" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A240" s="4">
         <v>239</v>
       </c>
       <c r="B240" s="11" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="C240" s="14" t="s">
-        <v>570</v>
+        <v>775</v>
       </c>
       <c r="D240" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A241" s="4">
         <v>240</v>
       </c>
@@ -8016,7 +7945,7 @@
         <v>136</v>
       </c>
       <c r="C241" s="14" t="s">
-        <v>571</v>
+        <v>776</v>
       </c>
       <c r="D241" s="21" t="s">
         <v>1</v>
@@ -8027,10 +7956,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="C242" s="14" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="D242" s="33" t="s">
         <v>0</v>
@@ -8041,16 +7970,16 @@
         <v>242</v>
       </c>
       <c r="B243" s="11" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="C243" s="25" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="D243" s="20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="244" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A244" s="10">
         <v>243</v>
       </c>
@@ -8058,7 +7987,7 @@
         <v>137</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>576</v>
+        <v>777</v>
       </c>
       <c r="D244" s="18" t="s">
         <v>1</v>
@@ -8069,10 +7998,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="C245" s="14" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="D245" s="18" t="s">
         <v>17</v>
@@ -8083,10 +8012,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="11" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="D246" s="18" t="s">
         <v>17</v>
@@ -8097,10 +8026,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C247" s="14" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="D247" s="18" t="s">
         <v>1</v>
@@ -8114,21 +8043,21 @@
         <v>138</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="D248" s="18" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="249" spans="1:4" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A249" s="4">
         <v>248</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="C249" s="14" t="s">
-        <v>585</v>
+        <v>778</v>
       </c>
       <c r="D249" s="18" t="s">
         <v>20</v>
@@ -8142,21 +8071,21 @@
         <v>139</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="D250" s="18" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A251" s="4">
         <v>250</v>
       </c>
       <c r="B251" s="11" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="C251" s="14" t="s">
-        <v>588</v>
+        <v>779</v>
       </c>
       <c r="D251" s="19" t="s">
         <v>20</v>
@@ -8170,13 +8099,13 @@
         <v>140</v>
       </c>
       <c r="C252" s="14" t="s">
-        <v>589</v>
+        <v>579</v>
       </c>
       <c r="D252" s="20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="253" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A253" s="4">
         <v>252</v>
       </c>
@@ -8184,7 +8113,7 @@
         <v>141</v>
       </c>
       <c r="C253" s="14" t="s">
-        <v>590</v>
+        <v>780</v>
       </c>
       <c r="D253" s="20" t="s">
         <v>20</v>
@@ -8198,7 +8127,7 @@
         <v>142</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="D254" s="20" t="s">
         <v>1</v>
@@ -8209,10 +8138,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>593</v>
+        <v>582</v>
       </c>
       <c r="D255" s="18" t="s">
         <v>20</v>
@@ -8223,10 +8152,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="11" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="C256" s="14" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="D256" s="18" t="s">
         <v>17</v>
@@ -8240,7 +8169,7 @@
         <v>143</v>
       </c>
       <c r="C257" s="14" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="D257" s="19" t="s">
         <v>0</v>
@@ -8254,7 +8183,7 @@
         <v>144</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="D258" s="18" t="s">
         <v>0</v>
@@ -8265,10 +8194,10 @@
         <v>258</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="C259" s="14" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
       <c r="D259" s="19" t="s">
         <v>20</v>
@@ -8282,7 +8211,7 @@
         <v>145</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>600</v>
+        <v>589</v>
       </c>
       <c r="D260" s="20" t="s">
         <v>1</v>
@@ -8296,7 +8225,7 @@
         <v>146</v>
       </c>
       <c r="C261" s="14" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
       <c r="D261" s="18" t="s">
         <v>0</v>
@@ -8310,7 +8239,7 @@
         <v>147</v>
       </c>
       <c r="C262" s="14" t="s">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="D262" s="19" t="s">
         <v>0</v>
@@ -8324,7 +8253,7 @@
         <v>148</v>
       </c>
       <c r="C263" s="25" t="s">
-        <v>603</v>
+        <v>592</v>
       </c>
       <c r="D263" s="21" t="s">
         <v>0</v>
@@ -8335,10 +8264,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="30" t="s">
-        <v>604</v>
+        <v>593</v>
       </c>
       <c r="C264" s="25" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="D264" s="19" t="s">
         <v>1</v>
@@ -8352,13 +8281,13 @@
         <v>149</v>
       </c>
       <c r="C265" s="25" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="D265" s="18" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A266" s="29">
         <v>265</v>
       </c>
@@ -8366,7 +8295,7 @@
         <v>150</v>
       </c>
       <c r="C266" s="14" t="s">
-        <v>607</v>
+        <v>781</v>
       </c>
       <c r="D266" s="35" t="s">
         <v>1</v>
@@ -8377,10 +8306,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="C267" s="14" t="s">
-        <v>609</v>
+        <v>597</v>
       </c>
       <c r="D267" s="18" t="s">
         <v>0</v>
@@ -8391,10 +8320,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="11" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="C268" s="14" t="s">
-        <v>611</v>
+        <v>599</v>
       </c>
       <c r="D268" s="18" t="s">
         <v>1</v>
@@ -8405,10 +8334,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="11" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="C269" s="14" t="s">
-        <v>613</v>
+        <v>601</v>
       </c>
       <c r="D269" s="18" t="s">
         <v>1</v>
@@ -8422,7 +8351,7 @@
         <v>151</v>
       </c>
       <c r="C270" s="14" t="s">
-        <v>614</v>
+        <v>602</v>
       </c>
       <c r="D270" s="18" t="s">
         <v>1</v>
@@ -8436,7 +8365,7 @@
         <v>152</v>
       </c>
       <c r="C271" s="14" t="s">
-        <v>615</v>
+        <v>603</v>
       </c>
       <c r="D271" s="18" t="s">
         <v>0</v>
@@ -8447,10 +8376,10 @@
         <v>271</v>
       </c>
       <c r="B272" s="11" t="s">
-        <v>616</v>
+        <v>604</v>
       </c>
       <c r="C272" s="14" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="D272" s="18" t="s">
         <v>0</v>
@@ -8464,7 +8393,7 @@
         <v>153</v>
       </c>
       <c r="C273" s="14" t="s">
-        <v>618</v>
+        <v>606</v>
       </c>
       <c r="D273" s="15" t="s">
         <v>0</v>
@@ -8478,7 +8407,7 @@
         <v>154</v>
       </c>
       <c r="C274" s="14" t="s">
-        <v>619</v>
+        <v>607</v>
       </c>
       <c r="D274" s="19" t="s">
         <v>20</v>
@@ -8492,7 +8421,7 @@
         <v>155</v>
       </c>
       <c r="C275" s="14" t="s">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="D275" s="18" t="s">
         <v>1</v>
@@ -8503,10 +8432,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="11" t="s">
-        <v>621</v>
+        <v>609</v>
       </c>
       <c r="C276" s="14" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
       <c r="D276" s="36" t="s">
         <v>0</v>
@@ -8517,10 +8446,10 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="C277" s="14" t="s">
-        <v>624</v>
+        <v>612</v>
       </c>
       <c r="D277" s="36" t="s">
         <v>20</v>
@@ -8531,10 +8460,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="11" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="C278" s="14" t="s">
-        <v>626</v>
+        <v>614</v>
       </c>
       <c r="D278" s="36" t="s">
         <v>0</v>
@@ -8545,10 +8474,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>767</v>
+        <v>753</v>
       </c>
       <c r="C279" s="14" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="D279" s="36" t="s">
         <v>17</v>
@@ -8559,10 +8488,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="11" t="s">
-        <v>628</v>
+        <v>616</v>
       </c>
       <c r="C280" s="14" t="s">
-        <v>629</v>
+        <v>617</v>
       </c>
       <c r="D280" s="19" t="s">
         <v>20</v>
@@ -8576,7 +8505,7 @@
         <v>156</v>
       </c>
       <c r="C281" s="14" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
       <c r="D281" s="19" t="s">
         <v>20</v>
@@ -8590,7 +8519,7 @@
         <v>157</v>
       </c>
       <c r="C282" s="14" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="D282" s="19" t="s">
         <v>17</v>
@@ -8604,7 +8533,7 @@
         <v>158</v>
       </c>
       <c r="C283" s="14" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="D283" s="19" t="s">
         <v>20</v>
@@ -8618,7 +8547,7 @@
         <v>159</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="D284" s="19" t="s">
         <v>0</v>
@@ -8632,7 +8561,7 @@
         <v>160</v>
       </c>
       <c r="C285" s="14" t="s">
-        <v>634</v>
+        <v>622</v>
       </c>
       <c r="D285" s="19" t="s">
         <v>17</v>
@@ -8646,7 +8575,7 @@
         <v>161</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>635</v>
+        <v>623</v>
       </c>
       <c r="D286" s="19" t="s">
         <v>17</v>
@@ -8660,7 +8589,7 @@
         <v>162</v>
       </c>
       <c r="C287" s="14" t="s">
-        <v>636</v>
+        <v>624</v>
       </c>
       <c r="D287" s="19" t="s">
         <v>0</v>
@@ -8674,7 +8603,7 @@
         <v>163</v>
       </c>
       <c r="C288" s="14" t="s">
-        <v>637</v>
+        <v>625</v>
       </c>
       <c r="D288" s="19" t="s">
         <v>17</v>
@@ -8688,7 +8617,7 @@
         <v>164</v>
       </c>
       <c r="C289" s="25" t="s">
-        <v>638</v>
+        <v>626</v>
       </c>
       <c r="D289" s="19" t="s">
         <v>17</v>
@@ -8702,13 +8631,13 @@
         <v>165</v>
       </c>
       <c r="C290" s="14" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="D290" s="19" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A291" s="4">
         <v>290</v>
       </c>
@@ -8716,7 +8645,7 @@
         <v>166</v>
       </c>
       <c r="C291" s="14" t="s">
-        <v>640</v>
+        <v>782</v>
       </c>
       <c r="D291" s="19" t="s">
         <v>17</v>
@@ -8727,10 +8656,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>641</v>
+        <v>628</v>
       </c>
       <c r="C292" s="14" t="s">
-        <v>642</v>
+        <v>629</v>
       </c>
       <c r="D292" s="8" t="s">
         <v>17</v>
@@ -8741,10 +8670,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="11" t="s">
-        <v>643</v>
+        <v>630</v>
       </c>
       <c r="C293" s="14" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="D293" s="19" t="s">
         <v>17</v>
@@ -8755,10 +8684,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="11" t="s">
-        <v>645</v>
+        <v>632</v>
       </c>
       <c r="C294" s="14" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="D294" s="19" t="s">
         <v>20</v>
@@ -8772,7 +8701,7 @@
         <v>167</v>
       </c>
       <c r="C295" s="14" t="s">
-        <v>647</v>
+        <v>634</v>
       </c>
       <c r="D295" s="19" t="s">
         <v>20</v>
@@ -8786,7 +8715,7 @@
         <v>168</v>
       </c>
       <c r="C296" s="14" t="s">
-        <v>648</v>
+        <v>635</v>
       </c>
       <c r="D296" s="19" t="s">
         <v>20</v>
@@ -8800,7 +8729,7 @@
         <v>145</v>
       </c>
       <c r="C297" s="14" t="s">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="D297" s="19" t="s">
         <v>0</v>
@@ -8814,7 +8743,7 @@
         <v>169</v>
       </c>
       <c r="C298" s="14" t="s">
-        <v>650</v>
+        <v>637</v>
       </c>
       <c r="D298" s="19" t="s">
         <v>1</v>
@@ -8828,7 +8757,7 @@
         <v>170</v>
       </c>
       <c r="C299" s="14" t="s">
-        <v>651</v>
+        <v>638</v>
       </c>
       <c r="D299" s="19" t="s">
         <v>0</v>
@@ -8839,10 +8768,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="11" t="s">
-        <v>652</v>
+        <v>639</v>
       </c>
       <c r="C300" s="14" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
       <c r="D300" s="19" t="s">
         <v>1</v>
@@ -8856,7 +8785,7 @@
         <v>171</v>
       </c>
       <c r="C301" s="14" t="s">
-        <v>654</v>
+        <v>641</v>
       </c>
       <c r="D301" s="15" t="s">
         <v>20</v>
@@ -8867,10 +8796,10 @@
         <v>301</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="C302" s="14" t="s">
-        <v>656</v>
+        <v>643</v>
       </c>
       <c r="D302" s="19" t="s">
         <v>0</v>
@@ -8884,7 +8813,7 @@
         <v>172</v>
       </c>
       <c r="C303" s="14" t="s">
-        <v>657</v>
+        <v>644</v>
       </c>
       <c r="D303" s="15" t="s">
         <v>17</v>
@@ -8898,7 +8827,7 @@
         <v>173</v>
       </c>
       <c r="C304" s="14" t="s">
-        <v>658</v>
+        <v>645</v>
       </c>
       <c r="D304" s="19" t="s">
         <v>17</v>
@@ -8912,7 +8841,7 @@
         <v>174</v>
       </c>
       <c r="C305" s="14" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="D305" s="19" t="s">
         <v>17</v>
@@ -8926,7 +8855,7 @@
         <v>175</v>
       </c>
       <c r="C306" s="14" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="D306" s="19" t="s">
         <v>17</v>
@@ -8940,7 +8869,7 @@
         <v>176</v>
       </c>
       <c r="C307" s="14" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="D307" s="15" t="s">
         <v>17</v>
@@ -8954,7 +8883,7 @@
         <v>177</v>
       </c>
       <c r="C308" s="14" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="D308" s="19" t="s">
         <v>17</v>
@@ -8968,7 +8897,7 @@
         <v>178</v>
       </c>
       <c r="C309" s="14" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="D309" s="19" t="s">
         <v>17</v>
@@ -8979,10 +8908,10 @@
         <v>309</v>
       </c>
       <c r="B310" s="11" t="s">
-        <v>664</v>
+        <v>651</v>
       </c>
       <c r="C310" s="14" t="s">
-        <v>665</v>
+        <v>652</v>
       </c>
       <c r="D310" s="19" t="s">
         <v>17</v>
@@ -8993,10 +8922,10 @@
         <v>310</v>
       </c>
       <c r="B311" s="11" t="s">
-        <v>666</v>
+        <v>653</v>
       </c>
       <c r="C311" s="14" t="s">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="D311" s="19" t="s">
         <v>17</v>
@@ -9010,7 +8939,7 @@
         <v>179</v>
       </c>
       <c r="C312" s="14" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="D312" s="19" t="s">
         <v>17</v>
@@ -9024,7 +8953,7 @@
         <v>180</v>
       </c>
       <c r="C313" s="14" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="D313" s="19" t="s">
         <v>17</v>
@@ -9035,10 +8964,10 @@
         <v>313</v>
       </c>
       <c r="B314" s="11" t="s">
-        <v>669</v>
+        <v>656</v>
       </c>
       <c r="C314" s="14" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
       <c r="D314" s="19" t="s">
         <v>17</v>
@@ -9052,7 +8981,7 @@
         <v>181</v>
       </c>
       <c r="C315" s="14" t="s">
-        <v>671</v>
+        <v>658</v>
       </c>
       <c r="D315" s="19" t="s">
         <v>0</v>
@@ -9066,7 +8995,7 @@
         <v>182</v>
       </c>
       <c r="C316" s="14" t="s">
-        <v>672</v>
+        <v>659</v>
       </c>
       <c r="D316" s="19" t="s">
         <v>1</v>
@@ -9080,7 +9009,7 @@
         <v>183</v>
       </c>
       <c r="C317" s="14" t="s">
-        <v>673</v>
+        <v>660</v>
       </c>
       <c r="D317" s="18" t="s">
         <v>1</v>
@@ -9091,10 +9020,10 @@
         <v>317</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>674</v>
+        <v>661</v>
       </c>
       <c r="C318" s="14" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="D318" s="20" t="s">
         <v>17</v>
@@ -9108,7 +9037,7 @@
         <v>184</v>
       </c>
       <c r="C319" s="14" t="s">
-        <v>676</v>
+        <v>663</v>
       </c>
       <c r="D319" s="19" t="s">
         <v>1</v>
@@ -9122,7 +9051,7 @@
         <v>185</v>
       </c>
       <c r="C320" s="14" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="D320" s="19" t="s">
         <v>20</v>
@@ -9136,7 +9065,7 @@
         <v>186</v>
       </c>
       <c r="C321" s="14" t="s">
-        <v>678</v>
+        <v>665</v>
       </c>
       <c r="D321" s="18" t="s">
         <v>20</v>
@@ -9150,7 +9079,7 @@
         <v>187</v>
       </c>
       <c r="C322" s="14" t="s">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="D322" s="23" t="s">
         <v>0</v>
@@ -9164,7 +9093,7 @@
         <v>188</v>
       </c>
       <c r="C323" s="14" t="s">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="D323" s="22" t="s">
         <v>20</v>
@@ -9178,7 +9107,7 @@
         <v>189</v>
       </c>
       <c r="C324" s="14" t="s">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="D324" s="22" t="s">
         <v>20</v>
@@ -9192,7 +9121,7 @@
         <v>190</v>
       </c>
       <c r="C325" s="14" t="s">
-        <v>682</v>
+        <v>669</v>
       </c>
       <c r="D325" s="15" t="s">
         <v>1</v>
@@ -9206,7 +9135,7 @@
         <v>191</v>
       </c>
       <c r="C326" s="14" t="s">
-        <v>683</v>
+        <v>670</v>
       </c>
       <c r="D326" s="19" t="s">
         <v>20</v>
@@ -9220,7 +9149,7 @@
         <v>192</v>
       </c>
       <c r="C327" s="14" t="s">
-        <v>684</v>
+        <v>671</v>
       </c>
       <c r="D327" s="19" t="s">
         <v>20</v>
@@ -9234,7 +9163,7 @@
         <v>193</v>
       </c>
       <c r="C328" s="14" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="D328" s="19" t="s">
         <v>17</v>
@@ -9245,10 +9174,10 @@
         <v>328</v>
       </c>
       <c r="B329" s="11" t="s">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="C329" s="14" t="s">
-        <v>687</v>
+        <v>674</v>
       </c>
       <c r="D329" s="19" t="s">
         <v>17</v>
@@ -9259,10 +9188,10 @@
         <v>329</v>
       </c>
       <c r="B330" s="11" t="s">
-        <v>688</v>
+        <v>675</v>
       </c>
       <c r="C330" s="14" t="s">
-        <v>689</v>
+        <v>676</v>
       </c>
       <c r="D330" s="19" t="s">
         <v>17</v>
@@ -9276,7 +9205,7 @@
         <v>194</v>
       </c>
       <c r="C331" s="14" t="s">
-        <v>690</v>
+        <v>677</v>
       </c>
       <c r="D331" s="19" t="s">
         <v>0</v>
@@ -9287,10 +9216,10 @@
         <v>331</v>
       </c>
       <c r="B332" s="11" t="s">
-        <v>691</v>
+        <v>678</v>
       </c>
       <c r="C332" s="14" t="s">
-        <v>692</v>
+        <v>679</v>
       </c>
       <c r="D332" s="23" t="s">
         <v>0</v>
@@ -9304,7 +9233,7 @@
         <v>5</v>
       </c>
       <c r="C333" s="14" t="s">
-        <v>693</v>
+        <v>680</v>
       </c>
       <c r="D333" s="19" t="s">
         <v>20</v>
@@ -9318,7 +9247,7 @@
         <v>195</v>
       </c>
       <c r="C334" s="14" t="s">
-        <v>694</v>
+        <v>681</v>
       </c>
       <c r="D334" s="19" t="s">
         <v>20</v>
@@ -9329,10 +9258,10 @@
         <v>334</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>695</v>
+        <v>682</v>
       </c>
       <c r="C335" s="14" t="s">
-        <v>696</v>
+        <v>683</v>
       </c>
       <c r="D335" s="19" t="s">
         <v>20</v>
@@ -9343,10 +9272,10 @@
         <v>335</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>697</v>
+        <v>684</v>
       </c>
       <c r="C336" s="14" t="s">
-        <v>698</v>
+        <v>685</v>
       </c>
       <c r="D336" s="19" t="s">
         <v>20</v>
@@ -9360,7 +9289,7 @@
         <v>196</v>
       </c>
       <c r="C337" s="14" t="s">
-        <v>699</v>
+        <v>686</v>
       </c>
       <c r="D337" s="15" t="s">
         <v>20</v>
@@ -9374,7 +9303,7 @@
         <v>197</v>
       </c>
       <c r="C338" s="14" t="s">
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="D338" s="19" t="s">
         <v>1</v>
@@ -9388,7 +9317,7 @@
         <v>198</v>
       </c>
       <c r="C339" s="14" t="s">
-        <v>701</v>
+        <v>688</v>
       </c>
       <c r="D339" s="19" t="s">
         <v>17</v>
@@ -9399,10 +9328,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>702</v>
+        <v>689</v>
       </c>
       <c r="C340" s="14" t="s">
-        <v>703</v>
+        <v>690</v>
       </c>
       <c r="D340" s="19" t="s">
         <v>1</v>
@@ -9416,7 +9345,7 @@
         <v>199</v>
       </c>
       <c r="C341" s="14" t="s">
-        <v>704</v>
+        <v>691</v>
       </c>
       <c r="D341" s="19" t="s">
         <v>1</v>
@@ -9430,7 +9359,7 @@
         <v>200</v>
       </c>
       <c r="C342" s="11" t="s">
-        <v>705</v>
+        <v>692</v>
       </c>
       <c r="D342" s="19" t="s">
         <v>0</v>
@@ -9444,7 +9373,7 @@
         <v>201</v>
       </c>
       <c r="C343" s="11" t="s">
-        <v>706</v>
+        <v>693</v>
       </c>
       <c r="D343" s="19" t="s">
         <v>1</v>
@@ -9458,7 +9387,7 @@
         <v>202</v>
       </c>
       <c r="C344" s="11" t="s">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="D344" s="19" t="s">
         <v>0</v>
@@ -9472,7 +9401,7 @@
         <v>203</v>
       </c>
       <c r="C345" s="11" t="s">
-        <v>707</v>
+        <v>694</v>
       </c>
       <c r="D345" s="19" t="s">
         <v>17</v>
@@ -9483,10 +9412,10 @@
         <v>345</v>
       </c>
       <c r="B346" s="11" t="s">
-        <v>708</v>
+        <v>695</v>
       </c>
       <c r="C346" s="11" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="D346" s="19" t="s">
         <v>17</v>
@@ -9500,7 +9429,7 @@
         <v>204</v>
       </c>
       <c r="C347" s="11" t="s">
-        <v>710</v>
+        <v>697</v>
       </c>
       <c r="D347" s="19" t="s">
         <v>0</v>
@@ -9514,7 +9443,7 @@
         <v>205</v>
       </c>
       <c r="C348" s="11" t="s">
-        <v>711</v>
+        <v>698</v>
       </c>
       <c r="D348" s="19" t="s">
         <v>0</v>
@@ -9528,7 +9457,7 @@
         <v>206</v>
       </c>
       <c r="C349" s="11" t="s">
-        <v>712</v>
+        <v>699</v>
       </c>
       <c r="D349" s="19" t="s">
         <v>0</v>
@@ -9542,7 +9471,7 @@
         <v>207</v>
       </c>
       <c r="C350" s="11" t="s">
-        <v>713</v>
+        <v>700</v>
       </c>
       <c r="D350" s="15" t="s">
         <v>1</v>
@@ -9553,10 +9482,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>714</v>
+        <v>701</v>
       </c>
       <c r="C351" s="11" t="s">
-        <v>715</v>
+        <v>702</v>
       </c>
       <c r="D351" s="19" t="s">
         <v>1</v>
@@ -9570,7 +9499,7 @@
         <v>208</v>
       </c>
       <c r="C352" s="11" t="s">
-        <v>716</v>
+        <v>703</v>
       </c>
       <c r="D352" s="19" t="s">
         <v>20</v>
@@ -9584,7 +9513,7 @@
         <v>209</v>
       </c>
       <c r="C353" s="11" t="s">
-        <v>717</v>
+        <v>704</v>
       </c>
       <c r="D353" s="19" t="s">
         <v>0</v>
@@ -9595,10 +9524,10 @@
         <v>353</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>718</v>
+        <v>705</v>
       </c>
       <c r="C354" s="11" t="s">
-        <v>719</v>
+        <v>706</v>
       </c>
       <c r="D354" s="19" t="s">
         <v>20</v>
@@ -9612,7 +9541,7 @@
         <v>210</v>
       </c>
       <c r="C355" s="11" t="s">
-        <v>720</v>
+        <v>707</v>
       </c>
       <c r="D355" s="19" t="s">
         <v>0</v>
@@ -9623,10 +9552,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>721</v>
+        <v>708</v>
       </c>
       <c r="C356" s="11" t="s">
-        <v>722</v>
+        <v>709</v>
       </c>
       <c r="D356" s="19" t="s">
         <v>1</v>
@@ -9640,7 +9569,7 @@
         <v>211</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>723</v>
+        <v>710</v>
       </c>
       <c r="D357" s="15" t="s">
         <v>20</v>
@@ -9654,7 +9583,7 @@
         <v>6</v>
       </c>
       <c r="C358" s="11" t="s">
-        <v>724</v>
+        <v>711</v>
       </c>
       <c r="D358" s="34" t="s">
         <v>17</v>
@@ -9668,7 +9597,7 @@
         <v>7</v>
       </c>
       <c r="C359" s="30" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="D359" s="30" t="s">
         <v>20</v>
@@ -9679,10 +9608,10 @@
         <v>359</v>
       </c>
       <c r="B360" s="11" t="s">
-        <v>726</v>
+        <v>713</v>
       </c>
       <c r="C360" s="11" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="D360" s="19" t="s">
         <v>17</v>
@@ -9693,10 +9622,10 @@
         <v>360</v>
       </c>
       <c r="B361" s="30" t="s">
-        <v>728</v>
+        <v>715</v>
       </c>
       <c r="C361" s="30" t="s">
-        <v>729</v>
+        <v>716</v>
       </c>
       <c r="D361" s="15" t="s">
         <v>20</v>
@@ -9707,10 +9636,10 @@
         <v>361</v>
       </c>
       <c r="B362" s="30" t="s">
-        <v>730</v>
+        <v>717</v>
       </c>
       <c r="C362" s="30" t="s">
-        <v>731</v>
+        <v>718</v>
       </c>
       <c r="D362" s="15" t="s">
         <v>17</v>
@@ -9724,7 +9653,7 @@
         <v>212</v>
       </c>
       <c r="C363" s="30" t="s">
-        <v>732</v>
+        <v>719</v>
       </c>
       <c r="D363" s="15" t="s">
         <v>20</v>
@@ -9738,7 +9667,7 @@
         <v>213</v>
       </c>
       <c r="C364" s="30" t="s">
-        <v>733</v>
+        <v>720</v>
       </c>
       <c r="D364" s="15" t="s">
         <v>0</v>
@@ -9752,7 +9681,7 @@
         <v>214</v>
       </c>
       <c r="C365" s="30" t="s">
-        <v>734</v>
+        <v>721</v>
       </c>
       <c r="D365" s="15" t="s">
         <v>0</v>
@@ -9766,7 +9695,7 @@
         <v>215</v>
       </c>
       <c r="C366" s="30" t="s">
-        <v>735</v>
+        <v>722</v>
       </c>
       <c r="D366" s="15" t="s">
         <v>20</v>
@@ -9780,7 +9709,7 @@
         <v>216</v>
       </c>
       <c r="C367" s="30" t="s">
-        <v>736</v>
+        <v>723</v>
       </c>
       <c r="D367" s="15" t="s">
         <v>20</v>
@@ -9791,10 +9720,10 @@
         <v>367</v>
       </c>
       <c r="B368" s="11" t="s">
-        <v>737</v>
+        <v>724</v>
       </c>
       <c r="C368" s="30" t="s">
-        <v>738</v>
+        <v>725</v>
       </c>
       <c r="D368" s="15" t="s">
         <v>0</v>
@@ -9808,7 +9737,7 @@
         <v>217</v>
       </c>
       <c r="C369" s="30" t="s">
-        <v>739</v>
+        <v>726</v>
       </c>
       <c r="D369" s="15" t="s">
         <v>20</v>
@@ -9819,10 +9748,10 @@
         <v>369</v>
       </c>
       <c r="B370" s="30" t="s">
-        <v>740</v>
+        <v>727</v>
       </c>
       <c r="C370" s="30" t="s">
-        <v>741</v>
+        <v>728</v>
       </c>
       <c r="D370" s="15" t="s">
         <v>17</v>
@@ -9836,7 +9765,7 @@
         <v>8</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="D371" s="15" t="s">
         <v>1</v>
@@ -9850,7 +9779,7 @@
         <v>218</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>743</v>
+        <v>730</v>
       </c>
       <c r="D372" s="15" t="s">
         <v>0</v>
@@ -9864,7 +9793,7 @@
         <v>219</v>
       </c>
       <c r="C373" s="30" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="D373" s="15" t="s">
         <v>1</v>
@@ -9878,7 +9807,7 @@
         <v>220</v>
       </c>
       <c r="C374" s="30" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="D374" s="15" t="s">
         <v>0</v>
@@ -9892,7 +9821,7 @@
         <v>221</v>
       </c>
       <c r="C375" s="30" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="D375" s="15" t="s">
         <v>1</v>
@@ -9903,10 +9832,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="11" t="s">
-        <v>747</v>
+        <v>734</v>
       </c>
       <c r="C376" s="30" t="s">
-        <v>748</v>
+        <v>735</v>
       </c>
       <c r="D376" s="15" t="s">
         <v>0</v>
@@ -9920,7 +9849,7 @@
         <v>222</v>
       </c>
       <c r="C377" s="30" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="D377" s="15" t="s">
         <v>20</v>
@@ -9934,7 +9863,7 @@
         <v>223</v>
       </c>
       <c r="C378" s="30" t="s">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="D378" s="15" t="s">
         <v>17</v>
@@ -9948,7 +9877,7 @@
         <v>224</v>
       </c>
       <c r="C379" s="30" t="s">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="D379" s="15" t="s">
         <v>20</v>
@@ -9962,7 +9891,7 @@
         <v>9</v>
       </c>
       <c r="C380" s="30" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="D380" s="15" t="s">
         <v>0</v>
@@ -9973,10 +9902,10 @@
         <v>380</v>
       </c>
       <c r="B381" s="30" t="s">
-        <v>753</v>
+        <v>740</v>
       </c>
       <c r="C381" s="30" t="s">
-        <v>754</v>
+        <v>741</v>
       </c>
       <c r="D381" s="15" t="s">
         <v>17</v>
@@ -9990,7 +9919,7 @@
         <v>225</v>
       </c>
       <c r="C382" s="30" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="D382" s="15" t="s">
         <v>1</v>
@@ -10004,7 +9933,7 @@
         <v>226</v>
       </c>
       <c r="C383" s="30" t="s">
-        <v>756</v>
+        <v>743</v>
       </c>
       <c r="D383" s="15" t="s">
         <v>0</v>
@@ -10018,13 +9947,13 @@
         <v>227</v>
       </c>
       <c r="C384" s="30" t="s">
-        <v>757</v>
+        <v>744</v>
       </c>
       <c r="D384" s="15" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A385" s="10">
         <v>384</v>
       </c>
@@ -10032,7 +9961,7 @@
         <v>228</v>
       </c>
       <c r="C385" s="30" t="s">
-        <v>758</v>
+        <v>783</v>
       </c>
       <c r="D385" s="15" t="s">
         <v>1</v>
@@ -10046,7 +9975,7 @@
         <v>229</v>
       </c>
       <c r="C386" s="11" t="s">
-        <v>759</v>
+        <v>745</v>
       </c>
       <c r="D386" s="15" t="s">
         <v>17</v>
@@ -10060,7 +9989,7 @@
         <v>230</v>
       </c>
       <c r="C387" s="11" t="s">
-        <v>760</v>
+        <v>746</v>
       </c>
       <c r="D387" s="15" t="s">
         <v>20</v>
@@ -10074,7 +10003,7 @@
         <v>231</v>
       </c>
       <c r="C388" s="11" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="D388" s="15" t="s">
         <v>17</v>
@@ -10085,10 +10014,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="11" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
       <c r="C389" s="11" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="D389" s="19" t="s">
         <v>1</v>
@@ -10099,10 +10028,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="11" t="s">
-        <v>764</v>
+        <v>750</v>
       </c>
       <c r="C390" s="11" t="s">
-        <v>765</v>
+        <v>751</v>
       </c>
       <c r="D390" s="19" t="s">
         <v>1</v>
@@ -10116,7 +10045,7 @@
         <v>232</v>
       </c>
       <c r="C391" s="11" t="s">
-        <v>766</v>
+        <v>752</v>
       </c>
       <c r="D391" s="19" t="s">
         <v>1</v>

--- a/data/Ngan-Hang-Cau-Hoi.xlsx
+++ b/data/Ngan-Hang-Cau-Hoi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9f54d0bdb7235122/Documents/My App/trac-nghiem-luat-dau-thau/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C69DD5D-4D78-4F88-9C95-3657EB0C4F3D}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3769E407-770F-4D1D-8F82-66C059EAE109}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0822E189-CD53-41B9-B216-EFA7EF505EBC}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="19200" windowHeight="11170" xr2:uid="{0822E189-CD53-41B9-B216-EFA7EF505EBC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -47,14 +47,6 @@
     <t>A</t>
   </si>
   <si>
-    <t>A. Gói thầu mua sắm hàng hóa thông dụng, đơn giản, có sẵn trên thị trường
-B. Gói thầu mua sắm hàng hóa mà hàng hóa đó trong nước sản xuất được và đáp ứng các yêu cầu về kỹ thuật, chất lượng, giá nhưng chủ đầu tư yêu cầu phải mua hàng hóa nhập khẩu
-C. Gói thầu mua sắm hàng hóa mà hàng hóa đó trong nước không sản xuất được hoặc sản xuất
-được nhưng không đáp ứng một trong các yêu cầu về kỹ thuật, chất lượng, giá
-D. Gói thầu mua sắm hàng hóa thông dụng đã được nhập khẩu và chào bán tại Việt Nam nhưng
-hàng hóa đó trong nước không sản xuất được</t>
-  </si>
-  <si>
     <t>A. Bắt buộc quy định trong hồ sơ mời thầu do đây là tiêu chí chứng minh nguồn lực tài chính
 B. Không bắt buộc quy định, hồ sơ mời thầu có thể đưa ra yêu cầu về cam kết cung cấp tín dụng hoặc không yêu cầu về cam kết cung cấp tín dụng
 C. Bắt buộc quy định trong hồ sơ mời thầu đối với gói thầu xây lắp áp dụng phương thức một giai đoạn hai túi hồ sơ
@@ -935,13 +927,6 @@
 D. Căn cứ theo phân cấp quyết định mua sắm của UBND tỉnh X</t>
   </si>
   <si>
-    <t>A. Sở Y tế A được tự quyết định việc mua sắm trên cơ sở bảo đảm công khai, minh bạch, hiệu quả và trách nhiệm giải trình trong trường hợp nhà tài trợ yêu cầu không lựa chọn nhà thầu theo quy định của Luật Đấu thầu
-B. Sở Y tế A phải tổ chức lựa chọn nhà thầu theo quy định của Luật Đấu thầu
-C. Trong mọi trường hợp Sở Y tế A không phải thực hiện theo Luật Đấu thầu do đây là nguồn doanh nghiệp trong nước tài trợ
-D. Phải xin ý kiến của UBND tỉnh A để có cơ sở xác định có phải tổ chức lựa chọn nhà thầu theo
-Luật Đấu thầu hay không</t>
-  </si>
-  <si>
     <t>Đối với gói thầu cung cấp dịch vụ tư vấn không qua mạng, trường hợp hồ sơ đề xuất về tài chính của nhà thầu không vượt qua bước
 đánh giá về kỹ thuật sẽ được xử lý như thế nào theo quy định của pháp luật về đấu thầu?</t>
   </si>
@@ -962,13 +947,6 @@
 đấu thầu?</t>
   </si>
   <si>
-    <t>A. Công ty B sử dụng nhà thầu phụ là công ty A, công ty A là nhà thầu tư vấn lập Chương V yêu cầu kỹ thuật cho E-HSMT của gói thầu xây lắp X
-B. Công ty B tham dự gói thầu xây lắp X đồng thời là nhà thầu tư vấn lập Chương V yêu cầu kỹ thuật của E-HSMT của gói thầu xây lắp X.
-C. Công ty B sử dụng nhà thầu phụ là công ty tư vấn C, công ty tư vấn C sở hữu 30% cổ phần của công ty A và công ty A là nhà thầu tư vấn thiết kế kỹ thuật cho dự án Y
-D. Công ty A là nhà thầu tư vấn lập hồ sơ mời thầu gói thầu xây lắp X có sở hữu 30% vốn góp của
-Công ty B</t>
-  </si>
-  <si>
     <t>A. Đối với đấu thầu trong nước, khi tham gia gói thầu của dự án thuộc lĩnh vực khoa học, công nghệ, đổi mới sáng tạo và chuyển đổi số thì nhà thầu trong nước được sử dụng nhà thầu phụ đặc biệt là nhà thầu nước ngoài đối với phần công việc đặc thù mà nhà thầu trong nước chưa thực hiện được hoặc cần chuyển giao công nghệ
 B. Trong mọi trường hợp, đối với đấu thầu trong nước, nhà thầu không được phép sử dụng nhà thầu phụ đặc biệt là nhà thầu nước ngoài
 C. Giá trị công việc tối đa dành cho nhà thầu phụ trong hợp đồng phải bao gồm khối lượng công việc dành cho nhà thầu phụ đặc biệt
@@ -1036,13 +1014,6 @@
 B. Chỉ gói thầu xây lắp
 C. Chỉ gói thầu dịch vụ phi tư vấn
 D. Gói thầu mua sắm hàng hóa và dịch vụ phi tư vấn</t>
-  </si>
-  <si>
-    <t>A. Nhà thầu đã trúng thầu thông qua đấu thầu rộng rãi, đấu thầu hạn chế và đã ký hợp đồng gói thầu thực hiện gói thầu trước đó
-B. Thời gian từ khi ký hợp đồng gói thầu trước đến ngày phê duyệt kết quả mua sắm trực tiếp không
-quá 12 tháng
-C. Đơn giá các phần việc thuộc gói thầu mua sắm trực tiếp không vượt đơn giá phần việc tương ứng của gói thầu đã ký trước đó thuộc gói thầu tương tự đã ký hợp đồng trước đó, đồng thời, phù hợp với giá thị trường tại thời điểm hoàn thiện hợp đồng
-D. Chủ đầu tư được áp dụng mua sắm trực tiếp nhiều lần đối với các loại hàng hóa thuộc gói thầu</t>
   </si>
   <si>
     <t>Hãy chọn phương án đúng về hình thức đặt
@@ -1308,13 +1279,6 @@
   <si>
     <t>Trường hợp hồ sơ mời thầu có quy định về xuất xứ theo nhóm nước, vùng lãnh thổ mà không bao gồm xuất xứ Việt Nam, nhà thầu chào hàng hóa có xuất xứ Việt Nam sẽ bị
 đánh giá như thế nào?</t>
-  </si>
-  <si>
-    <t>A. Hàng hóa của nhà thầu không được xem xét, đánh giá
-B. Hàng hóa của nhà thầu vẫn được xem xét, đánh giá
-C. Yêu cầu nhà thầu bổ sung hàng hóa theo đúng xuất xứ thuộc nhóm nước, vùng lãnh thổ theo yêu cầu hồ sơ mời thầu nhưng phải cùng ký mã hiệu, nhãn hiệu với hàng hóa nhà thầu đã đề xuất trong hồ sơ dự thầu
-D. Yêu cầu nhà thầu bổ sung hàng hóa theo đúng xuất xứ thuộc nhóm nước, vùng lãnh thổ theo yêu cầu hồ sơ mời thầu, không phải đáp ứng cùng ký mã hiệu, nhãn hiệu với hàng hóa nhà thầu đã đề
-xuất trong hồ sơ dự thầu</t>
   </si>
   <si>
     <t>Gói thầu mua sắm 20 máy điều hòa, tổ chức
@@ -1717,21 +1681,6 @@
 D. Phương án A và C đều đúng</t>
   </si>
   <si>
-    <t xml:space="preserve">A. Hồ sơ mời quan tâm, hồ sơ mời sơ tuyển, hồ sơ mời thầu được phát hành sau 01 ngày kể từ khi thông báo mời quan tâm, thông báo mời sơ tuyển, thông báo mời thầu được đăng tải thành công trên Hệ thống mạng đấu thầu quốc gia
-B. Hồ sơ mời quan tâm, hồ sơ mời sơ tuyển, hồ sơ mời thầu được phát hành trước khi đăng tải thông báo mời quan tâm, thông báo mời sơ tuyển, thông báo mời thầu
-C. Hồ sơ mời quan tâm, hồ sơ mời sơ tuyển, hồ sơ mời thầu được phát hành sau 03 ngày kể từ khi
-thông báo mời quan tâm, thông báo mời sơ tuyển, thông báo mời thầu được đăng tải thành công trên Hệ thống mạng đấu thầu quốc gia
-D. Hồ sơ mời quan tâm, hồ sơ mời sơ tuyển, hồ sơ mời thầu được phát hành ngay sau khi đăng tải thành công thông báo mời quan tâm, thông báo mời sơ tuyển, thông báo mời thầu
-</t>
-  </si>
-  <si>
-    <t>A. Đấu thầu trước là việc thực hiện trước một số thủ tục trước khi dự án được phê duyệt đầu tư nhằm mục đích đẩy nhanh tiến độ thực hiện dự án, trừ gói thầu cần thực hiện trước khi phê duyệt dự án
-B. Đấu thầu trước là việc thực hiện các gói thầu thuộc giai đoạn chuẩn bị đầu tư
-C. Đấu thầu trước là việc lựa chọn nhà thầu không cần phê duyệt kế hoạch lựa chọn nhà thầu để đẩy nhanh tiến độ thực hiện
-D. Đấu thầu trước là việc thực hiện trước một số thủ tục trước khi dự án, dự toán mua sắm được phê duyệt nhằm mục đích đẩy nhanh tiến độ thực hiện dự án, dự toán mua sắm, trừ gói thầu cần thực
-hiện trước khi phê duyệt dự án</t>
-  </si>
-  <si>
     <t>A. Thẩm định hồ sơ yêu cầu
 B. Đánh giá hồ sơ đề xuất và thương thảo về các đề xuất của nhà thầu
 C. Phát hành hồ sơ yêu cầu
@@ -1768,13 +1717,6 @@
 B. Tối đa không quá 30 ngày đối với đấu thầu trong nước và không quá 60 ngày đối với đấu thầu quốc tế
 C. Do người có thẩm quyền, chủ đầu tư có trách nhiệm quyết định
 D. Do chủ đầu tư quyết định trên cơ sở bảo đảm tiến độ của dự án, gói thầu</t>
-  </si>
-  <si>
-    <t>A. Chuẩn bị và gửi dự thảo hợp đồng cho nhà thầu; thương thảo, hoàn thiện hợp đồng; trình, thẩm định, phê duyệt và công khai kết quả lựa chọn nhà thầu; ký kết hợp đồng
-B. Chuẩn bị và gửi dự thảo hợp đồng cho nhà thầu; thương thảo hợp đồng; trình, thẩm định, phê duyệt kết quả lựa chọn nhà thầu; ký kết và quản lý thực hiện hợp đồng
-C. Chuẩn bị và gửi dự thảo hợp đồng cho nhà thầu; hoàn thiện hợp đồng, phê duyệt và công khai kết quả lựa chọn nhà thầu; ký kết và quản lý thực hiện hợp đồng
-D. Lập, phê duyệt hồ sơ yêu cầu; xác định nhà thầu dự kiến được mời nhận hồ sơ yêu cầu; đánh giá
-hồ sơ đề xuất và thương thảo về các đề xuất của nhà thầu; phê duyệt và công khai kết quả lựa chọn nhà thầu; hoàn thiện, ký kết và quản lý thực hiện hợp đồng</t>
   </si>
   <si>
     <t>Đối với gói thầu áp dụng một giai đoạn một túi hồ sơ, trường hợp nào được thực hiện
@@ -2710,13 +2652,6 @@
 B. Được thực hiện sau thời điểm mở thầu
 C. Được thực hiện trước thời điểm đóng thầu trong trường hợp đã phát hành hồ sơ mời thầu trước ngày 01/7/2025 nhưng đến ngày 4/8/2025 chưa đóng thầu
 D. Phương án A và C đều đúng</t>
-  </si>
-  <si>
-    <t>A. Nhà thầu chịu trách nhiệm theo dõi thông tin trên Hệ thống mạng đấu thầu quốc gia để cập nhật thông tin về việc sửa đổi E- HSMT, thay đổi thời điểm đóng thầu (nếu có) để làm cơ sở chuẩn bị E- HSDT
-B. Nhà thầu phải tự chịu trách nhiệm và chịu bất lợi trong quá trình tham dự thầu nếu không theo dõi, cập nhật thông tin sửa đổi E-HSMT, thời điểm đóng thầu trên Hệ thống mạng đấu thầu quốc gia trong quá trình tham dự thầu
-C. Hệ thống mạng đấu thầu quốc gia tự động gửi email thông báo về việc sửa đổi E-HSMT, thay
-đổi thời điểm đóng thầu (nếu có) cho các nhà thầu quan tâm đến gói thầu
-D. Các phương án trên đều đúng</t>
   </si>
   <si>
     <t>Trường hợp E-HSMT không đầy đủ thông tin
@@ -3122,13 +3057,6 @@
 D. Phương án B và C đều đúng</t>
   </si>
   <si>
-    <t>A. Chỉ Hiệp định Đối tác Toàn diện và Tiến bộ Xuyên Thái Bình Dương (CPTPP)
-B. Hiệp định CPTPP và Hiệp định thương mại tự do giữa Cộng hòa xã hội chủ nghĩa Việt Nam và Liên
-minh Châu Âu (EVFTA)
-C. Hiệp định CPTPP, Hiệp định EVFTA và Hiệp định Thương mại Tự do giữa Việt Nam và Liên hiệp Vương quốc Anh và Bắc Ailen (UKVFTA)
-D. Tất cả các hiệp định mà Việt Nam là thành viên</t>
-  </si>
-  <si>
     <t>A. 8 nước
 B. 9 nước
 C. 11 nước
@@ -3389,12 +3317,6 @@
 D. 04 bản chụp</t>
   </si>
   <si>
-    <t>A. Đối với lần chào giá đầu tiên nhà thầu nhập các trọng số là đơn giá của hàng hóa nhà thầu dự kiến xác định sẽ
-B.  Nhà thầu không được thay đổi trọng số của từng hạng mục hàng hóa trong quá trình chào giá
-C. Nhà thầu cần nghiên cứu công thức tính thành tiền và đơn giá dự thầu từ các trọng số để đề xuất các trọng số cho
-D. Nhà thầu phải điền các trọng số về đơn giá (N1, N2,...) của từng hạng mục</t>
-  </si>
-  <si>
     <t>A. Nhập ngẫu nhiên các giá trị trọng số
 B. Nhập trọng số bằng giá trị khối lượng từng hạng mục
 C. Nhập trọng số là đơn giá dự kiến chào cho từng hạng mục
@@ -3450,13 +3372,6 @@
 B. Từng thành viên liên danh phải cam kết có năng lực tự thực hiện nghĩa vụ bảo hành theo yêu cầu của E- HSMT hoặc có hợp đồng nguyên tắc với đơn vị có đủ khả năng thực hiện nghĩa vụ bảo hành theo yêu cầu của E-HSMT
 C. Nhà thầu liên danh có cam kết có năng lực thực hiện nghĩa vụ bảo hành theo yêu cầu của E-HSMT và có hợp đồng nguyên tắc với đơn vị có đủ khả năng thực hiện nghĩa vụ bảo hành theo yêu cầu của E-HSMT
 D. Nhà thầu liên danh có cam kết có năng lực tự thực hiện nghĩa vụ bảo hành theo yêu cầu của E-HSMT hoặc có hợp đồng nguyên tắc với đơn vị có đủ khả năng thực hiện nghĩa vụ bảo hành theo yêu cầu của E-HSMT</t>
-  </si>
-  <si>
-    <t>A. Không được yêu cầu về huy động nhân sự chủ chốt đối với phần công việc cung cấp hàng hóa
-B. Chỉ được yêu cầu về huy động nhân sự chủ chốt đối với các dịch vụ liên quan có yếu tố đặc thù, phức tạp cần
-thiết phải có nhân sự có hiểu biết, nhiều kinh nghiệm đảm nhận.
-C. Được yêu cầu về huy động nhân sự chủ chốt đối với phần công việc cung cấp hàng hóa mà hàng hóa đó có tính đặc thù cần sự khẳng định của nhà sản xuất, nhà cung cấp để đảm bảo tính khả thi trong việc cung cấp hàng hóa
-D. Không được nêu yêu cầu huy động về nhân sự chủ chốt đối với hàng hóa thông dụng, sẵn có trên thị trường, không đòi hỏi nhân sự thực hiện dịch vụ liên quan phải có trình độ cao</t>
   </si>
   <si>
     <t>A. Kế hoạch lựa chọn nhà thầu được lập cho toàn bộ dự án, dự toán mua sắm. Trường hợp chưa đủ điều kiện lập kế hoạch lựa chọn nhà thầu cho toàn bộ dự án, dự toán mua sắm thì lập kế hoạch lựa chọn nhà thầu cho một hoặc một số gói thầu để thực hiện trước
@@ -3819,6 +3734,79 @@
 B. Nhà thầu liên danh trong đó có thành viên liên danh là nhà thầu nội khối và thành viên này đảm nhận từ 25% trở lên giá trị công việc của gói thầu
 C. Nhà thầu liên danh trong đó có thành viên liên danh là nhà thầu Hoa Kỳ và thành viên này đảm nhận từ 50% trở lên giá trị công việc của gói thầu
 D. Nhà thầu liên danh trong đó có thành viên liên danh là nhà thầu nội khối và thành viên này đảm nhận từ 40% trở lên giá trị công việc của gói thầu</t>
+  </si>
+  <si>
+    <t>A. Công ty B sử dụng nhà thầu phụ là công ty A, công ty A là nhà thầu tư vấn lập Chương V yêu cầu kỹ thuật cho E-HSMT của gói thầu xây lắp X
+B. Công ty B tham dự gói thầu xây lắp X đồng thời là nhà thầu tư vấn lập Chương V yêu cầu kỹ thuật của E-HSMT của gói thầu xây lắp X.
+C. Công ty B sử dụng nhà thầu phụ là công ty tư vấn C, công ty tư vấn C sở hữu 30% cổ phần của công ty A và công ty A là nhà thầu tư vấn thiết kế kỹ thuật cho dự án Y
+D. Công ty A là nhà thầu tư vấn lập hồ sơ mời thầu gói thầu xây lắp X có sở hữu 30% vốn góp của Công ty B</t>
+  </si>
+  <si>
+    <t>A. Nhà thầu đã trúng thầu thông qua đấu thầu rộng rãi, đấu thầu hạn chế và đã ký hợp đồng gói thầu thực hiện gói thầu trước đó
+B. Thời gian từ khi ký hợp đồng gói thầu trước đến ngày phê duyệt kết quả mua sắm trực tiếp không quá 12 tháng
+C. Đơn giá các phần việc thuộc gói thầu mua sắm trực tiếp không vượt đơn giá phần việc tương ứng của gói thầu đã ký trước đó thuộc gói thầu tương tự đã ký hợp đồng trước đó, đồng thời, phù hợp với giá thị trường tại thời điểm hoàn thiện hợp đồng
+D. Chủ đầu tư được áp dụng mua sắm trực tiếp nhiều lần đối với các loại hàng hóa thuộc gói thầu</t>
+  </si>
+  <si>
+    <t>A. Chuẩn bị và gửi dự thảo hợp đồng cho nhà thầu; thương thảo, hoàn thiện hợp đồng; trình, thẩm định, phê duyệt và công khai kết quả lựa chọn nhà thầu; ký kết hợp đồng
+B. Chuẩn bị và gửi dự thảo hợp đồng cho nhà thầu; thương thảo hợp đồng; trình, thẩm định, phê duyệt kết quả lựa chọn nhà thầu; ký kết và quản lý thực hiện hợp đồng
+C. Chuẩn bị và gửi dự thảo hợp đồng cho nhà thầu; hoàn thiện hợp đồng, phê duyệt và công khai kết quả lựa chọn nhà thầu; ký kết và quản lý thực hiện hợp đồng
+D. Lập, phê duyệt hồ sơ yêu cầu; xác định nhà thầu dự kiến được mời nhận hồ sơ yêu cầu; đánh giá hồ sơ đề xuất và thương thảo về các đề xuất của nhà thầu; phê duyệt và công khai kết quả lựa chọn nhà thầu; hoàn thiện, ký kết và quản lý thực hiện hợp đồng</t>
+  </si>
+  <si>
+    <t>A. Gói thầu mua sắm hàng hóa thông dụng, đơn giản, có sẵn trên thị trường
+B. Gói thầu mua sắm hàng hóa mà hàng hóa đó trong nước sản xuất được và đáp ứng các yêu cầu về kỹ thuật, chất lượng, giá nhưng chủ đầu tư yêu cầu phải mua hàng hóa nhập khẩu
+C. Gói thầu mua sắm hàng hóa mà hàng hóa đó trong nước không sản xuất được hoặc sản xuất được nhưng không đáp ứng một trong các yêu cầu về kỹ thuật, chất lượng, giá
+D. Gói thầu mua sắm hàng hóa thông dụng đã được nhập khẩu và chào bán tại Việt Nam nhưn hàng hóa đó trong nước không sản xuất được</t>
+  </si>
+  <si>
+    <t>A. Sở Y tế A được tự quyết định việc mua sắm trên cơ sở bảo đảm công khai, minh bạch, hiệu quả và trách nhiệm giải trình trong trường hợp nhà tài trợ yêu cầu không lựa chọn nhà thầu theo quy định của Luật Đấu thầu
+B. Sở Y tế A phải tổ chức lựa chọn nhà thầu theo quy định của Luật Đấu thầu
+C. Trong mọi trường hợp Sở Y tế A không phải thực hiện theo Luật Đấu thầu do đây là nguồn doanh nghiệp trong nước tài trợ
+D. Phải xin ý kiến của UBND tỉnh A để có cơ sở xác định có phải tổ chức lựa chọn nhà thầu theo Luật Đấu thầu hay không</t>
+  </si>
+  <si>
+    <t>A. Hàng hóa của nhà thầu không được xem xét, đánh giá
+B. Hàng hóa của nhà thầu vẫn được xem xét, đánh giá
+C. Yêu cầu nhà thầu bổ sung hàng hóa theo đúng xuất xứ thuộc nhóm nước, vùng lãnh thổ theo yêu cầu hồ sơ mời thầu nhưng phải cùng ký mã hiệu, nhãn hiệu với hàng hóa nhà thầu đã đề xuất trong hồ sơ dự thầu
+D. Yêu cầu nhà thầu bổ sung hàng hóa theo đúng xuất xứ thuộc nhóm nước, vùng lãnh thổ theo yêu cầu hồ sơ mời thầu, không phải đáp ứng cùng ký mã hiệu, nhãn hiệu với hàng hóa nhà thầu đã đề xuất trong hồ sơ dự thầu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A. Hồ sơ mời quan tâm, hồ sơ mời sơ tuyển, hồ sơ mời thầu được phát hành sau 01 ngày kể từ khi thông báo mời quan tâm, thông báo mời sơ tuyển, thông báo mời thầu được đăng tải thành công trên Hệ thống mạng đấu thầu quốc gia
+B. Hồ sơ mời quan tâm, hồ sơ mời sơ tuyển, hồ sơ mời thầu được phát hành trước khi đăng tải thông báo mời quan tâm, thông báo mời sơ tuyển, thông báo mời thầu
+C. Hồ sơ mời quan tâm, hồ sơ mời sơ tuyển, hồ sơ mời thầu được phát hành sau 03 ngày kể từ khi thông báo mời quan tâm, thông báo mời sơ tuyển, thông báo mời thầu được đăng tải thành công trên Hệ thống mạng đấu thầu quốc gia
+D. Hồ sơ mời quan tâm, hồ sơ mời sơ tuyển, hồ sơ mời thầu được phát hành ngay sau khi đăng tải thành công thông báo mời quan tâm, thông báo mời sơ tuyển, thông báo mời thầu
+</t>
+  </si>
+  <si>
+    <t>A. Đấu thầu trước là việc thực hiện trước một số thủ tục trước khi dự án được phê duyệt đầu tư nhằm mục đích đẩy nhanh tiến độ thực hiện dự án, trừ gói thầu cần thực hiện trước khi phê duyệt dự án
+B. Đấu thầu trước là việc thực hiện các gói thầu thuộc giai đoạn chuẩn bị đầu tư
+C. Đấu thầu trước là việc lựa chọn nhà thầu không cần phê duyệt kế hoạch lựa chọn nhà thầu để đẩy nhanh tiến độ thực hiện
+D. Đấu thầu trước là việc thực hiện trước một số thủ tục trước khi dự án, dự toán mua sắm được phê duyệt nhằm mục đích đẩy nhanh tiến độ thực hiện dự án, dự toán mua sắm, trừ gói thầu cần thực hiện trước khi phê duyệt dự án</t>
+  </si>
+  <si>
+    <t>A. Chỉ Hiệp định Đối tác Toàn diện và Tiến bộ Xuyên Thái Bình Dương (CPTPP)
+B. Hiệp định CPTPP và Hiệp định thương mại tự do giữa Cộng hòa xã hội chủ nghĩa Việt Nam và Liên minh Châu Âu (EVFTA)
+C. Hiệp định CPTPP, Hiệp định EVFTA và Hiệp định Thương mại Tự do giữa Việt Nam và Liên hiệp Vương quốc Anh và Bắc Ailen (UKVFTA)
+D. Tất cả các hiệp định mà Việt Nam là thành viên</t>
+  </si>
+  <si>
+    <t>A. Nhà thầu chịu trách nhiệm theo dõi thông tin trên Hệ thống mạng đấu thầu quốc gia để cập nhật thông tin về việc sửa đổi E- HSMT, thay đổi thời điểm đóng thầu (nếu có) để làm cơ sở chuẩn bị E- HSDT
+B. Nhà thầu phải tự chịu trách nhiệm và chịu bất lợi trong quá trình tham dự thầu nếu không theo dõi, cập nhật thông tin sửa đổi E-HSMT, thời điểm đóng thầu trên Hệ thống mạng đấu thầu quốc gia trong quá trình tham dự thầu
+C. Hệ thống mạng đấu thầu quốc gia tự động gửi email thông báo về việc sửa đổi E-HSMT, thay đổi thời điểm đóng thầu (nếu có) cho các nhà thầu quan tâm đến gói thầu
+D. Các phương án trên đều đúng</t>
+  </si>
+  <si>
+    <t>A. Đối với lần chào giá đầu tiên nhà thầu nhập các trọng số là đơn giá của hàng hóa nhà thầu dự kiến xác định sẽ chào
+B.  Nhà thầu không được thay đổi trọng số của từng hạng mục hàng hóa trong quá trình chào giá
+C. Nhà thầu cần nghiên cứu công thức tính thành tiền và đơn giá dự thầu từ các trọng số để đề xuất các trọng số cho
+D. Nhà thầu phải điền các trọng số về đơn giá (N1, N2,...) của từng hạng mục</t>
+  </si>
+  <si>
+    <t>A. Không được yêu cầu về huy động nhân sự chủ chốt đối với phần công việc cung cấp hàng hóa
+B. Chỉ được yêu cầu về huy động nhân sự chủ chốt đối với các dịch vụ liên quan có yếu tố đặc thù, phức tạp cầnthiết phải có nhân sự có hiểu biết, nhiều kinh nghiệm đảm nhận.
+C. Được yêu cầu về huy động nhân sự chủ chốt đối với phần công việc cung cấp hàng hóa mà hàng hóa đó có tính đặc thù cần sự khẳng định của nhà sản xuất, nhà cung cấp để đảm bảo tính khả thi trong việc cung cấp hàng hóa
+D. Không được nêu yêu cầu huy động về nhân sự chủ chốt đối với hàng hóa thông dụng, sẵn có trên thị trường, không đòi hỏi nhân sự thực hiện dịch vụ liên quan phải có trình độ cao</t>
   </si>
 </sst>
 </file>
@@ -4579,16 +4567,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4596,10 +4584,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D2" s="6" t="s">
         <v>1</v>
@@ -4610,10 +4598,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>0</v>
@@ -4624,10 +4612,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>0</v>
@@ -4638,13 +4626,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>237</v>
-      </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4652,10 +4640,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>238</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>239</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>1</v>
@@ -4666,10 +4654,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>240</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>241</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>0</v>
@@ -4680,10 +4668,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>1</v>
@@ -4694,13 +4682,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4708,13 +4696,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="C10" s="14" t="s">
-        <v>245</v>
-      </c>
       <c r="D10" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4722,10 +4710,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>0</v>
@@ -4736,10 +4724,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>0</v>
@@ -4750,10 +4738,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>0</v>
@@ -4764,13 +4752,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>250</v>
-      </c>
       <c r="D14" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4778,27 +4766,27 @@
         <v>14</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>252</v>
-      </c>
       <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="93" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>15</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>2</v>
+        <v>775</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4806,13 +4794,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4820,10 +4808,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>254</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>255</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>1</v>
@@ -4834,13 +4822,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4848,13 +4836,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4862,10 +4850,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>1</v>
@@ -4876,13 +4864,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C22" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>260</v>
-      </c>
       <c r="D22" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4890,13 +4878,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C23" s="14" t="s">
         <v>261</v>
       </c>
-      <c r="C23" s="14" t="s">
-        <v>262</v>
-      </c>
       <c r="D23" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4904,13 +4892,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="C24" s="14" t="s">
-        <v>264</v>
-      </c>
       <c r="D24" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4918,24 +4906,24 @@
         <v>24</v>
       </c>
       <c r="B25" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>266</v>
-      </c>
       <c r="D25" s="17" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>25</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>267</v>
+        <v>776</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>1</v>
@@ -4946,10 +4934,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D27" s="18" t="s">
         <v>1</v>
@@ -4960,27 +4948,27 @@
         <v>27</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>272</v>
+        <v>772</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -4988,10 +4976,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="25" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="D30" s="20" t="s">
         <v>1</v>
@@ -5002,10 +4990,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>1</v>
@@ -5016,13 +5004,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5030,13 +5018,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5044,10 +5032,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>1</v>
@@ -5058,10 +5046,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>0</v>
@@ -5072,10 +5060,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D36" s="13" t="s">
         <v>0</v>
@@ -5086,13 +5074,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5100,10 +5088,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D38" s="13" t="s">
         <v>1</v>
@@ -5114,24 +5102,24 @@
         <v>38</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D39" s="12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A40" s="7">
         <v>39</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>285</v>
+        <v>773</v>
       </c>
       <c r="D40" s="17" t="s">
         <v>0</v>
@@ -5142,10 +5130,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D41" s="13" t="s">
         <v>1</v>
@@ -5156,10 +5144,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D42" s="13" t="s">
         <v>1</v>
@@ -5170,10 +5158,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D43" s="17" t="s">
         <v>1</v>
@@ -5184,10 +5172,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D44" s="13" t="s">
         <v>1</v>
@@ -5198,10 +5186,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>0</v>
@@ -5212,10 +5200,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D46" s="21" t="s">
         <v>0</v>
@@ -5226,13 +5214,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5240,10 +5228,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D48" s="13" t="s">
         <v>1</v>
@@ -5254,10 +5242,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D49" s="17" t="s">
         <v>1</v>
@@ -5268,10 +5256,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D50" s="8" t="s">
         <v>0</v>
@@ -5282,10 +5270,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>0</v>
@@ -5296,13 +5284,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5310,13 +5298,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5324,10 +5312,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>1</v>
@@ -5338,10 +5326,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>1</v>
@@ -5352,10 +5340,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>1</v>
@@ -5366,13 +5354,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5380,10 +5368,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>1</v>
@@ -5394,13 +5382,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5408,13 +5396,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5422,13 +5410,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5436,10 +5424,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D62" s="22" t="s">
         <v>0</v>
@@ -5450,13 +5438,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D63" s="22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5464,13 +5452,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D64" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5478,13 +5466,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5492,13 +5480,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5506,13 +5494,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5520,13 +5508,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D68" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5534,13 +5522,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C69" s="14" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D69" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5548,13 +5536,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -5562,10 +5550,10 @@
         <v>70</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>0</v>
@@ -5576,27 +5564,27 @@
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A73" s="4">
         <v>72</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C73" s="14" t="s">
-        <v>335</v>
+        <v>777</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5604,10 +5592,10 @@
         <v>73</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>1</v>
@@ -5618,10 +5606,10 @@
         <v>74</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C75" s="14" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>1</v>
@@ -5632,10 +5620,10 @@
         <v>75</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>1</v>
@@ -5646,10 +5634,10 @@
         <v>76</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C77" s="14" t="s">
-        <v>758</v>
+        <v>746</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>1</v>
@@ -5660,10 +5648,10 @@
         <v>77</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>1</v>
@@ -5674,13 +5662,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C79" s="14" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5688,13 +5676,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D80" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5702,10 +5690,10 @@
         <v>80</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C81" s="14" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="D81" s="19" t="s">
         <v>1</v>
@@ -5716,10 +5704,10 @@
         <v>81</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D82" s="20" t="s">
         <v>0</v>
@@ -5730,13 +5718,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C83" s="14" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5744,10 +5732,10 @@
         <v>83</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D84" s="19" t="s">
         <v>1</v>
@@ -5758,13 +5746,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C85" s="14" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D85" s="22" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5772,10 +5760,10 @@
         <v>85</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D86" s="20" t="s">
         <v>1</v>
@@ -5786,13 +5774,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="C87" s="14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5800,10 +5788,10 @@
         <v>87</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D88" s="20" t="s">
         <v>1</v>
@@ -5814,13 +5802,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C89" s="14" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5828,13 +5816,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="D90" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5842,10 +5830,10 @@
         <v>90</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="C91" s="14" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D91" s="18" t="s">
         <v>0</v>
@@ -5856,13 +5844,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="D92" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5870,10 +5858,10 @@
         <v>92</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D93" s="20" t="s">
         <v>1</v>
@@ -5884,10 +5872,10 @@
         <v>93</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D94" s="18" t="s">
         <v>0</v>
@@ -5898,10 +5886,10 @@
         <v>94</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D95" s="24" t="s">
         <v>1</v>
@@ -5912,13 +5900,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="D96" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5926,13 +5914,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D97" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5940,13 +5928,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C98" s="25" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="D98" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5954,13 +5942,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C99" s="25" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="D99" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5968,10 +5956,10 @@
         <v>99</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C100" s="25" t="s">
-        <v>759</v>
+        <v>747</v>
       </c>
       <c r="D100" s="26" t="s">
         <v>1</v>
@@ -5982,13 +5970,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="D101" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -5996,10 +5984,10 @@
         <v>101</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D102" s="22" t="s">
         <v>0</v>
@@ -6010,13 +5998,13 @@
         <v>102</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D103" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6024,10 +6012,10 @@
         <v>103</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="D104" s="24" t="s">
         <v>1</v>
@@ -6038,13 +6026,13 @@
         <v>104</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C105" s="14" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D105" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6052,13 +6040,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D106" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6066,13 +6054,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="D107" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6080,13 +6068,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6094,13 +6082,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6108,13 +6096,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="D110" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6122,13 +6110,13 @@
         <v>110</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="D111" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6136,13 +6124,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="D112" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6150,10 +6138,10 @@
         <v>112</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>761</v>
+        <v>749</v>
       </c>
       <c r="D113" s="19" t="s">
         <v>1</v>
@@ -6164,10 +6152,10 @@
         <v>113</v>
       </c>
       <c r="B114" s="30" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="C114" s="30" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>0</v>
@@ -6178,10 +6166,10 @@
         <v>114</v>
       </c>
       <c r="B115" s="30" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C115" s="30" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D115" s="15" t="s">
         <v>1</v>
@@ -6192,10 +6180,10 @@
         <v>115</v>
       </c>
       <c r="B116" s="30" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C116" s="30" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D116" s="12" t="s">
         <v>1</v>
@@ -6206,10 +6194,10 @@
         <v>116</v>
       </c>
       <c r="B117" s="30" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C117" s="30" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D117" s="12" t="s">
         <v>1</v>
@@ -6220,13 +6208,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C118" s="30" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6234,10 +6222,10 @@
         <v>118</v>
       </c>
       <c r="B119" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C119" s="30" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>0</v>
@@ -6248,13 +6236,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C120" s="30" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6262,10 +6250,10 @@
         <v>120</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D121" s="15" t="s">
         <v>1</v>
@@ -6276,10 +6264,10 @@
         <v>121</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>1</v>
@@ -6290,10 +6278,10 @@
         <v>122</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="D123" s="15" t="s">
         <v>1</v>
@@ -6304,10 +6292,10 @@
         <v>123</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>762</v>
+        <v>750</v>
       </c>
       <c r="D124" s="19" t="s">
         <v>0</v>
@@ -6318,10 +6306,10 @@
         <v>124</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="D125" s="21" t="s">
         <v>1</v>
@@ -6332,13 +6320,13 @@
         <v>125</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6346,38 +6334,38 @@
         <v>126</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="D127" s="21" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:4" ht="93" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
       <c r="A128" s="10">
         <v>127</v>
       </c>
       <c r="B128" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>408</v>
+        <v>778</v>
       </c>
       <c r="D128" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A129" s="4">
         <v>128</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>409</v>
+        <v>779</v>
       </c>
       <c r="D129" s="19" t="s">
         <v>1</v>
@@ -6388,10 +6376,10 @@
         <v>129</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="D130" s="22" t="s">
         <v>1</v>
@@ -6402,13 +6390,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D131" s="22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6416,10 +6404,10 @@
         <v>131</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="D132" s="19" t="s">
         <v>1</v>
@@ -6430,10 +6418,10 @@
         <v>132</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="D133" s="15" t="s">
         <v>1</v>
@@ -6444,27 +6432,27 @@
         <v>133</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="D134" s="31" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A135" s="7">
         <v>134</v>
       </c>
       <c r="B135" s="16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>417</v>
+        <v>774</v>
       </c>
       <c r="D135" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6472,10 +6460,10 @@
         <v>135</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="D136" s="21" t="s">
         <v>0</v>
@@ -6486,10 +6474,10 @@
         <v>136</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="D137" s="24" t="s">
         <v>0</v>
@@ -6500,10 +6488,10 @@
         <v>137</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="D138" s="22" t="s">
         <v>1</v>
@@ -6514,10 +6502,10 @@
         <v>138</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="D139" s="22" t="s">
         <v>0</v>
@@ -6528,13 +6516,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>754</v>
+        <v>742</v>
       </c>
       <c r="D140" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -6542,13 +6530,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="D141" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6556,10 +6544,10 @@
         <v>141</v>
       </c>
       <c r="B142" s="11" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="D142" s="22" t="s">
         <v>1</v>
@@ -6570,13 +6558,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="D143" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6584,13 +6572,13 @@
         <v>143</v>
       </c>
       <c r="B144" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="D144" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6598,13 +6586,13 @@
         <v>144</v>
       </c>
       <c r="B145" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>755</v>
+        <v>743</v>
       </c>
       <c r="D145" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6612,13 +6600,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="11" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="D146" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6626,10 +6614,10 @@
         <v>146</v>
       </c>
       <c r="B147" s="11" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="D147" s="24" t="s">
         <v>1</v>
@@ -6640,13 +6628,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="D148" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6654,13 +6642,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="D149" s="21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6668,13 +6656,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="D150" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -6682,13 +6670,13 @@
         <v>150</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D151" s="24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6696,10 +6684,10 @@
         <v>151</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="D152" s="22" t="s">
         <v>1</v>
@@ -6710,10 +6698,10 @@
         <v>152</v>
       </c>
       <c r="B153" s="11" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="D153" s="18" t="s">
         <v>0</v>
@@ -6724,10 +6712,10 @@
         <v>153</v>
       </c>
       <c r="B154" s="11" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="D154" s="18" t="s">
         <v>1</v>
@@ -6738,13 +6726,13 @@
         <v>154</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="D155" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6752,13 +6740,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="D156" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6766,13 +6754,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="C157" s="14" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="D157" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6780,10 +6768,10 @@
         <v>157</v>
       </c>
       <c r="B158" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="D158" s="18" t="s">
         <v>0</v>
@@ -6794,10 +6782,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="D159" s="18" t="s">
         <v>1</v>
@@ -6808,13 +6796,13 @@
         <v>159</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="D160" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6822,13 +6810,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="D161" s="23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6836,10 +6824,10 @@
         <v>161</v>
       </c>
       <c r="B162" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="D162" s="18" t="s">
         <v>0</v>
@@ -6850,13 +6838,13 @@
         <v>162</v>
       </c>
       <c r="B163" s="11" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C163" s="14" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="D163" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6864,10 +6852,10 @@
         <v>163</v>
       </c>
       <c r="B164" s="11" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="D164" s="24" t="s">
         <v>1</v>
@@ -6878,13 +6866,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="C165" s="14" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="D165" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6892,13 +6880,13 @@
         <v>165</v>
       </c>
       <c r="B166" s="11" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="D166" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6906,13 +6894,13 @@
         <v>166</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="D167" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6920,10 +6908,10 @@
         <v>167</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="D168" s="18" t="s">
         <v>0</v>
@@ -6934,10 +6922,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C169" s="14" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="D169" s="26" t="s">
         <v>1</v>
@@ -6948,13 +6936,13 @@
         <v>169</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="D170" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6962,13 +6950,13 @@
         <v>170</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="D171" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6976,13 +6964,13 @@
         <v>171</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="D172" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -6990,10 +6978,10 @@
         <v>172</v>
       </c>
       <c r="B173" s="11" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C173" s="14" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="D173" s="19" t="s">
         <v>1</v>
@@ -7004,13 +6992,13 @@
         <v>173</v>
       </c>
       <c r="B174" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="D174" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7018,13 +7006,13 @@
         <v>174</v>
       </c>
       <c r="B175" s="11" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="C175" s="14" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="D175" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7032,13 +7020,13 @@
         <v>175</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="D176" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7046,10 +7034,10 @@
         <v>176</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="C177" s="14" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="D177" s="19" t="s">
         <v>0</v>
@@ -7060,13 +7048,13 @@
         <v>177</v>
       </c>
       <c r="B178" s="11" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="D178" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7074,13 +7062,13 @@
         <v>178</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="C179" s="14" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="D179" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7088,13 +7076,13 @@
         <v>179</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="D180" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7102,10 +7090,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="C181" s="14" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="D181" s="19" t="s">
         <v>0</v>
@@ -7116,10 +7104,10 @@
         <v>181</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="D182" s="19" t="s">
         <v>1</v>
@@ -7130,13 +7118,13 @@
         <v>182</v>
       </c>
       <c r="B183" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C183" s="14" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="D183" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7144,13 +7132,13 @@
         <v>183</v>
       </c>
       <c r="B184" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="D184" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7158,10 +7146,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C185" s="14" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="D185" s="19" t="s">
         <v>0</v>
@@ -7172,13 +7160,13 @@
         <v>185</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
       <c r="D186" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7186,13 +7174,13 @@
         <v>186</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="C187" s="14" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="D187" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7200,10 +7188,10 @@
         <v>187</v>
       </c>
       <c r="B188" s="11" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="D188" s="18" t="s">
         <v>1</v>
@@ -7214,13 +7202,13 @@
         <v>188</v>
       </c>
       <c r="B189" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C189" s="14" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="D189" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7228,10 +7216,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="11" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="D190" s="22" t="s">
         <v>1</v>
@@ -7242,10 +7230,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="11" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="C191" s="14" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="D191" s="18" t="s">
         <v>0</v>
@@ -7256,10 +7244,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="11" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="C192" s="14" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="D192" s="18" t="s">
         <v>1</v>
@@ -7270,10 +7258,10 @@
         <v>192</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C193" s="14" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="D193" s="18" t="s">
         <v>0</v>
@@ -7284,10 +7272,10 @@
         <v>193</v>
       </c>
       <c r="B194" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="D194" s="15" t="s">
         <v>1</v>
@@ -7298,10 +7286,10 @@
         <v>194</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="C195" s="14" t="s">
-        <v>772</v>
+        <v>760</v>
       </c>
       <c r="D195" s="19" t="s">
         <v>1</v>
@@ -7312,13 +7300,13 @@
         <v>195</v>
       </c>
       <c r="B196" s="11" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="C196" s="14" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="D196" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7326,10 +7314,10 @@
         <v>196</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C197" s="14" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="D197" s="19" t="s">
         <v>1</v>
@@ -7340,10 +7328,10 @@
         <v>197</v>
       </c>
       <c r="B198" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>773</v>
+        <v>761</v>
       </c>
       <c r="D198" s="18" t="s">
         <v>0</v>
@@ -7354,10 +7342,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="11" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="C199" s="14" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="D199" s="18" t="s">
         <v>0</v>
@@ -7368,10 +7356,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="D200" s="19" t="s">
         <v>1</v>
@@ -7382,10 +7370,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="11" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="C201" s="14" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="D201" s="24" t="s">
         <v>1</v>
@@ -7396,13 +7384,13 @@
         <v>201</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="D202" s="23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7410,13 +7398,13 @@
         <v>202</v>
       </c>
       <c r="B203" s="16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C203" s="14" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="D203" s="24" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7424,13 +7412,13 @@
         <v>203</v>
       </c>
       <c r="B204" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="D204" s="24" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -7438,10 +7426,10 @@
         <v>204</v>
       </c>
       <c r="B205" s="11" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="C205" s="14" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="D205" s="18" t="s">
         <v>0</v>
@@ -7452,10 +7440,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="11" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="C206" s="14" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="D206" s="18" t="s">
         <v>1</v>
@@ -7466,13 +7454,13 @@
         <v>206</v>
       </c>
       <c r="B207" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C207" s="14" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="D207" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7480,10 +7468,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="11" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="D208" s="18" t="s">
         <v>1</v>
@@ -7494,10 +7482,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="11" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="C209" s="14" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="D209" s="18" t="s">
         <v>1</v>
@@ -7508,10 +7496,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="11" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="D210" s="18" t="s">
         <v>0</v>
@@ -7522,13 +7510,13 @@
         <v>210</v>
       </c>
       <c r="B211" s="11" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="C211" s="14" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="D211" s="32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7536,10 +7524,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="11" t="s">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="C212" s="14" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="D212" s="21" t="s">
         <v>0</v>
@@ -7550,13 +7538,13 @@
         <v>212</v>
       </c>
       <c r="B213" s="11" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="C213" s="14" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="D213" s="32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7564,10 +7552,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="D214" s="21" t="s">
         <v>0</v>
@@ -7578,13 +7566,13 @@
         <v>214</v>
       </c>
       <c r="B215" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C215" s="14" t="s">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="D215" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7592,13 +7580,13 @@
         <v>215</v>
       </c>
       <c r="B216" s="11" t="s">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C216" s="14" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="D216" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7606,10 +7594,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C217" s="14" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="D217" s="18" t="s">
         <v>0</v>
@@ -7620,13 +7608,13 @@
         <v>217</v>
       </c>
       <c r="B218" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="D218" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7634,13 +7622,13 @@
         <v>218</v>
       </c>
       <c r="B219" s="11" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C219" s="14" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="D219" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7648,13 +7636,13 @@
         <v>219</v>
       </c>
       <c r="B220" s="11" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="D220" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7662,13 +7650,13 @@
         <v>220</v>
       </c>
       <c r="B221" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C221" s="14" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="D221" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7676,10 +7664,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="D222" s="18" t="s">
         <v>0</v>
@@ -7690,10 +7678,10 @@
         <v>222</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C223" s="14" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="D223" s="18" t="s">
         <v>0</v>
@@ -7704,10 +7692,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="D224" s="18" t="s">
         <v>0</v>
@@ -7718,10 +7706,10 @@
         <v>224</v>
       </c>
       <c r="B225" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C225" s="14" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="D225" s="18" t="s">
         <v>0</v>
@@ -7732,10 +7720,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="11" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="D226" s="18" t="s">
         <v>1</v>
@@ -7746,13 +7734,13 @@
         <v>226</v>
       </c>
       <c r="B227" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C227" s="14" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="D227" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -7760,10 +7748,10 @@
         <v>227</v>
       </c>
       <c r="B228" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="D228" s="18" t="s">
         <v>0</v>
@@ -7774,13 +7762,13 @@
         <v>228</v>
       </c>
       <c r="B229" s="11" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="C229" s="14" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="D229" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7788,13 +7776,13 @@
         <v>229</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="D230" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7802,10 +7790,10 @@
         <v>230</v>
       </c>
       <c r="B231" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C231" s="14" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="D231" s="19" t="s">
         <v>1</v>
@@ -7816,10 +7804,10 @@
         <v>231</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C232" s="14" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
       <c r="D232" s="19" t="s">
         <v>0</v>
@@ -7830,13 +7818,13 @@
         <v>232</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C233" s="14" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="D233" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7844,10 +7832,10 @@
         <v>233</v>
       </c>
       <c r="B234" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="D234" s="18" t="s">
         <v>0</v>
@@ -7858,13 +7846,13 @@
         <v>234</v>
       </c>
       <c r="B235" s="11" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="C235" s="14" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="D235" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7872,10 +7860,10 @@
         <v>235</v>
       </c>
       <c r="B236" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C236" s="11" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="D236" s="20" t="s">
         <v>0</v>
@@ -7886,10 +7874,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="16" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="C237" s="14" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>0</v>
@@ -7900,13 +7888,13 @@
         <v>237</v>
       </c>
       <c r="B238" s="11" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="D238" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7914,10 +7902,10 @@
         <v>238</v>
       </c>
       <c r="B239" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C239" s="14" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>0</v>
@@ -7928,10 +7916,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="11" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="C240" s="14" t="s">
-        <v>775</v>
+        <v>763</v>
       </c>
       <c r="D240" s="20" t="s">
         <v>0</v>
@@ -7942,10 +7930,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C241" s="14" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
       <c r="D241" s="21" t="s">
         <v>1</v>
@@ -7956,10 +7944,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="C242" s="14" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="D242" s="33" t="s">
         <v>0</v>
@@ -7970,13 +7958,13 @@
         <v>242</v>
       </c>
       <c r="B243" s="11" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="C243" s="25" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="D243" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -7984,10 +7972,10 @@
         <v>243</v>
       </c>
       <c r="B244" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="D244" s="18" t="s">
         <v>1</v>
@@ -7998,13 +7986,13 @@
         <v>244</v>
       </c>
       <c r="B245" s="11" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="C245" s="14" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="D245" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8012,13 +8000,13 @@
         <v>245</v>
       </c>
       <c r="B246" s="11" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="D246" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8026,10 +8014,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="C247" s="14" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="D247" s="18" t="s">
         <v>1</v>
@@ -8040,13 +8028,13 @@
         <v>247</v>
       </c>
       <c r="B248" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="D248" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8054,13 +8042,13 @@
         <v>248</v>
       </c>
       <c r="B249" s="11" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="C249" s="14" t="s">
-        <v>778</v>
+        <v>766</v>
       </c>
       <c r="D249" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8068,10 +8056,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="D250" s="18" t="s">
         <v>0</v>
@@ -8082,13 +8070,13 @@
         <v>250</v>
       </c>
       <c r="B251" s="11" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="C251" s="14" t="s">
-        <v>779</v>
+        <v>767</v>
       </c>
       <c r="D251" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8096,13 +8084,13 @@
         <v>251</v>
       </c>
       <c r="B252" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C252" s="14" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="D252" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8110,13 +8098,13 @@
         <v>252</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C253" s="14" t="s">
-        <v>780</v>
+        <v>768</v>
       </c>
       <c r="D253" s="20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8124,10 +8112,10 @@
         <v>253</v>
       </c>
       <c r="B254" s="16" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="D254" s="20" t="s">
         <v>1</v>
@@ -8138,13 +8126,13 @@
         <v>254</v>
       </c>
       <c r="B255" s="11" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C255" s="14" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="D255" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8152,13 +8140,13 @@
         <v>255</v>
       </c>
       <c r="B256" s="11" t="s">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="C256" s="14" t="s">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="D256" s="18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8166,10 +8154,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C257" s="14" t="s">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="D257" s="19" t="s">
         <v>0</v>
@@ -8180,10 +8168,10 @@
         <v>257</v>
       </c>
       <c r="B258" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="D258" s="18" t="s">
         <v>0</v>
@@ -8194,13 +8182,13 @@
         <v>258</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="C259" s="14" t="s">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="D259" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="124" x14ac:dyDescent="0.35">
@@ -8208,10 +8196,10 @@
         <v>259</v>
       </c>
       <c r="B260" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="D260" s="20" t="s">
         <v>1</v>
@@ -8222,10 +8210,10 @@
         <v>260</v>
       </c>
       <c r="B261" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C261" s="14" t="s">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="D261" s="18" t="s">
         <v>0</v>
@@ -8236,24 +8224,24 @@
         <v>261</v>
       </c>
       <c r="B262" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C262" s="14" t="s">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="D262" s="19" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A263" s="28">
         <v>262</v>
       </c>
       <c r="B263" s="34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C263" s="25" t="s">
-        <v>592</v>
+        <v>781</v>
       </c>
       <c r="D263" s="21" t="s">
         <v>0</v>
@@ -8264,10 +8252,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="30" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="C264" s="25" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="D264" s="19" t="s">
         <v>1</v>
@@ -8278,10 +8266,10 @@
         <v>264</v>
       </c>
       <c r="B265" s="34" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C265" s="25" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="D265" s="18" t="s">
         <v>1</v>
@@ -8292,10 +8280,10 @@
         <v>265</v>
       </c>
       <c r="B266" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C266" s="14" t="s">
-        <v>781</v>
+        <v>769</v>
       </c>
       <c r="D266" s="35" t="s">
         <v>1</v>
@@ -8306,10 +8294,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="11" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="C267" s="14" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="D267" s="18" t="s">
         <v>0</v>
@@ -8320,10 +8308,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="11" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="C268" s="14" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="D268" s="18" t="s">
         <v>1</v>
@@ -8334,10 +8322,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="11" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="C269" s="14" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="D269" s="18" t="s">
         <v>1</v>
@@ -8348,10 +8336,10 @@
         <v>269</v>
       </c>
       <c r="B270" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C270" s="14" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="D270" s="18" t="s">
         <v>1</v>
@@ -8362,10 +8350,10 @@
         <v>270</v>
       </c>
       <c r="B271" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C271" s="14" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="D271" s="18" t="s">
         <v>0</v>
@@ -8376,10 +8364,10 @@
         <v>271</v>
       </c>
       <c r="B272" s="11" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="C272" s="14" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="D272" s="18" t="s">
         <v>0</v>
@@ -8390,10 +8378,10 @@
         <v>272</v>
       </c>
       <c r="B273" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C273" s="14" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="D273" s="15" t="s">
         <v>0</v>
@@ -8404,13 +8392,13 @@
         <v>273</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C274" s="14" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="D274" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8418,10 +8406,10 @@
         <v>274</v>
       </c>
       <c r="B275" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C275" s="14" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="D275" s="18" t="s">
         <v>1</v>
@@ -8432,10 +8420,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="11" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="C276" s="14" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="D276" s="36" t="s">
         <v>0</v>
@@ -8446,13 +8434,13 @@
         <v>276</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="C277" s="14" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="D277" s="36" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8460,10 +8448,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="11" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="C278" s="14" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="D278" s="36" t="s">
         <v>0</v>
@@ -8474,13 +8462,13 @@
         <v>278</v>
       </c>
       <c r="B279" s="11" t="s">
-        <v>753</v>
+        <v>741</v>
       </c>
       <c r="C279" s="14" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="D279" s="36" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8488,13 +8476,13 @@
         <v>279</v>
       </c>
       <c r="B280" s="11" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="C280" s="14" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="D280" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8502,13 +8490,13 @@
         <v>280</v>
       </c>
       <c r="B281" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C281" s="14" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="D281" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8516,13 +8504,13 @@
         <v>281</v>
       </c>
       <c r="B282" s="11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C282" s="14" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="D282" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8530,13 +8518,13 @@
         <v>282</v>
       </c>
       <c r="B283" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C283" s="14" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="D283" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8544,10 +8532,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="D284" s="19" t="s">
         <v>0</v>
@@ -8558,13 +8546,13 @@
         <v>284</v>
       </c>
       <c r="B285" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C285" s="14" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="D285" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8572,13 +8560,13 @@
         <v>285</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="D286" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8586,10 +8574,10 @@
         <v>286</v>
       </c>
       <c r="B287" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C287" s="14" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="D287" s="19" t="s">
         <v>0</v>
@@ -8600,13 +8588,13 @@
         <v>287</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C288" s="14" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="D288" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8614,13 +8602,13 @@
         <v>288</v>
       </c>
       <c r="B289" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C289" s="25" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="D289" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8628,13 +8616,13 @@
         <v>289</v>
       </c>
       <c r="B290" s="11" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C290" s="14" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="D290" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8642,13 +8630,13 @@
         <v>290</v>
       </c>
       <c r="B291" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C291" s="14" t="s">
-        <v>782</v>
+        <v>770</v>
       </c>
       <c r="D291" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8656,13 +8644,13 @@
         <v>291</v>
       </c>
       <c r="B292" s="11" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="C292" s="14" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="D292" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8670,13 +8658,13 @@
         <v>292</v>
       </c>
       <c r="B293" s="11" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="C293" s="14" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="D293" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="93" x14ac:dyDescent="0.35">
@@ -8684,13 +8672,13 @@
         <v>293</v>
       </c>
       <c r="B294" s="11" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="C294" s="14" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="D294" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8698,13 +8686,13 @@
         <v>294</v>
       </c>
       <c r="B295" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C295" s="14" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="D295" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8712,13 +8700,13 @@
         <v>295</v>
       </c>
       <c r="B296" s="11" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C296" s="14" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="D296" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -8726,10 +8714,10 @@
         <v>296</v>
       </c>
       <c r="B297" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C297" s="14" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="D297" s="19" t="s">
         <v>0</v>
@@ -8740,10 +8728,10 @@
         <v>297</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C298" s="14" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="D298" s="19" t="s">
         <v>1</v>
@@ -8754,10 +8742,10 @@
         <v>298</v>
       </c>
       <c r="B299" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C299" s="14" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="D299" s="19" t="s">
         <v>0</v>
@@ -8768,10 +8756,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="11" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="C300" s="14" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="D300" s="19" t="s">
         <v>1</v>
@@ -8782,13 +8770,13 @@
         <v>300</v>
       </c>
       <c r="B301" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C301" s="14" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="D301" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8796,10 +8784,10 @@
         <v>301</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="C302" s="14" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="D302" s="19" t="s">
         <v>0</v>
@@ -8810,13 +8798,13 @@
         <v>302</v>
       </c>
       <c r="B303" s="11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C303" s="14" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="D303" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8824,13 +8812,13 @@
         <v>303</v>
       </c>
       <c r="B304" s="11" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C304" s="14" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="D304" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8838,13 +8826,13 @@
         <v>304</v>
       </c>
       <c r="B305" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C305" s="14" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="D305" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8852,13 +8840,13 @@
         <v>305</v>
       </c>
       <c r="B306" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C306" s="14" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="D306" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8866,13 +8854,13 @@
         <v>306</v>
       </c>
       <c r="B307" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C307" s="14" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="D307" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8880,13 +8868,13 @@
         <v>307</v>
       </c>
       <c r="B308" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C308" s="14" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="D308" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8894,13 +8882,13 @@
         <v>308</v>
       </c>
       <c r="B309" s="11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C309" s="14" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="D309" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8908,13 +8896,13 @@
         <v>309</v>
       </c>
       <c r="B310" s="11" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="C310" s="14" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="D310" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8922,13 +8910,13 @@
         <v>310</v>
       </c>
       <c r="B311" s="11" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="C311" s="14" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="D311" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8936,13 +8924,13 @@
         <v>311</v>
       </c>
       <c r="B312" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C312" s="14" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="D312" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8950,13 +8938,13 @@
         <v>312</v>
       </c>
       <c r="B313" s="11" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C313" s="14" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="D313" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8964,13 +8952,13 @@
         <v>313</v>
       </c>
       <c r="B314" s="11" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C314" s="14" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="D314" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -8978,10 +8966,10 @@
         <v>314</v>
       </c>
       <c r="B315" s="11" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C315" s="14" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="D315" s="19" t="s">
         <v>0</v>
@@ -8992,10 +8980,10 @@
         <v>315</v>
       </c>
       <c r="B316" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C316" s="14" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="D316" s="19" t="s">
         <v>1</v>
@@ -9006,10 +8994,10 @@
         <v>316</v>
       </c>
       <c r="B317" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C317" s="14" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="D317" s="18" t="s">
         <v>1</v>
@@ -9020,13 +9008,13 @@
         <v>317</v>
       </c>
       <c r="B318" s="11" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="C318" s="14" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="D318" s="20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9034,27 +9022,27 @@
         <v>318</v>
       </c>
       <c r="B319" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C319" s="14" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="D319" s="19" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A320" s="10">
         <v>319</v>
       </c>
       <c r="B320" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C320" s="14" t="s">
-        <v>664</v>
+        <v>780</v>
       </c>
       <c r="D320" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9062,13 +9050,13 @@
         <v>320</v>
       </c>
       <c r="B321" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C321" s="14" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -9076,10 +9064,10 @@
         <v>321</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C322" s="14" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
       <c r="D322" s="23" t="s">
         <v>0</v>
@@ -9090,13 +9078,13 @@
         <v>322</v>
       </c>
       <c r="B323" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C323" s="14" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="D323" s="22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9104,13 +9092,13 @@
         <v>323</v>
       </c>
       <c r="B324" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C324" s="14" t="s">
-        <v>668</v>
+        <v>658</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9118,10 +9106,10 @@
         <v>324</v>
       </c>
       <c r="B325" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C325" s="14" t="s">
-        <v>669</v>
+        <v>659</v>
       </c>
       <c r="D325" s="15" t="s">
         <v>1</v>
@@ -9132,13 +9120,13 @@
         <v>325</v>
       </c>
       <c r="B326" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C326" s="14" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="D326" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9146,13 +9134,13 @@
         <v>326</v>
       </c>
       <c r="B327" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C327" s="14" t="s">
-        <v>671</v>
+        <v>661</v>
       </c>
       <c r="D327" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9160,13 +9148,13 @@
         <v>327</v>
       </c>
       <c r="B328" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C328" s="14" t="s">
-        <v>672</v>
+        <v>662</v>
       </c>
       <c r="D328" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9174,13 +9162,13 @@
         <v>328</v>
       </c>
       <c r="B329" s="11" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C329" s="14" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="D329" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9188,13 +9176,13 @@
         <v>329</v>
       </c>
       <c r="B330" s="11" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="C330" s="14" t="s">
-        <v>676</v>
+        <v>666</v>
       </c>
       <c r="D330" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9202,10 +9190,10 @@
         <v>330</v>
       </c>
       <c r="B331" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C331" s="14" t="s">
-        <v>677</v>
+        <v>667</v>
       </c>
       <c r="D331" s="19" t="s">
         <v>0</v>
@@ -9216,10 +9204,10 @@
         <v>331</v>
       </c>
       <c r="B332" s="11" t="s">
-        <v>678</v>
+        <v>668</v>
       </c>
       <c r="C332" s="14" t="s">
-        <v>679</v>
+        <v>669</v>
       </c>
       <c r="D332" s="23" t="s">
         <v>0</v>
@@ -9230,13 +9218,13 @@
         <v>332</v>
       </c>
       <c r="B333" s="11" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C333" s="14" t="s">
-        <v>680</v>
+        <v>670</v>
       </c>
       <c r="D333" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9244,13 +9232,13 @@
         <v>333</v>
       </c>
       <c r="B334" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C334" s="14" t="s">
-        <v>681</v>
+        <v>671</v>
       </c>
       <c r="D334" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9258,13 +9246,13 @@
         <v>334</v>
       </c>
       <c r="B335" s="11" t="s">
-        <v>682</v>
+        <v>672</v>
       </c>
       <c r="C335" s="14" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="D335" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9272,13 +9260,13 @@
         <v>335</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="C336" s="14" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
       <c r="D336" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9286,13 +9274,13 @@
         <v>336</v>
       </c>
       <c r="B337" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C337" s="14" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
       <c r="D337" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9300,10 +9288,10 @@
         <v>337</v>
       </c>
       <c r="B338" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C338" s="14" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
       <c r="D338" s="19" t="s">
         <v>1</v>
@@ -9314,13 +9302,13 @@
         <v>338</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C339" s="14" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="D339" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9328,10 +9316,10 @@
         <v>339</v>
       </c>
       <c r="B340" s="11" t="s">
-        <v>689</v>
+        <v>679</v>
       </c>
       <c r="C340" s="14" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="D340" s="19" t="s">
         <v>1</v>
@@ -9342,10 +9330,10 @@
         <v>340</v>
       </c>
       <c r="B341" s="11" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C341" s="14" t="s">
-        <v>691</v>
+        <v>681</v>
       </c>
       <c r="D341" s="19" t="s">
         <v>1</v>
@@ -9356,10 +9344,10 @@
         <v>341</v>
       </c>
       <c r="B342" s="11" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C342" s="11" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="D342" s="19" t="s">
         <v>0</v>
@@ -9370,10 +9358,10 @@
         <v>342</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C343" s="11" t="s">
-        <v>693</v>
+        <v>683</v>
       </c>
       <c r="D343" s="19" t="s">
         <v>1</v>
@@ -9384,10 +9372,10 @@
         <v>343</v>
       </c>
       <c r="B344" s="11" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C344" s="11" t="s">
-        <v>763</v>
+        <v>751</v>
       </c>
       <c r="D344" s="19" t="s">
         <v>0</v>
@@ -9398,13 +9386,13 @@
         <v>344</v>
       </c>
       <c r="B345" s="11" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C345" s="11" t="s">
-        <v>694</v>
+        <v>684</v>
       </c>
       <c r="D345" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9412,13 +9400,13 @@
         <v>345</v>
       </c>
       <c r="B346" s="11" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="C346" s="11" t="s">
-        <v>696</v>
+        <v>686</v>
       </c>
       <c r="D346" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9426,10 +9414,10 @@
         <v>346</v>
       </c>
       <c r="B347" s="11" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C347" s="11" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
       <c r="D347" s="19" t="s">
         <v>0</v>
@@ -9440,10 +9428,10 @@
         <v>347</v>
       </c>
       <c r="B348" s="11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C348" s="11" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
       <c r="D348" s="19" t="s">
         <v>0</v>
@@ -9454,10 +9442,10 @@
         <v>348</v>
       </c>
       <c r="B349" s="11" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C349" s="11" t="s">
-        <v>699</v>
+        <v>689</v>
       </c>
       <c r="D349" s="19" t="s">
         <v>0</v>
@@ -9468,10 +9456,10 @@
         <v>349</v>
       </c>
       <c r="B350" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C350" s="11" t="s">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="D350" s="15" t="s">
         <v>1</v>
@@ -9482,10 +9470,10 @@
         <v>350</v>
       </c>
       <c r="B351" s="11" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
       <c r="C351" s="11" t="s">
-        <v>702</v>
+        <v>692</v>
       </c>
       <c r="D351" s="19" t="s">
         <v>1</v>
@@ -9496,13 +9484,13 @@
         <v>351</v>
       </c>
       <c r="B352" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C352" s="11" t="s">
-        <v>703</v>
+        <v>693</v>
       </c>
       <c r="D352" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9510,10 +9498,10 @@
         <v>352</v>
       </c>
       <c r="B353" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C353" s="11" t="s">
-        <v>704</v>
+        <v>694</v>
       </c>
       <c r="D353" s="19" t="s">
         <v>0</v>
@@ -9524,13 +9512,13 @@
         <v>353</v>
       </c>
       <c r="B354" s="11" t="s">
-        <v>705</v>
+        <v>695</v>
       </c>
       <c r="C354" s="11" t="s">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="D354" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9538,10 +9526,10 @@
         <v>354</v>
       </c>
       <c r="B355" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C355" s="11" t="s">
-        <v>707</v>
+        <v>697</v>
       </c>
       <c r="D355" s="19" t="s">
         <v>0</v>
@@ -9552,10 +9540,10 @@
         <v>355</v>
       </c>
       <c r="B356" s="11" t="s">
-        <v>708</v>
+        <v>698</v>
       </c>
       <c r="C356" s="11" t="s">
-        <v>709</v>
+        <v>699</v>
       </c>
       <c r="D356" s="19" t="s">
         <v>1</v>
@@ -9566,13 +9554,13 @@
         <v>356</v>
       </c>
       <c r="B357" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C357" s="11" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="D357" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9580,13 +9568,13 @@
         <v>357</v>
       </c>
       <c r="B358" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C358" s="11" t="s">
-        <v>711</v>
+        <v>782</v>
       </c>
       <c r="D358" s="34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9594,13 +9582,13 @@
         <v>358</v>
       </c>
       <c r="B359" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C359" s="30" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="D359" s="30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9608,13 +9596,13 @@
         <v>359</v>
       </c>
       <c r="B360" s="11" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="C360" s="11" t="s">
-        <v>714</v>
+        <v>703</v>
       </c>
       <c r="D360" s="19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9622,13 +9610,13 @@
         <v>360</v>
       </c>
       <c r="B361" s="30" t="s">
-        <v>715</v>
+        <v>704</v>
       </c>
       <c r="C361" s="30" t="s">
-        <v>716</v>
+        <v>705</v>
       </c>
       <c r="D361" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9636,13 +9624,13 @@
         <v>361</v>
       </c>
       <c r="B362" s="30" t="s">
-        <v>717</v>
+        <v>706</v>
       </c>
       <c r="C362" s="30" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="D362" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9650,13 +9638,13 @@
         <v>362</v>
       </c>
       <c r="B363" s="30" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C363" s="30" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="D363" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9664,10 +9652,10 @@
         <v>363</v>
       </c>
       <c r="B364" s="30" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C364" s="30" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="D364" s="15" t="s">
         <v>0</v>
@@ -9678,27 +9666,27 @@
         <v>364</v>
       </c>
       <c r="B365" s="30" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C365" s="30" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="D365" s="15" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:4" ht="62" x14ac:dyDescent="0.35">
       <c r="A366" s="10">
         <v>365</v>
       </c>
       <c r="B366" s="30" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C366" s="30" t="s">
-        <v>722</v>
+        <v>783</v>
       </c>
       <c r="D366" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9706,13 +9694,13 @@
         <v>366</v>
       </c>
       <c r="B367" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C367" s="30" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="D367" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9720,10 +9708,10 @@
         <v>367</v>
       </c>
       <c r="B368" s="11" t="s">
-        <v>724</v>
+        <v>712</v>
       </c>
       <c r="C368" s="30" t="s">
-        <v>725</v>
+        <v>713</v>
       </c>
       <c r="D368" s="15" t="s">
         <v>0</v>
@@ -9734,13 +9722,13 @@
         <v>368</v>
       </c>
       <c r="B369" s="30" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C369" s="30" t="s">
-        <v>726</v>
+        <v>714</v>
       </c>
       <c r="D369" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -9748,13 +9736,13 @@
         <v>369</v>
       </c>
       <c r="B370" s="30" t="s">
-        <v>727</v>
+        <v>715</v>
       </c>
       <c r="C370" s="30" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="D370" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="77.5" x14ac:dyDescent="0.35">
@@ -9762,10 +9750,10 @@
         <v>370</v>
       </c>
       <c r="B371" s="30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C371" s="30" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="D371" s="15" t="s">
         <v>1</v>
@@ -9776,10 +9764,10 @@
         <v>371</v>
       </c>
       <c r="B372" s="30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C372" s="30" t="s">
-        <v>730</v>
+        <v>718</v>
       </c>
       <c r="D372" s="15" t="s">
         <v>0</v>
@@ -9790,10 +9778,10 @@
         <v>372</v>
       </c>
       <c r="B373" s="30" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C373" s="30" t="s">
-        <v>731</v>
+        <v>719</v>
       </c>
       <c r="D373" s="15" t="s">
         <v>1</v>
@@ -9804,10 +9792,10 @@
         <v>373</v>
       </c>
       <c r="B374" s="30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C374" s="30" t="s">
-        <v>732</v>
+        <v>720</v>
       </c>
       <c r="D374" s="15" t="s">
         <v>0</v>
@@ -9818,10 +9806,10 @@
         <v>374</v>
       </c>
       <c r="B375" s="30" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C375" s="30" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="D375" s="15" t="s">
         <v>1</v>
@@ -9832,10 +9820,10 @@
         <v>375</v>
       </c>
       <c r="B376" s="11" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="C376" s="30" t="s">
-        <v>735</v>
+        <v>723</v>
       </c>
       <c r="D376" s="15" t="s">
         <v>0</v>
@@ -9846,13 +9834,13 @@
         <v>376</v>
       </c>
       <c r="B377" s="30" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C377" s="30" t="s">
-        <v>736</v>
+        <v>724</v>
       </c>
       <c r="D377" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9860,13 +9848,13 @@
         <v>377</v>
       </c>
       <c r="B378" s="30" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C378" s="30" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="D378" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9874,13 +9862,13 @@
         <v>378</v>
       </c>
       <c r="B379" s="30" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C379" s="30" t="s">
-        <v>738</v>
+        <v>726</v>
       </c>
       <c r="D379" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9888,10 +9876,10 @@
         <v>379</v>
       </c>
       <c r="B380" s="30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C380" s="30" t="s">
-        <v>739</v>
+        <v>727</v>
       </c>
       <c r="D380" s="15" t="s">
         <v>0</v>
@@ -9902,13 +9890,13 @@
         <v>380</v>
       </c>
       <c r="B381" s="30" t="s">
-        <v>740</v>
+        <v>728</v>
       </c>
       <c r="C381" s="30" t="s">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="D381" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9916,10 +9904,10 @@
         <v>381</v>
       </c>
       <c r="B382" s="30" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C382" s="30" t="s">
-        <v>742</v>
+        <v>730</v>
       </c>
       <c r="D382" s="15" t="s">
         <v>1</v>
@@ -9930,10 +9918,10 @@
         <v>382</v>
       </c>
       <c r="B383" s="30" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C383" s="30" t="s">
-        <v>743</v>
+        <v>731</v>
       </c>
       <c r="D383" s="15" t="s">
         <v>0</v>
@@ -9944,10 +9932,10 @@
         <v>383</v>
       </c>
       <c r="B384" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C384" s="30" t="s">
-        <v>744</v>
+        <v>732</v>
       </c>
       <c r="D384" s="15" t="s">
         <v>0</v>
@@ -9958,10 +9946,10 @@
         <v>384</v>
       </c>
       <c r="B385" s="30" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C385" s="30" t="s">
-        <v>783</v>
+        <v>771</v>
       </c>
       <c r="D385" s="15" t="s">
         <v>1</v>
@@ -9972,13 +9960,13 @@
         <v>385</v>
       </c>
       <c r="B386" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C386" s="11" t="s">
-        <v>745</v>
+        <v>733</v>
       </c>
       <c r="D386" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -9986,13 +9974,13 @@
         <v>386</v>
       </c>
       <c r="B387" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C387" s="11" t="s">
-        <v>746</v>
+        <v>734</v>
       </c>
       <c r="D387" s="15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -10000,13 +9988,13 @@
         <v>387</v>
       </c>
       <c r="B388" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C388" s="11" t="s">
-        <v>747</v>
+        <v>735</v>
       </c>
       <c r="D388" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="62" x14ac:dyDescent="0.35">
@@ -10014,10 +10002,10 @@
         <v>388</v>
       </c>
       <c r="B389" s="11" t="s">
-        <v>748</v>
+        <v>736</v>
       </c>
       <c r="C389" s="11" t="s">
-        <v>749</v>
+        <v>737</v>
       </c>
       <c r="D389" s="19" t="s">
         <v>1</v>
@@ -10028,10 +10016,10 @@
         <v>389</v>
       </c>
       <c r="B390" s="11" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="C390" s="11" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
       <c r="D390" s="19" t="s">
         <v>1</v>
@@ -10042,10 +10030,10 @@
         <v>390</v>
       </c>
       <c r="B391" s="11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C391" s="11" t="s">
-        <v>752</v>
+        <v>740</v>
       </c>
       <c r="D391" s="19" t="s">
         <v>1</v>

--- a/data/Ngan-Hang-Cau-Hoi.xlsx
+++ b/data/Ngan-Hang-Cau-Hoi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9f54d0bdb7235122/Documents/My App/trac-nghiem-luat-dau-thau/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA9AAE09-2CF5-46CB-A30D-32E79182B449}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C6706F-7B15-414B-84B2-FA000E4A3D95}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0822E189-CD53-41B9-B216-EFA7EF505EBC}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="19200" windowHeight="11170" xr2:uid="{0822E189-CD53-41B9-B216-EFA7EF505EBC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1763,13 +1763,6 @@
 D. Phương án A và B đều đúng</t>
   </si>
   <si>
-    <t>A. Nhà thầu đã ký kết thỏa thuận khung phải thực hiện biện pháp bảo đảm thực hiện hợp đồng trước hoặc cùng thời điểm hợp đồng có hiệu lực cho đơn vị mua sắm tập trung
-B. Nhà thầu đã ký kết thỏa thuận khung phải thực hiện biện pháp bảo đảm thực hiện hợp đồng trước hoặc cùng thời điểm hợp đồng có hiệu lực cho đơn vị có nhu cầu mua sắm
-C. Nhà thầu đã ký kết thỏa thuận khung không phải thực hiện biện pháp bảo đảm thực hiện hợp đồng trước thời điểm hợp đồng có hiệu lực cho đơn vị có nhu cầu mua sắm
-D. Nhà thầu đã ký kết thỏa thuận khung phải thực hiện biện pháp bảo đảm thực hiện hợp đồng sau
-thời điểm hợp đồng có hiệu lực cho đơn vị mua sắm tập trung</t>
-  </si>
-  <si>
     <t>Đối với các gói thầu mua sắm tập trung,
 trách nhiệm cung cấp thông tin về kết quả
 thực hiện hợp đồng của nhà thầu do ai thực hiện?</t>
@@ -2649,13 +2642,6 @@
 B. Các thành viên liên danh bắt buộc phải sử dụng cùng thể thức bảo lãnh dự thầu điện tử
 C. Các thành viên liên danh phải sử dụng cùng thể thức: bảo lãnh dự thầu điện tử hoặc bảo lãnh dự thầu bằng giấy
 D. Các thành viên liên danh bắt buộc phải sử dụng cùng thể thức bảo lãnh dự thầu bằng giấy</t>
-  </si>
-  <si>
-    <t>A. Trong vòng 05 ngày làm việc, kể từ ngày nhận được yêu cầu của chủ đầu tư, nếu nhà thầu từ chối hoặc không nộp bản gốc thư bảo lãnh dự thầu, giấy chứng nhận bảo hiểm bảo lãnh (đối với trường hợp sử dụng bảo lãnh dự thầu bằng văn bản giấy) theo yêu cầu của chủ đầu tư thì nhà thầu sẽ bị xử lý theo đúng cam kết của nhà thầu trong đơn dự thầu
-B. Trong vòng 05 ngày làm việc, kể từ ngày nhận được yêu cầu của bên mời thầu, nếu nhà thầu từ chối hoặc không nộp bản gốc thư bảo lãnh dự thầu, giấy chứng nhận bảo hiểm bảo lãnh (đối với trường hợp sử dụng bảo lãnh dự thầu bằng văn bản giấy) theo yêu cầu của bên mời thầu thì nhà thầu sẽ bị xử lý theo đúng cam kết của nhà thầu trong đơn dự thầu
-C. Trong vòng 05 ngày làm việc, kể từ ngày nhận được yêu cầu của tổ chuyên gia, nếu nhà thầu từ chối hoặc không nộp bản gốc thư bảo lãnh dự thầu, giấy chứng nhận bảo hiểm bảo lãnh (đối với trường hợp sử dụng bảo lãnh dự thầu bằng văn bản giấy) theo yêu cầu của tổ chuyên gia thì nhà thầu sẽ bị xử lý theo đúng cam kết của nhà thầu trong đơn dự thầu
-D. Trong vòng 05 ngày làm việc, kể từ ngày nhận được yêu cầu của tư vấn đấu thầu, nếu nhà thầu từ chối hoặc không nộp bản gốc thư bảo lãnh dự thầu, giấy chứng nhận bảo hiểm bảo lãnh (đối với trường hợp sử dụng bảo lãnh dự thầu bằng văn bản giấy) theo yêu cầu của tư vấn đấu thầu thì nhà
-thầu sẽ bị xử lý theo đúng cam kết của nhà thầu trong đơn dự thầu.</t>
   </si>
   <si>
     <t>A. Gói thầu hỗn hợp theo phương thức 02 giai đoạn
@@ -3830,6 +3816,18 @@
   </si>
   <si>
     <t>Hạng mục</t>
+  </si>
+  <si>
+    <t>A. Nhà thầu đã ký kết thỏa thuận khung phải thực hiện biện pháp bảo đảm thực hiện hợp đồng trước hoặc cùng thời điểm hợp đồng có hiệu lực cho đơn vị mua sắm tập trung
+B. Nhà thầu đã ký kết thỏa thuận khung phải thực hiện biện pháp bảo đảm thực hiện hợp đồng trước hoặc cùng thời điểm hợp đồng có hiệu lực cho đơn vị có nhu cầu mua sắm
+C. Nhà thầu đã ký kết thỏa thuận khung không phải thực hiện biện pháp bảo đảm thực hiện hợp đồng trước thời điểm hợp đồng có hiệu lực cho đơn vị có nhu cầu mua sắm
+D. Nhà thầu đã ký kết thỏa thuận khung phải thực hiện biện pháp bảo đảm thực hiện hợp đồng sau thời điểm hợp đồng có hiệu lực cho đơn vị mua sắm tập trung</t>
+  </si>
+  <si>
+    <t>A. Trong vòng 05 ngày làm việc, kể từ ngày nhận được yêu cầu của chủ đầu tư, nếu nhà thầu từ chối hoặc không nộp bản gốc thư bảo lãnh dự thầu, giấy chứng nhận bảo hiểm bảo lãnh (đối với trường hợp sử dụng bảo lãnh dự thầu bằng văn bản giấy) theo yêu cầu của chủ đầu tư thì nhà thầu sẽ bị xử lý theo đúng cam kết của nhà thầu trong đơn dự thầu
+B. Trong vòng 05 ngày làm việc, kể từ ngày nhận được yêu cầu của bên mời thầu, nếu nhà thầu từ chối hoặc không nộp bản gốc thư bảo lãnh dự thầu, giấy chứng nhận bảo hiểm bảo lãnh (đối với trường hợp sử dụng bảo lãnh dự thầu bằng văn bản giấy) theo yêu cầu của bên mời thầu thì nhà thầu sẽ bị xử lý theo đúng cam kết của nhà thầu trong đơn dự thầu
+C. Trong vòng 05 ngày làm việc, kể từ ngày nhận được yêu cầu của tổ chuyên gia, nếu nhà thầu từ chối hoặc không nộp bản gốc thư bảo lãnh dự thầu, giấy chứng nhận bảo hiểm bảo lãnh (đối với trường hợp sử dụng bảo lãnh dự thầu bằng văn bản giấy) theo yêu cầu của tổ chuyên gia thì nhà thầu sẽ bị xử lý theo đúng cam kết của nhà thầu trong đơn dự thầu
+D. Trong vòng 05 ngày làm việc, kể từ ngày nhận được yêu cầu của tư vấn đấu thầu, nếu nhà thầu từ chối hoặc không nộp bản gốc thư bảo lãnh dự thầu, giấy chứng nhận bảo hiểm bảo lãnh (đối với trường hợp sử dụng bảo lãnh dự thầu bằng văn bản giấy) theo yêu cầu của tư vấn đấu thầu thì nhà thầu sẽ bị xử lý theo đúng cam kết của nhà thầu trong đơn dự thầu.</t>
   </si>
 </sst>
 </file>
@@ -4272,7 +4270,7 @@
         <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>10</v>
@@ -4418,7 +4416,7 @@
         <v>235</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>16</v>
@@ -4803,7 +4801,7 @@
         <v>23</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>19</v>
@@ -5153,7 +5151,7 @@
         <v>28</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>1</v>
@@ -5258,7 +5256,7 @@
         <v>268</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>19</v>
@@ -5643,7 +5641,7 @@
         <v>38</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>0</v>
@@ -6798,7 +6796,7 @@
         <v>329</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>16</v>
@@ -6938,7 +6936,7 @@
         <v>335</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>1</v>
@@ -7078,7 +7076,7 @@
         <v>57</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>1</v>
@@ -7673,7 +7671,7 @@
         <v>366</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>19</v>
@@ -7743,7 +7741,7 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>1</v>
@@ -7778,7 +7776,7 @@
         <v>65</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>16</v>
@@ -7988,7 +7986,7 @@
         <v>68</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>19</v>
@@ -8198,7 +8196,7 @@
         <v>383</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>1</v>
@@ -8583,7 +8581,7 @@
         <v>399</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>0</v>
@@ -8618,7 +8616,7 @@
         <v>77</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>1</v>
@@ -8688,7 +8686,7 @@
         <v>78</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>0</v>
@@ -8723,7 +8721,7 @@
         <v>79</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>0</v>
@@ -8758,7 +8756,7 @@
         <v>80</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>1</v>
@@ -8968,7 +8966,7 @@
         <v>84</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>19</v>
@@ -9143,13 +9141,13 @@
         <v>88</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:5" ht="62" x14ac:dyDescent="0.35">
       <c r="A141" s="6">
         <v>140</v>
       </c>
@@ -9178,7 +9176,7 @@
         <v>89</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>414</v>
+        <v>783</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>16</v>
@@ -9210,10 +9208,10 @@
         <v>Mua sắm tập trung</v>
       </c>
       <c r="C142" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>416</v>
       </c>
       <c r="E142" s="3" t="s">
         <v>1</v>
@@ -9248,7 +9246,7 @@
         <v>90</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E143" s="3" t="s">
         <v>19</v>
@@ -9283,7 +9281,7 @@
         <v>91</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E144" s="3" t="s">
         <v>16</v>
@@ -9318,7 +9316,7 @@
         <v>92</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>16</v>
@@ -9350,10 +9348,10 @@
         <v>Mua sắm tập trung</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>19</v>
@@ -9385,10 +9383,10 @@
         <v>Mua sắm tập trung</v>
       </c>
       <c r="C147" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>1</v>
@@ -9420,10 +9418,10 @@
         <v>Mua sắm tập trung</v>
       </c>
       <c r="C148" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>16</v>
@@ -9458,7 +9456,7 @@
         <v>93</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>19</v>
@@ -9490,10 +9488,10 @@
         <v>Mua sắm tập trung</v>
       </c>
       <c r="C150" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>426</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>19</v>
@@ -9528,7 +9526,7 @@
         <v>94</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>16</v>
@@ -9563,7 +9561,7 @@
         <v>95</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>1</v>
@@ -9595,10 +9593,10 @@
         <v>Chủ đầu tư, người có thẩm quyền và tổ chuyên gia</v>
       </c>
       <c r="C153" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>430</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>0</v>
@@ -9630,10 +9628,10 @@
         <v>Chủ đầu tư, người có thẩm quyền và tổ chuyên gia</v>
       </c>
       <c r="C154" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>1</v>
@@ -9668,7 +9666,7 @@
         <v>96</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>16</v>
@@ -9700,10 +9698,10 @@
         <v>Chủ đầu tư, người có thẩm quyền và tổ chuyên gia</v>
       </c>
       <c r="C156" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>434</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>435</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>16</v>
@@ -9735,10 +9733,10 @@
         <v>Chủ đầu tư, người có thẩm quyền và tổ chuyên gia</v>
       </c>
       <c r="C157" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>437</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>16</v>
@@ -9773,7 +9771,7 @@
         <v>97</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E158" s="3" t="s">
         <v>0</v>
@@ -9805,10 +9803,10 @@
         <v>Thanh tra, kiểm tra và xử lý vi phạm</v>
       </c>
       <c r="C159" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>439</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>440</v>
       </c>
       <c r="E159" s="3" t="s">
         <v>1</v>
@@ -9843,7 +9841,7 @@
         <v>98</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E160" s="3" t="s">
         <v>16</v>
@@ -9875,10 +9873,10 @@
         <v>Thanh tra, kiểm tra và xử lý vi phạm</v>
       </c>
       <c r="C161" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>443</v>
       </c>
       <c r="E161" s="3" t="s">
         <v>19</v>
@@ -9913,7 +9911,7 @@
         <v>99</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E162" s="3" t="s">
         <v>0</v>
@@ -9945,10 +9943,10 @@
         <v>Thanh tra, kiểm tra và xử lý vi phạm</v>
       </c>
       <c r="C163" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="E163" s="3" t="s">
         <v>19</v>
@@ -9980,10 +9978,10 @@
         <v>Thanh tra, kiểm tra và xử lý vi phạm</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>1</v>
@@ -10015,10 +10013,10 @@
         <v>Thanh tra, kiểm tra và xử lý vi phạm</v>
       </c>
       <c r="C165" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>448</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>449</v>
       </c>
       <c r="E165" s="3" t="s">
         <v>16</v>
@@ -10050,10 +10048,10 @@
         <v>Thanh tra, kiểm tra và xử lý vi phạm</v>
       </c>
       <c r="C166" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>450</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>451</v>
       </c>
       <c r="E166" s="3" t="s">
         <v>19</v>
@@ -10085,10 +10083,10 @@
         <v>Thanh tra, kiểm tra và xử lý vi phạm</v>
       </c>
       <c r="C167" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>452</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>453</v>
       </c>
       <c r="E167" s="3" t="s">
         <v>19</v>
@@ -10120,10 +10118,10 @@
         <v>Thanh tra, kiểm tra và xử lý vi phạm</v>
       </c>
       <c r="C168" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>454</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>455</v>
       </c>
       <c r="E168" s="3" t="s">
         <v>0</v>
@@ -10158,7 +10156,7 @@
         <v>100</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E169" s="3" t="s">
         <v>1</v>
@@ -10190,10 +10188,10 @@
         <v>Thanh tra, kiểm tra và xử lý vi phạm</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E170" s="3" t="s">
         <v>16</v>
@@ -10228,7 +10226,7 @@
         <v>101</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>16</v>
@@ -10263,7 +10261,7 @@
         <v>102</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>19</v>
@@ -10295,10 +10293,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C173" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>461</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>1</v>
@@ -10333,7 +10331,7 @@
         <v>103</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>16</v>
@@ -10365,10 +10363,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C175" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>463</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>464</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>16</v>
@@ -10403,7 +10401,7 @@
         <v>104</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>16</v>
@@ -10435,10 +10433,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C177" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>466</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>467</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>0</v>
@@ -10470,10 +10468,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C178" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>468</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>469</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>16</v>
@@ -10505,10 +10503,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C179" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>470</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>471</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>19</v>
@@ -10540,10 +10538,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C180" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="D180" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>16</v>
@@ -10575,10 +10573,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>0</v>
@@ -10610,10 +10608,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C182" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>475</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>476</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>1</v>
@@ -10648,7 +10646,7 @@
         <v>105</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>19</v>
@@ -10683,7 +10681,7 @@
         <v>106</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>16</v>
@@ -10718,7 +10716,7 @@
         <v>107</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>0</v>
@@ -10750,10 +10748,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C186" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>480</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>481</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>16</v>
@@ -10785,10 +10783,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C187" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>482</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>483</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>19</v>
@@ -10820,10 +10818,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C188" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>485</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>1</v>
@@ -10858,7 +10856,7 @@
         <v>108</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>19</v>
@@ -10890,10 +10888,10 @@
         <v>Giải quyết kiến nghị</v>
       </c>
       <c r="C190" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>488</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>1</v>
@@ -10925,10 +10923,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C191" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>490</v>
       </c>
       <c r="E191" s="3" t="s">
         <v>0</v>
@@ -10960,10 +10958,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C192" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>491</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>492</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>1</v>
@@ -10998,7 +10996,7 @@
         <v>109</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>0</v>
@@ -11033,7 +11031,7 @@
         <v>110</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>1</v>
@@ -11065,10 +11063,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>1</v>
@@ -11100,10 +11098,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>16</v>
@@ -11138,7 +11136,7 @@
         <v>111</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>1</v>
@@ -11173,7 +11171,7 @@
         <v>112</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>0</v>
@@ -11205,10 +11203,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C199" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="D199" s="1" t="s">
-        <v>498</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>0</v>
@@ -11240,10 +11238,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C200" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="D200" s="1" t="s">
-        <v>500</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>1</v>
@@ -11275,10 +11273,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C201" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>1</v>
@@ -11313,7 +11311,7 @@
         <v>113</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>19</v>
@@ -11348,7 +11346,7 @@
         <v>114</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>16</v>
@@ -11383,7 +11381,7 @@
         <v>115</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>19</v>
@@ -11415,10 +11413,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C205" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>505</v>
-      </c>
-      <c r="D205" s="1" t="s">
-        <v>506</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>0</v>
@@ -11450,10 +11448,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C206" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>507</v>
-      </c>
-      <c r="D206" s="1" t="s">
-        <v>508</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>1</v>
@@ -11488,7 +11486,7 @@
         <v>116</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>19</v>
@@ -11520,10 +11518,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C208" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>510</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>511</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>1</v>
@@ -11555,10 +11553,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C209" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="D209" s="1" t="s">
-        <v>513</v>
       </c>
       <c r="E209" s="3" t="s">
         <v>1</v>
@@ -11590,10 +11588,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C210" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>515</v>
       </c>
       <c r="E210" s="3" t="s">
         <v>0</v>
@@ -11625,10 +11623,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C211" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>516</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>517</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>16</v>
@@ -11660,10 +11658,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C212" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>518</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>519</v>
       </c>
       <c r="E212" s="3" t="s">
         <v>0</v>
@@ -11695,10 +11693,10 @@
         <v>Tình huống thực tiễn trong đấu thầu</v>
       </c>
       <c r="C213" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>521</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>19</v>
@@ -11733,7 +11731,7 @@
         <v>117</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>0</v>
@@ -11768,7 +11766,7 @@
         <v>118</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E215" s="3" t="s">
         <v>19</v>
@@ -11800,10 +11798,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C216" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="D216" s="1" t="s">
-        <v>525</v>
       </c>
       <c r="E216" s="3" t="s">
         <v>19</v>
@@ -11838,7 +11836,7 @@
         <v>119</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E217" s="3" t="s">
         <v>0</v>
@@ -11873,7 +11871,7 @@
         <v>120</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="E218" s="3" t="s">
         <v>19</v>
@@ -11905,10 +11903,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C219" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="D219" s="1" t="s">
         <v>528</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>529</v>
       </c>
       <c r="E219" s="3" t="s">
         <v>16</v>
@@ -11940,10 +11938,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C220" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="D220" s="1" t="s">
-        <v>531</v>
       </c>
       <c r="E220" s="3" t="s">
         <v>19</v>
@@ -11978,7 +11976,7 @@
         <v>121</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>16</v>
@@ -12013,7 +12011,7 @@
         <v>122</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>0</v>
@@ -12048,7 +12046,7 @@
         <v>123</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>0</v>
@@ -12083,7 +12081,7 @@
         <v>124</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="E224" s="3" t="s">
         <v>0</v>
@@ -12118,7 +12116,7 @@
         <v>125</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="E225" s="3" t="s">
         <v>0</v>
@@ -12150,10 +12148,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C226" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D226" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="D226" s="1" t="s">
-        <v>538</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>1</v>
@@ -12188,7 +12186,7 @@
         <v>126</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>16</v>
@@ -12223,7 +12221,7 @@
         <v>127</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E228" s="3" t="s">
         <v>0</v>
@@ -12255,10 +12253,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C229" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D229" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="D229" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="E229" s="3" t="s">
         <v>19</v>
@@ -12293,7 +12291,7 @@
         <v>128</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E230" s="3" t="s">
         <v>19</v>
@@ -12328,7 +12326,7 @@
         <v>129</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E231" s="3" t="s">
         <v>1</v>
@@ -12363,7 +12361,7 @@
         <v>130</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E232" s="3" t="s">
         <v>0</v>
@@ -12398,7 +12396,7 @@
         <v>131</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="E233" s="3" t="s">
         <v>19</v>
@@ -12433,7 +12431,7 @@
         <v>132</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="E234" s="3" t="s">
         <v>0</v>
@@ -12465,10 +12463,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C235" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D235" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>548</v>
       </c>
       <c r="E235" s="3" t="s">
         <v>16</v>
@@ -12503,7 +12501,7 @@
         <v>133</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E236" s="3" t="s">
         <v>0</v>
@@ -12535,10 +12533,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C237" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D237" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>551</v>
       </c>
       <c r="E237" s="3" t="s">
         <v>0</v>
@@ -12570,10 +12568,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C238" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D238" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="D238" s="1" t="s">
-        <v>553</v>
       </c>
       <c r="E238" s="3" t="s">
         <v>19</v>
@@ -12608,7 +12606,7 @@
         <v>134</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E239" s="3" t="s">
         <v>0</v>
@@ -12640,10 +12638,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>0</v>
@@ -12678,7 +12676,7 @@
         <v>135</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>1</v>
@@ -12710,10 +12708,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C242" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="D242" s="1" t="s">
-        <v>557</v>
       </c>
       <c r="E242" s="3" t="s">
         <v>0</v>
@@ -12745,10 +12743,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C243" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D243" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>559</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>19</v>
@@ -12783,7 +12781,7 @@
         <v>136</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="E244" s="3" t="s">
         <v>1</v>
@@ -12815,10 +12813,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C245" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="D245" s="1" t="s">
         <v>560</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>561</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>16</v>
@@ -12850,10 +12848,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C246" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="D246" s="1" t="s">
         <v>562</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>563</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>16</v>
@@ -12885,10 +12883,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C247" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D247" s="1" t="s">
         <v>564</v>
-      </c>
-      <c r="D247" s="1" t="s">
-        <v>565</v>
       </c>
       <c r="E247" s="3" t="s">
         <v>1</v>
@@ -12923,7 +12921,7 @@
         <v>137</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>19</v>
@@ -12955,10 +12953,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>19</v>
@@ -12993,7 +12991,7 @@
         <v>138</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>0</v>
@@ -13025,10 +13023,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>19</v>
@@ -13063,7 +13061,7 @@
         <v>139</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>19</v>
@@ -13098,7 +13096,7 @@
         <v>140</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>19</v>
@@ -13133,7 +13131,7 @@
         <v>141</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>1</v>
@@ -13165,10 +13163,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C255" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="D255" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="D255" s="1" t="s">
-        <v>573</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>19</v>
@@ -13200,10 +13198,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C256" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="D256" s="1" t="s">
-        <v>575</v>
       </c>
       <c r="E256" s="3" t="s">
         <v>16</v>
@@ -13238,7 +13236,7 @@
         <v>142</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E257" s="3" t="s">
         <v>0</v>
@@ -13273,7 +13271,7 @@
         <v>143</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E258" s="3" t="s">
         <v>0</v>
@@ -13305,10 +13303,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C259" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="D259" s="1" t="s">
-        <v>579</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>19</v>
@@ -13343,7 +13341,7 @@
         <v>144</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>580</v>
+        <v>784</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>1</v>
@@ -13378,7 +13376,7 @@
         <v>145</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>0</v>
@@ -13413,7 +13411,7 @@
         <v>146</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>0</v>
@@ -13448,7 +13446,7 @@
         <v>147</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>0</v>
@@ -13480,10 +13478,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>1</v>
@@ -13518,7 +13516,7 @@
         <v>148</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>1</v>
@@ -13553,7 +13551,7 @@
         <v>149</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>1</v>
@@ -13585,10 +13583,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>0</v>
@@ -13620,10 +13618,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>1</v>
@@ -13655,10 +13653,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E269" s="3" t="s">
         <v>1</v>
@@ -13693,7 +13691,7 @@
         <v>150</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E270" s="3" t="s">
         <v>1</v>
@@ -13728,7 +13726,7 @@
         <v>151</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>0</v>
@@ -13760,10 +13758,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E272" s="3" t="s">
         <v>0</v>
@@ -13798,7 +13796,7 @@
         <v>152</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E273" s="3" t="s">
         <v>0</v>
@@ -13833,7 +13831,7 @@
         <v>153</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E274" s="3" t="s">
         <v>19</v>
@@ -13868,7 +13866,7 @@
         <v>154</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E275" s="3" t="s">
         <v>1</v>
@@ -13900,10 +13898,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E276" s="3" t="s">
         <v>0</v>
@@ -13935,10 +13933,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E277" s="3" t="s">
         <v>19</v>
@@ -13970,10 +13968,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E278" s="3" t="s">
         <v>0</v>
@@ -14005,10 +14003,10 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E279" s="3" t="s">
         <v>16</v>
@@ -14040,10 +14038,10 @@
         <v>Phương pháp đánh giá và xét duyệt trúng thầu</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E280" s="3" t="s">
         <v>19</v>
@@ -14078,7 +14076,7 @@
         <v>155</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E281" s="3" t="s">
         <v>19</v>
@@ -14113,7 +14111,7 @@
         <v>156</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E282" s="3" t="s">
         <v>16</v>
@@ -14148,7 +14146,7 @@
         <v>157</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E283" s="3" t="s">
         <v>19</v>
@@ -14183,7 +14181,7 @@
         <v>158</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E284" s="3" t="s">
         <v>0</v>
@@ -14218,7 +14216,7 @@
         <v>159</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E285" s="3" t="s">
         <v>16</v>
@@ -14253,7 +14251,7 @@
         <v>160</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E286" s="3" t="s">
         <v>16</v>
@@ -14288,7 +14286,7 @@
         <v>161</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E287" s="3" t="s">
         <v>0</v>
@@ -14323,7 +14321,7 @@
         <v>162</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E288" s="3" t="s">
         <v>16</v>
@@ -14358,7 +14356,7 @@
         <v>163</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E289" s="3" t="s">
         <v>16</v>
@@ -14393,7 +14391,7 @@
         <v>164</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E290" s="3" t="s">
         <v>16</v>
@@ -14428,7 +14426,7 @@
         <v>165</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="E291" s="3" t="s">
         <v>16</v>
@@ -14460,10 +14458,10 @@
         <v>Phương pháp đánh giá và xét duyệt trúng thầu</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E292" s="3" t="s">
         <v>16</v>
@@ -14495,10 +14493,10 @@
         <v>Phương pháp đánh giá và xét duyệt trúng thầu</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E293" s="3" t="s">
         <v>16</v>
@@ -14530,10 +14528,10 @@
         <v>Phương pháp đánh giá và xét duyệt trúng thầu</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E294" s="3" t="s">
         <v>19</v>
@@ -14568,7 +14566,7 @@
         <v>166</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E295" s="3" t="s">
         <v>19</v>
@@ -14603,7 +14601,7 @@
         <v>167</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E296" s="3" t="s">
         <v>19</v>
@@ -14638,7 +14636,7 @@
         <v>144</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E297" s="3" t="s">
         <v>0</v>
@@ -14673,7 +14671,7 @@
         <v>168</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E298" s="3" t="s">
         <v>1</v>
@@ -14708,7 +14706,7 @@
         <v>169</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E299" s="3" t="s">
         <v>0</v>
@@ -14740,10 +14738,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E300" s="3" t="s">
         <v>1</v>
@@ -14778,7 +14776,7 @@
         <v>170</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E301" s="3" t="s">
         <v>19</v>
@@ -14810,10 +14808,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E302" s="3" t="s">
         <v>0</v>
@@ -14848,7 +14846,7 @@
         <v>171</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E303" s="3" t="s">
         <v>16</v>
@@ -14883,7 +14881,7 @@
         <v>172</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E304" s="3" t="s">
         <v>16</v>
@@ -14918,7 +14916,7 @@
         <v>173</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E305" s="3" t="s">
         <v>16</v>
@@ -14953,7 +14951,7 @@
         <v>174</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E306" s="3" t="s">
         <v>16</v>
@@ -14988,7 +14986,7 @@
         <v>175</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E307" s="3" t="s">
         <v>16</v>
@@ -15023,7 +15021,7 @@
         <v>176</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E308" s="3" t="s">
         <v>16</v>
@@ -15058,7 +15056,7 @@
         <v>177</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E309" s="3" t="s">
         <v>16</v>
@@ -15090,10 +15088,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E310" s="3" t="s">
         <v>16</v>
@@ -15125,10 +15123,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>16</v>
@@ -15163,7 +15161,7 @@
         <v>178</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E312" s="3" t="s">
         <v>16</v>
@@ -15198,7 +15196,7 @@
         <v>179</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E313" s="3" t="s">
         <v>16</v>
@@ -15230,10 +15228,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E314" s="3" t="s">
         <v>16</v>
@@ -15268,7 +15266,7 @@
         <v>180</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E315" s="3" t="s">
         <v>0</v>
@@ -15303,7 +15301,7 @@
         <v>181</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E316" s="3" t="s">
         <v>1</v>
@@ -15338,7 +15336,7 @@
         <v>182</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E317" s="3" t="s">
         <v>1</v>
@@ -15370,10 +15368,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E318" s="3" t="s">
         <v>16</v>
@@ -15408,7 +15406,7 @@
         <v>183</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E319" s="3" t="s">
         <v>1</v>
@@ -15443,7 +15441,7 @@
         <v>184</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="E320" s="3" t="s">
         <v>19</v>
@@ -15478,7 +15476,7 @@
         <v>185</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E321" s="3" t="s">
         <v>19</v>
@@ -15513,7 +15511,7 @@
         <v>186</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E322" s="3" t="s">
         <v>0</v>
@@ -15548,7 +15546,7 @@
         <v>187</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E323" s="3" t="s">
         <v>19</v>
@@ -15583,7 +15581,7 @@
         <v>188</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E324" s="3" t="s">
         <v>19</v>
@@ -15618,7 +15616,7 @@
         <v>189</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E325" s="3" t="s">
         <v>1</v>
@@ -15653,7 +15651,7 @@
         <v>190</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E326" s="3" t="s">
         <v>19</v>
@@ -15688,7 +15686,7 @@
         <v>191</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E327" s="3" t="s">
         <v>19</v>
@@ -15723,7 +15721,7 @@
         <v>192</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E328" s="3" t="s">
         <v>16</v>
@@ -15755,10 +15753,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E329" s="3" t="s">
         <v>16</v>
@@ -15790,10 +15788,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E330" s="3" t="s">
         <v>16</v>
@@ -15828,7 +15826,7 @@
         <v>193</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E331" s="3" t="s">
         <v>0</v>
@@ -15860,10 +15858,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E332" s="3" t="s">
         <v>0</v>
@@ -15898,7 +15896,7 @@
         <v>4</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E333" s="3" t="s">
         <v>19</v>
@@ -15933,7 +15931,7 @@
         <v>194</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E334" s="3" t="s">
         <v>19</v>
@@ -15965,10 +15963,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E335" s="3" t="s">
         <v>19</v>
@@ -16000,10 +15998,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>19</v>
@@ -16038,7 +16036,7 @@
         <v>195</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E337" s="3" t="s">
         <v>19</v>
@@ -16073,7 +16071,7 @@
         <v>196</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E338" s="3" t="s">
         <v>1</v>
@@ -16108,7 +16106,7 @@
         <v>197</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E339" s="3" t="s">
         <v>16</v>
@@ -16140,10 +16138,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E340" s="3" t="s">
         <v>1</v>
@@ -16178,7 +16176,7 @@
         <v>198</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E341" s="3" t="s">
         <v>1</v>
@@ -16213,7 +16211,7 @@
         <v>199</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="E342" s="3" t="s">
         <v>0</v>
@@ -16248,7 +16246,7 @@
         <v>200</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E343" s="3" t="s">
         <v>1</v>
@@ -16283,7 +16281,7 @@
         <v>201</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E344" s="3" t="s">
         <v>0</v>
@@ -16318,7 +16316,7 @@
         <v>202</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E345" s="3" t="s">
         <v>16</v>
@@ -16350,10 +16348,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E346" s="3" t="s">
         <v>16</v>
@@ -16388,7 +16386,7 @@
         <v>203</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E347" s="3" t="s">
         <v>0</v>
@@ -16423,7 +16421,7 @@
         <v>204</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E348" s="3" t="s">
         <v>0</v>
@@ -16458,7 +16456,7 @@
         <v>205</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E349" s="3" t="s">
         <v>0</v>
@@ -16493,7 +16491,7 @@
         <v>206</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>1</v>
@@ -16525,10 +16523,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E351" s="3" t="s">
         <v>1</v>
@@ -16563,7 +16561,7 @@
         <v>207</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E352" s="3" t="s">
         <v>19</v>
@@ -16598,7 +16596,7 @@
         <v>208</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E353" s="3" t="s">
         <v>0</v>
@@ -16630,10 +16628,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>19</v>
@@ -16668,7 +16666,7 @@
         <v>209</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>0</v>
@@ -16700,10 +16698,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E356" s="3" t="s">
         <v>1</v>
@@ -16738,7 +16736,7 @@
         <v>210</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="E357" s="3" t="s">
         <v>19</v>
@@ -16773,7 +16771,7 @@
         <v>5</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="E358" s="3" t="s">
         <v>16</v>
@@ -16808,7 +16806,7 @@
         <v>6</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E359" s="3" t="s">
         <v>19</v>
@@ -16840,10 +16838,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E360" s="3" t="s">
         <v>16</v>
@@ -16875,10 +16873,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E361" s="3" t="s">
         <v>19</v>
@@ -16910,10 +16908,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E362" s="3" t="s">
         <v>16</v>
@@ -16948,7 +16946,7 @@
         <v>211</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E363" s="3" t="s">
         <v>19</v>
@@ -16983,7 +16981,7 @@
         <v>212</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E364" s="3" t="s">
         <v>0</v>
@@ -17018,7 +17016,7 @@
         <v>213</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="E365" s="3" t="s">
         <v>0</v>
@@ -17053,7 +17051,7 @@
         <v>214</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>19</v>
@@ -17088,7 +17086,7 @@
         <v>215</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>19</v>
@@ -17120,10 +17118,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>0</v>
@@ -17158,7 +17156,7 @@
         <v>216</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>19</v>
@@ -17190,10 +17188,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="E370" s="3" t="s">
         <v>16</v>
@@ -17228,7 +17226,7 @@
         <v>7</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>1</v>
@@ -17263,7 +17261,7 @@
         <v>217</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="E372" s="3" t="s">
         <v>0</v>
@@ -17298,7 +17296,7 @@
         <v>218</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="E373" s="3" t="s">
         <v>1</v>
@@ -17333,7 +17331,7 @@
         <v>219</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="E374" s="3" t="s">
         <v>0</v>
@@ -17368,7 +17366,7 @@
         <v>220</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>1</v>
@@ -17400,10 +17398,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="E376" s="3" t="s">
         <v>0</v>
@@ -17438,7 +17436,7 @@
         <v>221</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>19</v>
@@ -17473,7 +17471,7 @@
         <v>222</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="E378" s="3" t="s">
         <v>16</v>
@@ -17508,7 +17506,7 @@
         <v>223</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="E379" s="3" t="s">
         <v>19</v>
@@ -17543,7 +17541,7 @@
         <v>8</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="E380" s="3" t="s">
         <v>0</v>
@@ -17575,10 +17573,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E381" s="3" t="s">
         <v>16</v>
@@ -17613,7 +17611,7 @@
         <v>224</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E382" s="3" t="s">
         <v>1</v>
@@ -17648,7 +17646,7 @@
         <v>225</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E383" s="3" t="s">
         <v>0</v>
@@ -17683,7 +17681,7 @@
         <v>226</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="E384" s="3" t="s">
         <v>0</v>
@@ -17718,7 +17716,7 @@
         <v>227</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="E385" s="3" t="s">
         <v>1</v>
@@ -17753,7 +17751,7 @@
         <v>228</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="E386" s="3" t="s">
         <v>16</v>
@@ -17788,7 +17786,7 @@
         <v>229</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E387" s="3" t="s">
         <v>19</v>
@@ -17823,7 +17821,7 @@
         <v>230</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="E388" s="3" t="s">
         <v>16</v>
@@ -17855,10 +17853,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="E389" s="3" t="s">
         <v>1</v>
@@ -17890,10 +17888,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="E390" s="3" t="s">
         <v>1</v>
@@ -17928,7 +17926,7 @@
         <v>231</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="E391" s="3" t="s">
         <v>1</v>

--- a/data/Ngan-Hang-Cau-Hoi.xlsx
+++ b/data/Ngan-Hang-Cau-Hoi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9f54d0bdb7235122/Documents/My App/trac-nghiem-luat-dau-thau/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C6706F-7B15-414B-84B2-FA000E4A3D95}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{D1DCDABD-225D-4CEF-B71D-B3A374D525E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EEBC7F1-7AFC-4890-80E5-AC58F1414A8B}"/>
   <bookViews>
     <workbookView xWindow="3420" yWindow="3420" windowWidth="19200" windowHeight="11170" xr2:uid="{0822E189-CD53-41B9-B216-EFA7EF505EBC}"/>
   </bookViews>
@@ -2906,13 +2906,6 @@
 D. Các phương án trên đều sai</t>
   </si>
   <si>
-    <t>A. Nhà thầu có từ 50% lao động trở lên là người khuyết tật, thương binh, dân tộc thiểu số có hợp đồng lao động với thời gian thực hiện hợp đồng từ 03 tháng trở lên và đến thời điểm đóng thầu hợp đồng vẫn còn hiệu lực
-B. Nhà thầu có từ 25% lao động trở lên là người khuyết tật, thương binh, dân tộc thiểu số có hợp đồng lao động với thời gian thực hiện hợp đồng từ 03 tháng trở lên và đến thời điểm đóng thầu hợp đồng vẫn còn hiệu lực
-C. Nhà thầu có từ 50% lao động trở lên là người khuyết tật, thương binh, dân tộc thiểu số có hợp đồng lao động với thời gian thực hiện hợp đồng dưới 03 tháng và đến thời điểm đóng thầu hợp đồng vẫn còn hiệu lực
-D. Nhà thầu có từ 25% lao động trở lên là người khuyết tật, thương binh, dân tộc thiểu số có hợp
-đồng lao động với thời gian thực hiện hợp đồng dưới 03 tháng và đến thời điểm đóng thầu hợp đồng vẫn còn hiệu lực</t>
-  </si>
-  <si>
     <t>A. Nhà thầu A sử dụng tài khoản tham gia Hệ thống của chi nhánh B để tham dự thầu
 B. Nhà thầu A sử dụng tài khoản tham gia Hệ thống của chính đơn vị mình để tham dự thầu
 C. Nhà thầu A sử dụng tài khoản tham gia Hệ thống của công ty con hạch toán phụ thuộc C để tham dự thầu
@@ -3063,13 +3056,6 @@
 B. 9 nước
 C. 11 nước
 D. 12 nước</t>
-  </si>
-  <si>
-    <t>A. Hiệp định Đối tác Toàn diện và Tiến bộ Xuyên Thái Bình Dương (CPTPP)
-B. Hiệp định thương mại tự do giữa Cộng hòa xã hội chủ nghĩa Việt Nam và Liên minh Châu Âu
-(EVFTA)
-C. Hiệp định EVFTA và Hiệp định Thương mại Tự do giữa Việt Nam và Liên hiệp Vương quốc Anh và Bắc Ailen (UKVFTA)
-D. Hiệp định Đối tác Kinh tế Toàn diện Khu vực (RCEP)</t>
   </si>
   <si>
     <t>A. Mua sắm thiết bị văn phòng
@@ -3383,11 +3369,6 @@
 B. Phải bao gồm Tờ khai thuế (thông báo nộp tiền của cơ quan thuế đối với hộ kinh doanh) và xác nhận của cơ quan thuế về việc thực hiện nghĩa vụ thuế
 C. Phải bao gồm Tờ khai thuế (thông báo nộp tiền của cơ quan thuế đối với hộ kinh doanh), giấy nộp tiền có xác nhận của cơ quan thuế được in từ Hệ thống thuế điện tử và xác nhận của cơ quan thuế về việc thực hiện nghĩa vụ thuế.
 D. Phương án A hoặc B đúng</t>
-  </si>
-  <si>
-    <t>A. Trước khi phê duyệt kế hoạch lựa chọn nhà thầu, chủ đầu tư phê duyệt dự toán đối với khối lượng mua thêm  B .Trước khi phê duyệt kế hoạch lựa chọn nhà thầu, chủ đầu tư trình cấp có thẩm quyền phê duyệt dự toán đối với khối lượng mua thêm
-C. Trong quá trình thực hiện hợp đồng, trường hợp sử dụng khối lượng tùy chọn mua thêm, trước khi thực hiện chủ đầu tư phê duyệt dự toán cho khối lượng mua thêm
-D. Không phải phê duyệt dự toán tùy chọn mua thêm</t>
   </si>
   <si>
     <t>Ban Quản lý dự án đầu tư xây dựng tỉnh tổ chức đấu thầu rộng rãi qua mạng đối với gói thầu xây lắp . Nhà thầu A được xếp hạng nhất tại gói thầu này, tuy nhiên, do trong E-HSDT, nhà thầu A đề xuất 01 nhân sự chủ chốt đã huy động cho hợp đồng khác có thời gian làm việc trùng với thời gian thực hiện gói thầu này.
@@ -3828,6 +3809,24 @@
 B. Trong vòng 05 ngày làm việc, kể từ ngày nhận được yêu cầu của bên mời thầu, nếu nhà thầu từ chối hoặc không nộp bản gốc thư bảo lãnh dự thầu, giấy chứng nhận bảo hiểm bảo lãnh (đối với trường hợp sử dụng bảo lãnh dự thầu bằng văn bản giấy) theo yêu cầu của bên mời thầu thì nhà thầu sẽ bị xử lý theo đúng cam kết của nhà thầu trong đơn dự thầu
 C. Trong vòng 05 ngày làm việc, kể từ ngày nhận được yêu cầu của tổ chuyên gia, nếu nhà thầu từ chối hoặc không nộp bản gốc thư bảo lãnh dự thầu, giấy chứng nhận bảo hiểm bảo lãnh (đối với trường hợp sử dụng bảo lãnh dự thầu bằng văn bản giấy) theo yêu cầu của tổ chuyên gia thì nhà thầu sẽ bị xử lý theo đúng cam kết của nhà thầu trong đơn dự thầu
 D. Trong vòng 05 ngày làm việc, kể từ ngày nhận được yêu cầu của tư vấn đấu thầu, nếu nhà thầu từ chối hoặc không nộp bản gốc thư bảo lãnh dự thầu, giấy chứng nhận bảo hiểm bảo lãnh (đối với trường hợp sử dụng bảo lãnh dự thầu bằng văn bản giấy) theo yêu cầu của tư vấn đấu thầu thì nhà thầu sẽ bị xử lý theo đúng cam kết của nhà thầu trong đơn dự thầu.</t>
+  </si>
+  <si>
+    <t>A. Trước khi phê duyệt kế hoạch lựa chọn nhà thầu, chủ đầu tư phê duyệt dự toán đối với khối lượng mua thêm
+B .Trước khi phê duyệt kế hoạch lựa chọn nhà thầu, chủ đầu tư trình cấp có thẩm quyền phê duyệt dự toán đối với khối lượng mua thêm
+C. Trong quá trình thực hiện hợp đồng, trường hợp sử dụng khối lượng tùy chọn mua thêm, trước khi thực hiện chủ đầu tư phê duyệt dự toán cho khối lượng mua thêm
+D. Không phải phê duyệt dự toán tùy chọn mua thêm</t>
+  </si>
+  <si>
+    <t>A. Nhà thầu có từ 50% lao động trở lên là người khuyết tật, thương binh, dân tộc thiểu số có hợp đồng lao động với thời gian thực hiện hợp đồng từ 03 tháng trở lên và đến thời điểm đóng thầu hợp đồng vẫn còn hiệu lực
+B. Nhà thầu có từ 25% lao động trở lên là người khuyết tật, thương binh, dân tộc thiểu số có hợp đồng lao động với thời gian thực hiện hợp đồng từ 03 tháng trở lên và đến thời điểm đóng thầu hợp đồng vẫn còn hiệu lực
+C. Nhà thầu có từ 50% lao động trở lên là người khuyết tật, thương binh, dân tộc thiểu số có hợp đồng lao động với thời gian thực hiện hợp đồng dưới 03 tháng và đến thời điểm đóng thầu hợp đồng vẫn còn hiệu lực
+D. Nhà thầu có từ 25% lao động trở lên là người khuyết tật, thương binh, dân tộc thiểu số có hợp đồng lao động với thời gian thực hiện hợp đồng dưới 03 tháng và đến thời điểm đóng thầu hợp đồng vẫn còn hiệu lực</t>
+  </si>
+  <si>
+    <t>A. Hiệp định Đối tác Toàn diện và Tiến bộ Xuyên Thái Bình Dương (CPTPP)
+B. Hiệp định thương mại tự do giữa Cộng hòa xã hội chủ nghĩa Việt Nam và Liên minh Châu Âu (EVFTA)
+C. Hiệp định EVFTA và Hiệp định Thương mại Tự do giữa Việt Nam và Liên hiệp Vương quốc Anh và Bắc Ailen (UKVFTA)
+D. Hiệp định Đối tác Kinh tế Toàn diện Khu vực (RCEP)</t>
   </si>
 </sst>
 </file>
@@ -3932,10 +3931,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4270,7 +4265,7 @@
         <v>9</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>10</v>
@@ -4416,7 +4411,7 @@
         <v>235</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>16</v>
@@ -4801,7 +4796,7 @@
         <v>23</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>19</v>
@@ -5151,7 +5146,7 @@
         <v>28</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>1</v>
@@ -5256,7 +5251,7 @@
         <v>268</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>19</v>
@@ -5641,7 +5636,7 @@
         <v>38</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="E40" s="3" t="s">
         <v>0</v>
@@ -6796,7 +6791,7 @@
         <v>329</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E73" s="3" t="s">
         <v>16</v>
@@ -6936,7 +6931,7 @@
         <v>335</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>1</v>
@@ -7076,7 +7071,7 @@
         <v>57</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>1</v>
@@ -7671,7 +7666,7 @@
         <v>366</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>19</v>
@@ -7741,7 +7736,7 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>1</v>
@@ -7776,7 +7771,7 @@
         <v>65</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>16</v>
@@ -7986,7 +7981,7 @@
         <v>68</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="E107" s="3" t="s">
         <v>19</v>
@@ -8196,7 +8191,7 @@
         <v>383</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>1</v>
@@ -8581,7 +8576,7 @@
         <v>399</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>0</v>
@@ -8616,7 +8611,7 @@
         <v>77</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>1</v>
@@ -8686,7 +8681,7 @@
         <v>78</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>0</v>
@@ -8721,7 +8716,7 @@
         <v>79</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>0</v>
@@ -8756,7 +8751,7 @@
         <v>80</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>1</v>
@@ -8966,7 +8961,7 @@
         <v>84</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>19</v>
@@ -9141,7 +9136,7 @@
         <v>88</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="E140" s="3" t="s">
         <v>16</v>
@@ -9176,7 +9171,7 @@
         <v>89</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="E141" s="3" t="s">
         <v>16</v>
@@ -9316,7 +9311,7 @@
         <v>92</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>16</v>
@@ -9351,7 +9346,7 @@
         <v>418</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="E146" s="3" t="s">
         <v>19</v>
@@ -9981,7 +9976,7 @@
         <v>446</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="E164" s="3" t="s">
         <v>1</v>
@@ -11066,7 +11061,7 @@
         <v>494</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>1</v>
@@ -11101,7 +11096,7 @@
         <v>495</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>16</v>
@@ -11136,7 +11131,7 @@
         <v>111</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>1</v>
@@ -11171,7 +11166,7 @@
         <v>112</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>0</v>
@@ -11346,7 +11341,7 @@
         <v>114</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>16</v>
@@ -12361,7 +12356,7 @@
         <v>130</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E232" s="3" t="s">
         <v>0</v>
@@ -12641,7 +12636,7 @@
         <v>554</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="E240" s="3" t="s">
         <v>0</v>
@@ -12676,7 +12671,7 @@
         <v>135</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="E241" s="3" t="s">
         <v>1</v>
@@ -12781,7 +12776,7 @@
         <v>136</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="E244" s="3" t="s">
         <v>1</v>
@@ -12956,7 +12951,7 @@
         <v>566</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>19</v>
@@ -13026,7 +13021,7 @@
         <v>568</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>19</v>
@@ -13096,7 +13091,7 @@
         <v>140</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>19</v>
@@ -13341,7 +13336,7 @@
         <v>144</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>1</v>
@@ -13446,7 +13441,7 @@
         <v>147</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>0</v>
@@ -13551,7 +13546,7 @@
         <v>149</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>1</v>
@@ -14003,7 +13998,7 @@
         <v>Hệ thống mạng đấu thầu quốc gia (Đấu thầu qua mạng)</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D279" s="1" t="s">
         <v>603</v>
@@ -14426,7 +14421,7 @@
         <v>165</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="E291" s="3" t="s">
         <v>16</v>
@@ -14642,7 +14637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:5" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:5" ht="62" x14ac:dyDescent="0.35">
       <c r="A298" s="6">
         <v>297</v>
       </c>
@@ -14671,7 +14666,7 @@
         <v>168</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>625</v>
+        <v>783</v>
       </c>
       <c r="E298" s="3" t="s">
         <v>1</v>
@@ -14706,7 +14701,7 @@
         <v>169</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E299" s="3" t="s">
         <v>0</v>
@@ -14738,10 +14733,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C300" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="D300" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="D300" s="1" t="s">
-        <v>628</v>
       </c>
       <c r="E300" s="3" t="s">
         <v>1</v>
@@ -14776,7 +14771,7 @@
         <v>170</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="E301" s="3" t="s">
         <v>19</v>
@@ -14808,10 +14803,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C302" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="D302" s="1" t="s">
         <v>630</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>631</v>
       </c>
       <c r="E302" s="3" t="s">
         <v>0</v>
@@ -14846,7 +14841,7 @@
         <v>171</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="E303" s="3" t="s">
         <v>16</v>
@@ -14881,7 +14876,7 @@
         <v>172</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="E304" s="3" t="s">
         <v>16</v>
@@ -14916,7 +14911,7 @@
         <v>173</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="E305" s="3" t="s">
         <v>16</v>
@@ -14951,7 +14946,7 @@
         <v>174</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="E306" s="3" t="s">
         <v>16</v>
@@ -14986,7 +14981,7 @@
         <v>175</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E307" s="3" t="s">
         <v>16</v>
@@ -15021,7 +15016,7 @@
         <v>176</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="E308" s="3" t="s">
         <v>16</v>
@@ -15056,7 +15051,7 @@
         <v>177</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E309" s="3" t="s">
         <v>16</v>
@@ -15088,10 +15083,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C310" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="D310" s="1" t="s">
         <v>639</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>640</v>
       </c>
       <c r="E310" s="3" t="s">
         <v>16</v>
@@ -15123,10 +15118,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E311" s="3" t="s">
         <v>16</v>
@@ -15161,7 +15156,7 @@
         <v>178</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E312" s="3" t="s">
         <v>16</v>
@@ -15196,7 +15191,7 @@
         <v>179</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="E313" s="3" t="s">
         <v>16</v>
@@ -15228,10 +15223,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C314" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="D314" s="1" t="s">
         <v>644</v>
-      </c>
-      <c r="D314" s="1" t="s">
-        <v>645</v>
       </c>
       <c r="E314" s="3" t="s">
         <v>16</v>
@@ -15266,7 +15261,7 @@
         <v>180</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="E315" s="3" t="s">
         <v>0</v>
@@ -15301,7 +15296,7 @@
         <v>181</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="E316" s="3" t="s">
         <v>1</v>
@@ -15336,7 +15331,7 @@
         <v>182</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="E317" s="3" t="s">
         <v>1</v>
@@ -15368,10 +15363,10 @@
         <v>Quy định chuyên sâu và tình huống nâng cao</v>
       </c>
       <c r="C318" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="D318" s="1" t="s">
         <v>649</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>650</v>
       </c>
       <c r="E318" s="3" t="s">
         <v>16</v>
@@ -15406,7 +15401,7 @@
         <v>183</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="E319" s="3" t="s">
         <v>1</v>
@@ -15441,7 +15436,7 @@
         <v>184</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E320" s="3" t="s">
         <v>19</v>
@@ -15476,13 +15471,13 @@
         <v>185</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="E321" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="322" spans="1:5" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:5" ht="62" x14ac:dyDescent="0.35">
       <c r="A322" s="6">
         <v>321</v>
       </c>
@@ -15511,7 +15506,7 @@
         <v>186</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>653</v>
+        <v>784</v>
       </c>
       <c r="E322" s="3" t="s">
         <v>0</v>
@@ -15546,7 +15541,7 @@
         <v>187</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E323" s="3" t="s">
         <v>19</v>
@@ -15581,7 +15576,7 @@
         <v>188</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E324" s="3" t="s">
         <v>19</v>
@@ -15616,7 +15611,7 @@
         <v>189</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E325" s="3" t="s">
         <v>1</v>
@@ -15651,7 +15646,7 @@
         <v>190</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E326" s="3" t="s">
         <v>19</v>
@@ -15686,7 +15681,7 @@
         <v>191</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E327" s="3" t="s">
         <v>19</v>
@@ -15721,7 +15716,7 @@
         <v>192</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E328" s="3" t="s">
         <v>16</v>
@@ -15753,10 +15748,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E329" s="3" t="s">
         <v>16</v>
@@ -15788,10 +15783,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E330" s="3" t="s">
         <v>16</v>
@@ -15826,7 +15821,7 @@
         <v>193</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E331" s="3" t="s">
         <v>0</v>
@@ -15858,10 +15853,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E332" s="3" t="s">
         <v>0</v>
@@ -15896,7 +15891,7 @@
         <v>4</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E333" s="3" t="s">
         <v>19</v>
@@ -15931,7 +15926,7 @@
         <v>194</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E334" s="3" t="s">
         <v>19</v>
@@ -15963,10 +15958,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E335" s="3" t="s">
         <v>19</v>
@@ -15998,10 +15993,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E336" s="3" t="s">
         <v>19</v>
@@ -16036,7 +16031,7 @@
         <v>195</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E337" s="3" t="s">
         <v>19</v>
@@ -16071,7 +16066,7 @@
         <v>196</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E338" s="3" t="s">
         <v>1</v>
@@ -16106,7 +16101,7 @@
         <v>197</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E339" s="3" t="s">
         <v>16</v>
@@ -16138,10 +16133,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E340" s="3" t="s">
         <v>1</v>
@@ -16176,7 +16171,7 @@
         <v>198</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E341" s="3" t="s">
         <v>1</v>
@@ -16211,7 +16206,7 @@
         <v>199</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="E342" s="3" t="s">
         <v>0</v>
@@ -16246,7 +16241,7 @@
         <v>200</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E343" s="3" t="s">
         <v>1</v>
@@ -16281,7 +16276,7 @@
         <v>201</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="E344" s="3" t="s">
         <v>0</v>
@@ -16316,7 +16311,7 @@
         <v>202</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E345" s="3" t="s">
         <v>16</v>
@@ -16348,10 +16343,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E346" s="3" t="s">
         <v>16</v>
@@ -16386,7 +16381,7 @@
         <v>203</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E347" s="3" t="s">
         <v>0</v>
@@ -16421,7 +16416,7 @@
         <v>204</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E348" s="3" t="s">
         <v>0</v>
@@ -16456,7 +16451,7 @@
         <v>205</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E349" s="3" t="s">
         <v>0</v>
@@ -16491,7 +16486,7 @@
         <v>206</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E350" s="3" t="s">
         <v>1</v>
@@ -16523,10 +16518,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E351" s="3" t="s">
         <v>1</v>
@@ -16561,7 +16556,7 @@
         <v>207</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E352" s="3" t="s">
         <v>19</v>
@@ -16596,7 +16591,7 @@
         <v>208</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E353" s="3" t="s">
         <v>0</v>
@@ -16628,10 +16623,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E354" s="3" t="s">
         <v>19</v>
@@ -16666,7 +16661,7 @@
         <v>209</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="E355" s="3" t="s">
         <v>0</v>
@@ -16698,10 +16693,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="E356" s="3" t="s">
         <v>1</v>
@@ -16736,7 +16731,7 @@
         <v>210</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="E357" s="3" t="s">
         <v>19</v>
@@ -16771,7 +16766,7 @@
         <v>5</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="E358" s="3" t="s">
         <v>16</v>
@@ -16806,7 +16801,7 @@
         <v>6</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="E359" s="3" t="s">
         <v>19</v>
@@ -16838,10 +16833,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E360" s="3" t="s">
         <v>16</v>
@@ -16873,10 +16868,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E361" s="3" t="s">
         <v>19</v>
@@ -16908,10 +16903,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="E362" s="3" t="s">
         <v>16</v>
@@ -16946,7 +16941,7 @@
         <v>211</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="E363" s="3" t="s">
         <v>19</v>
@@ -16981,7 +16976,7 @@
         <v>212</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="E364" s="3" t="s">
         <v>0</v>
@@ -17016,7 +17011,7 @@
         <v>213</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E365" s="3" t="s">
         <v>0</v>
@@ -17051,7 +17046,7 @@
         <v>214</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="E366" s="3" t="s">
         <v>19</v>
@@ -17086,7 +17081,7 @@
         <v>215</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E367" s="3" t="s">
         <v>19</v>
@@ -17118,16 +17113,16 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E368" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:5" ht="46.5" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:5" ht="62" x14ac:dyDescent="0.35">
       <c r="A369" s="6">
         <v>368</v>
       </c>
@@ -17156,7 +17151,7 @@
         <v>216</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>710</v>
+        <v>782</v>
       </c>
       <c r="E369" s="3" t="s">
         <v>19</v>
@@ -17188,10 +17183,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="E370" s="3" t="s">
         <v>16</v>
@@ -17226,7 +17221,7 @@
         <v>7</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E371" s="3" t="s">
         <v>1</v>
@@ -17261,7 +17256,7 @@
         <v>217</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="E372" s="3" t="s">
         <v>0</v>
@@ -17296,7 +17291,7 @@
         <v>218</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="E373" s="3" t="s">
         <v>1</v>
@@ -17331,7 +17326,7 @@
         <v>219</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="E374" s="3" t="s">
         <v>0</v>
@@ -17366,7 +17361,7 @@
         <v>220</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="E375" s="3" t="s">
         <v>1</v>
@@ -17398,10 +17393,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="E376" s="3" t="s">
         <v>0</v>
@@ -17436,7 +17431,7 @@
         <v>221</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="E377" s="3" t="s">
         <v>19</v>
@@ -17471,7 +17466,7 @@
         <v>222</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="E378" s="3" t="s">
         <v>16</v>
@@ -17506,7 +17501,7 @@
         <v>223</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E379" s="3" t="s">
         <v>19</v>
@@ -17541,7 +17536,7 @@
         <v>8</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="E380" s="3" t="s">
         <v>0</v>
@@ -17573,10 +17568,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="E381" s="3" t="s">
         <v>16</v>
@@ -17611,7 +17606,7 @@
         <v>224</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E382" s="3" t="s">
         <v>1</v>
@@ -17646,7 +17641,7 @@
         <v>225</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="E383" s="3" t="s">
         <v>0</v>
@@ -17681,7 +17676,7 @@
         <v>226</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E384" s="3" t="s">
         <v>0</v>
@@ -17716,7 +17711,7 @@
         <v>227</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="E385" s="3" t="s">
         <v>1</v>
@@ -17751,7 +17746,7 @@
         <v>228</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="E386" s="3" t="s">
         <v>16</v>
@@ -17786,7 +17781,7 @@
         <v>229</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E387" s="3" t="s">
         <v>19</v>
@@ -17821,7 +17816,7 @@
         <v>230</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="E388" s="3" t="s">
         <v>16</v>
@@ -17853,10 +17848,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="E389" s="3" t="s">
         <v>1</v>
@@ -17888,10 +17883,10 @@
         <v>Hội nhập quốc tế và đấu thầu theo FTA (CPTPP, EVFTA, UKVFTA)</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="E390" s="3" t="s">
         <v>1</v>
@@ -17926,7 +17921,7 @@
         <v>231</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="E391" s="3" t="s">
         <v>1</v>
